--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.20</t>
+          <t>Created with PyAnalyseries v5.24</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>#ffbb78</t>
+          <t>#ff7434</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>#7be32c</t>
+          <t>#21e3b9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -28602,7 +28602,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>#962cff</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>

--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Serie Id-000476B5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Serie Id-A9AA9941" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Serie Id-56TY87JG" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SAMPLE Id-4EA5A3B8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Serie Id-B54E03C0" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Serie Id-B54E03C0" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SAMPLE Id-4EA5A3B8" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="INTERPOLATION Id-20A10A97" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.24</t>
+          <t>Created with PyAnalyseries v5.26</t>
         </is>
       </c>
     </row>
@@ -458,77 +458,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="112" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Parameters</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SAMPLE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sample every 50.0</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>50.0 ; linear; True</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>&lt;BR&gt;Sample with parameters :&lt;ul&gt;&lt;li&gt;Step : 50.0&lt;li&gt;Kind of interpolation : linear&lt;li&gt;Integrated : True&lt;/ul&gt;</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -711,6 +640,77 @@
       </c>
       <c r="B14" t="n">
         <v>4.63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="112" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SAMPLE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sample every 50.0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>50.0 ; linear; True</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>&lt;BR&gt;Sample with parameters :&lt;ul&gt;&lt;li&gt;Step : 50.0&lt;li&gt;Kind of interpolation : linear&lt;li&gt;Integrated : True&lt;/ul&gt;</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.24</t>
+          <t>Created with PyAnalyseries v5.32</t>
         </is>
       </c>
     </row>
@@ -449,6 +449,14 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>Do not modify or accordingly with documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saved 2025/12/13 at 00:39:52</t>
         </is>
       </c>
     </row>
@@ -463,14 +471,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="112" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="108" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,10 +500,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -517,9 +531,10 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
-          <t>&lt;BR&gt;Sample with parameters :&lt;ul&gt;&lt;li&gt;Step : 50.0&lt;li&gt;Kind of interpolation : linear&lt;li&gt;Integrated : True&lt;/ul&gt;</t>
+          <t>Sample with parameters :&lt;ul&gt;&lt;li&gt;Step : 50.0&lt;li&gt;Kind of interpolation : linear&lt;li&gt;Integrated : True&lt;/ul&gt;</t>
         </is>
       </c>
     </row>
@@ -534,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -543,8 +558,9 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -580,10 +596,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -611,7 +632,8 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Imported serie</t>
         </is>
@@ -724,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -732,8 +754,9 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -764,10 +787,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -797,6 +825,7 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -825,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1002"/>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -834,8 +863,9 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="143" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="143" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -871,10 +901,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -902,7 +937,8 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Insolation serie "Daily insolation" with parameters:&lt;ul&gt;&lt;li&gt;Solar constant [W/m2]: 1365&lt;li&gt;Latitude [°]: 65&lt;li&gt;True longitude [°]: 90&lt;/ul&gt;</t>
         </is>
@@ -8919,7 +8955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:I385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8928,8 +8964,9 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8965,10 +9002,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -9001,6 +9043,7 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -12077,7 +12120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L385"/>
+  <dimension ref="A1:M385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12086,12 +12129,13 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="154" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="150" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12127,32 +12171,37 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>InterpolationMode</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>X1Coords</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>X2Coords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
-          <t>depthODP849 [cm]</t>
+          <t>X2Coords</t>
         </is>
       </c>
     </row>
@@ -12182,24 +12231,25 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
-          <t>&lt;BR&gt;Serie &lt;i&gt;&lt;b&gt;Id-34AE56JH&lt;/i&gt;&lt;/b&gt; interpolated with INTERPOLATION &lt;i&gt;&lt;b&gt;Id-20A10A97&lt;/i&gt;&lt;/b&gt; with mode PCHIP&lt;BR&gt;---&gt; serie &lt;i&gt;&lt;b&gt;Id-B19318ED&lt;/b&gt;&lt;/i&gt;</t>
+          <t>Serie &lt;i&gt;&lt;b&gt;Id-34AE56JH&lt;/i&gt;&lt;/b&gt; interpolated with INTERPOLATION &lt;i&gt;&lt;b&gt;Id-20A10A97&lt;/i&gt;&lt;/b&gt; with mode PCHIP&lt;BR&gt;---&gt; serie &lt;i&gt;&lt;b&gt;Id-B19318ED&lt;/b&gt;&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>PCHIP</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>124.8344370860927</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1391.467880794702</v>
       </c>
-      <c r="L2" t="n">
-        <v>7</v>
+      <c r="M2" t="n">
+        <v>1391.467880794702</v>
       </c>
     </row>
     <row r="3">
@@ -12209,14 +12259,14 @@
       <c r="B3" t="n">
         <v>0.08</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>388.3002207505519</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1986.542384105961</v>
       </c>
-      <c r="L3" t="n">
-        <v>17</v>
+      <c r="M3" t="n">
+        <v>1986.542384105961</v>
       </c>
     </row>
     <row r="4">
@@ -12226,14 +12276,14 @@
       <c r="B4" t="n">
         <v>0.19</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>582.2110375275936</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>3467.087748344371</v>
       </c>
-      <c r="L4" t="n">
-        <v>28</v>
+      <c r="M4" t="n">
+        <v>3467.087748344371</v>
       </c>
     </row>
     <row r="5">
@@ -12243,8 +12293,8 @@
       <c r="B5" t="n">
         <v>-0.15</v>
       </c>
-      <c r="L5" t="n">
-        <v>45</v>
+      <c r="M5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -12254,8 +12304,8 @@
       <c r="B6" t="n">
         <v>-0.27</v>
       </c>
-      <c r="L6" t="n">
-        <v>55</v>
+      <c r="M6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -12265,8 +12315,8 @@
       <c r="B7" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L7" t="n">
-        <v>69</v>
+      <c r="M7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -12276,8 +12326,8 @@
       <c r="B8" t="n">
         <v>-0.12</v>
       </c>
-      <c r="L8" t="n">
-        <v>89</v>
+      <c r="M8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -12287,8 +12337,8 @@
       <c r="B9" t="n">
         <v>0.02</v>
       </c>
-      <c r="L9" t="n">
-        <v>109</v>
+      <c r="M9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -12298,8 +12348,8 @@
       <c r="B10" t="n">
         <v>0.05</v>
       </c>
-      <c r="L10" t="n">
-        <v>118</v>
+      <c r="M10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -12309,8 +12359,8 @@
       <c r="B11" t="n">
         <v>0.02</v>
       </c>
-      <c r="L11" t="n">
-        <v>128</v>
+      <c r="M11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -12320,8 +12370,8 @@
       <c r="B12" t="n">
         <v>0.1</v>
       </c>
-      <c r="L12" t="n">
-        <v>139</v>
+      <c r="M12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -12331,8 +12381,8 @@
       <c r="B13" t="n">
         <v>0.05</v>
       </c>
-      <c r="L13" t="n">
-        <v>150</v>
+      <c r="M13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -12342,8 +12392,8 @@
       <c r="B14" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L14" t="n">
-        <v>161</v>
+      <c r="M14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -12353,8 +12403,8 @@
       <c r="B15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L15" t="n">
-        <v>185</v>
+      <c r="M15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -12364,8 +12414,8 @@
       <c r="B16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L16" t="n">
-        <v>194</v>
+      <c r="M16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -12375,8 +12425,8 @@
       <c r="B17" t="n">
         <v>-0.21</v>
       </c>
-      <c r="L17" t="n">
-        <v>217</v>
+      <c r="M17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -12386,8 +12436,8 @@
       <c r="B18" t="n">
         <v>-0.11</v>
       </c>
-      <c r="L18" t="n">
-        <v>231</v>
+      <c r="M18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -12397,8 +12447,8 @@
       <c r="B19" t="n">
         <v>0.3</v>
       </c>
-      <c r="L19" t="n">
-        <v>243</v>
+      <c r="M19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -12408,8 +12458,8 @@
       <c r="B20" t="n">
         <v>0.13</v>
       </c>
-      <c r="L20" t="n">
-        <v>249</v>
+      <c r="M20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -12419,8 +12469,8 @@
       <c r="B21" t="n">
         <v>0.25</v>
       </c>
-      <c r="L21" t="n">
-        <v>256</v>
+      <c r="M21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -12430,8 +12480,8 @@
       <c r="B22" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L22" t="n">
-        <v>271</v>
+      <c r="M22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -12441,8 +12491,8 @@
       <c r="B23" t="n">
         <v>0.12</v>
       </c>
-      <c r="L23" t="n">
-        <v>275</v>
+      <c r="M23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -12452,8 +12502,8 @@
       <c r="B24" t="n">
         <v>0.22</v>
       </c>
-      <c r="L24" t="n">
-        <v>280</v>
+      <c r="M24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -12463,8 +12513,8 @@
       <c r="B25" t="n">
         <v>0.21</v>
       </c>
-      <c r="L25" t="n">
-        <v>289</v>
+      <c r="M25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -12474,8 +12524,8 @@
       <c r="B26" t="n">
         <v>0.21</v>
       </c>
-      <c r="L26" t="n">
-        <v>292</v>
+      <c r="M26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -12485,8 +12535,8 @@
       <c r="B27" t="n">
         <v>0.2</v>
       </c>
-      <c r="L27" t="n">
-        <v>296</v>
+      <c r="M27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -12496,8 +12546,8 @@
       <c r="B28" t="n">
         <v>0.045</v>
       </c>
-      <c r="L28" t="n">
-        <v>306</v>
+      <c r="M28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -12507,8 +12557,8 @@
       <c r="B29" t="n">
         <v>0.17</v>
       </c>
-      <c r="L29" t="n">
-        <v>315</v>
+      <c r="M29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -12518,8 +12568,8 @@
       <c r="B30" t="n">
         <v>0.09</v>
       </c>
-      <c r="L30" t="n">
-        <v>324</v>
+      <c r="M30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -12529,8 +12579,8 @@
       <c r="B31" t="n">
         <v>-0.08500000000000001</v>
       </c>
-      <c r="L31" t="n">
-        <v>333</v>
+      <c r="M31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -12540,8 +12590,8 @@
       <c r="B32" t="n">
         <v>0.08</v>
       </c>
-      <c r="L32" t="n">
-        <v>344</v>
+      <c r="M32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -12551,8 +12601,8 @@
       <c r="B33" t="n">
         <v>0.05</v>
       </c>
-      <c r="L33" t="n">
-        <v>355</v>
+      <c r="M33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -12562,8 +12612,8 @@
       <c r="B34" t="n">
         <v>0.23</v>
       </c>
-      <c r="L34" t="n">
-        <v>366</v>
+      <c r="M34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -12573,8 +12623,8 @@
       <c r="B35" t="n">
         <v>0.12</v>
       </c>
-      <c r="L35" t="n">
-        <v>377</v>
+      <c r="M35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -12584,8 +12634,8 @@
       <c r="B36" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L36" t="n">
-        <v>388</v>
+      <c r="M36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -12595,8 +12645,8 @@
       <c r="B37" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L37" t="n">
-        <v>398</v>
+      <c r="M37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -12606,8 +12656,8 @@
       <c r="B38" t="n">
         <v>-0.23</v>
       </c>
-      <c r="L38" t="n">
-        <v>408</v>
+      <c r="M38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -12617,8 +12667,8 @@
       <c r="B39" t="n">
         <v>-0.3</v>
       </c>
-      <c r="L39" t="n">
-        <v>418</v>
+      <c r="M39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -12628,8 +12678,8 @@
       <c r="B40" t="n">
         <v>-0.3</v>
       </c>
-      <c r="L40" t="n">
-        <v>428</v>
+      <c r="M40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -12639,8 +12689,8 @@
       <c r="B41" t="n">
         <v>-0.32</v>
       </c>
-      <c r="L41" t="n">
-        <v>437</v>
+      <c r="M41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -12650,8 +12700,8 @@
       <c r="B42" t="n">
         <v>-0.38</v>
       </c>
-      <c r="L42" t="n">
-        <v>447</v>
+      <c r="M42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -12661,8 +12711,8 @@
       <c r="B43" t="n">
         <v>-0.45</v>
       </c>
-      <c r="L43" t="n">
-        <v>456</v>
+      <c r="M43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -12672,8 +12722,8 @@
       <c r="B44" t="n">
         <v>-0.33</v>
       </c>
-      <c r="L44" t="n">
-        <v>467</v>
+      <c r="M44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -12683,8 +12733,8 @@
       <c r="B45" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L45" t="n">
-        <v>477</v>
+      <c r="M45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -12694,8 +12744,8 @@
       <c r="B46" t="n">
         <v>-0.19</v>
       </c>
-      <c r="L46" t="n">
-        <v>488</v>
+      <c r="M46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -12705,8 +12755,8 @@
       <c r="B47" t="n">
         <v>-0.46</v>
       </c>
-      <c r="L47" t="n">
-        <v>498</v>
+      <c r="M47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -12716,8 +12766,8 @@
       <c r="B48" t="n">
         <v>-0.39</v>
       </c>
-      <c r="L48" t="n">
-        <v>508</v>
+      <c r="M48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -12727,8 +12777,8 @@
       <c r="B49" t="n">
         <v>-0.21</v>
       </c>
-      <c r="L49" t="n">
-        <v>518</v>
+      <c r="M49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -12738,8 +12788,8 @@
       <c r="B50" t="n">
         <v>-0.45</v>
       </c>
-      <c r="L50" t="n">
-        <v>528</v>
+      <c r="M50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -12749,8 +12799,8 @@
       <c r="B51" t="n">
         <v>-0.395</v>
       </c>
-      <c r="L51" t="n">
-        <v>538</v>
+      <c r="M51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -12760,8 +12810,8 @@
       <c r="B52" t="n">
         <v>-0.13</v>
       </c>
-      <c r="L52" t="n">
-        <v>548</v>
+      <c r="M52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -12771,8 +12821,8 @@
       <c r="B53" t="n">
         <v>-0.305</v>
       </c>
-      <c r="L53" t="n">
-        <v>558</v>
+      <c r="M53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -12782,8 +12832,8 @@
       <c r="B54" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L54" t="n">
-        <v>568</v>
+      <c r="M54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -12793,8 +12843,8 @@
       <c r="B55" t="n">
         <v>-0.35</v>
       </c>
-      <c r="L55" t="n">
-        <v>578</v>
+      <c r="M55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -12804,8 +12854,8 @@
       <c r="B56" t="n">
         <v>-0.325</v>
       </c>
-      <c r="L56" t="n">
-        <v>589</v>
+      <c r="M56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -12815,8 +12865,8 @@
       <c r="B57" t="n">
         <v>-0.41</v>
       </c>
-      <c r="L57" t="n">
-        <v>599</v>
+      <c r="M57" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -12826,8 +12876,8 @@
       <c r="B58" t="n">
         <v>-0.42</v>
       </c>
-      <c r="L58" t="n">
-        <v>608</v>
+      <c r="M58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -12837,8 +12887,8 @@
       <c r="B59" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L59" t="n">
-        <v>618</v>
+      <c r="M59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -12848,8 +12898,8 @@
       <c r="B60" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L60" t="n">
-        <v>628</v>
+      <c r="M60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -12859,8 +12909,8 @@
       <c r="B61" t="n">
         <v>-0.135</v>
       </c>
-      <c r="L61" t="n">
-        <v>638</v>
+      <c r="M61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -12870,8 +12920,8 @@
       <c r="B62" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L62" t="n">
-        <v>647</v>
+      <c r="M62" t="n">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -12881,8 +12931,8 @@
       <c r="B63" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L63" t="n">
-        <v>657</v>
+      <c r="M63" t="n">
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -12892,8 +12942,8 @@
       <c r="B64" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L64" t="n">
-        <v>667</v>
+      <c r="M64" t="n">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -12903,8 +12953,8 @@
       <c r="B65" t="n">
         <v>-0.08500000000000001</v>
       </c>
-      <c r="L65" t="n">
-        <v>677</v>
+      <c r="M65" t="n">
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -12914,8 +12964,8 @@
       <c r="B66" t="n">
         <v>-0.0433</v>
       </c>
-      <c r="L66" t="n">
-        <v>688</v>
+      <c r="M66" t="n">
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -12925,8 +12975,8 @@
       <c r="B67" t="n">
         <v>0.11</v>
       </c>
-      <c r="L67" t="n">
-        <v>698</v>
+      <c r="M67" t="n">
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -12936,8 +12986,8 @@
       <c r="B68" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L68" t="n">
-        <v>708</v>
+      <c r="M68" t="n">
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -12947,8 +12997,8 @@
       <c r="B69" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L69" t="n">
-        <v>718</v>
+      <c r="M69" t="n">
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -12958,8 +13008,8 @@
       <c r="B70" t="n">
         <v>-0.23</v>
       </c>
-      <c r="L70" t="n">
-        <v>728</v>
+      <c r="M70" t="n">
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -12969,8 +13019,8 @@
       <c r="B71" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L71" t="n">
-        <v>737</v>
+      <c r="M71" t="n">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -12980,8 +13030,8 @@
       <c r="B72" t="n">
         <v>-0.405</v>
       </c>
-      <c r="L72" t="n">
-        <v>747</v>
+      <c r="M72" t="n">
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -12991,8 +13041,8 @@
       <c r="B73" t="n">
         <v>-0.505</v>
       </c>
-      <c r="L73" t="n">
-        <v>756</v>
+      <c r="M73" t="n">
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -13002,8 +13052,8 @@
       <c r="B74" t="n">
         <v>-0.36</v>
       </c>
-      <c r="L74" t="n">
-        <v>757</v>
+      <c r="M74" t="n">
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -13013,8 +13063,8 @@
       <c r="B75" t="n">
         <v>-0.19</v>
       </c>
-      <c r="L75" t="n">
-        <v>766</v>
+      <c r="M75" t="n">
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -13024,8 +13074,8 @@
       <c r="B76" t="n">
         <v>-0.11</v>
       </c>
-      <c r="L76" t="n">
-        <v>778</v>
+      <c r="M76" t="n">
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -13035,8 +13085,8 @@
       <c r="B77" t="n">
         <v>0.15</v>
       </c>
-      <c r="L77" t="n">
-        <v>791</v>
+      <c r="M77" t="n">
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -13046,8 +13096,8 @@
       <c r="B78" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L78" t="n">
-        <v>803</v>
+      <c r="M78" t="n">
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -13057,8 +13107,8 @@
       <c r="B79" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L79" t="n">
-        <v>813</v>
+      <c r="M79" t="n">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -13068,8 +13118,8 @@
       <c r="B80" t="n">
         <v>-0.5</v>
       </c>
-      <c r="L80" t="n">
-        <v>824</v>
+      <c r="M80" t="n">
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -13079,8 +13129,8 @@
       <c r="B81" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L81" t="n">
-        <v>835</v>
+      <c r="M81" t="n">
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -13090,8 +13140,8 @@
       <c r="B82" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L82" t="n">
-        <v>849</v>
+      <c r="M82" t="n">
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -13101,8 +13151,8 @@
       <c r="B83" t="n">
         <v>-0.43</v>
       </c>
-      <c r="L83" t="n">
-        <v>861</v>
+      <c r="M83" t="n">
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -13112,8 +13162,8 @@
       <c r="B84" t="n">
         <v>-0.535</v>
       </c>
-      <c r="L84" t="n">
-        <v>871</v>
+      <c r="M84" t="n">
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -13123,8 +13173,8 @@
       <c r="B85" t="n">
         <v>-0.32</v>
       </c>
-      <c r="L85" t="n">
-        <v>879</v>
+      <c r="M85" t="n">
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -13134,8 +13184,8 @@
       <c r="B86" t="n">
         <v>-0.37</v>
       </c>
-      <c r="L86" t="n">
-        <v>889</v>
+      <c r="M86" t="n">
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -13145,8 +13195,8 @@
       <c r="B87" t="n">
         <v>-0.58</v>
       </c>
-      <c r="L87" t="n">
-        <v>895</v>
+      <c r="M87" t="n">
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -13156,8 +13206,8 @@
       <c r="B88" t="n">
         <v>-0.4</v>
       </c>
-      <c r="L88" t="n">
-        <v>905</v>
+      <c r="M88" t="n">
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -13167,8 +13217,8 @@
       <c r="B89" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L89" t="n">
-        <v>916</v>
+      <c r="M89" t="n">
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -13178,8 +13228,8 @@
       <c r="B90" t="n">
         <v>-0.095</v>
       </c>
-      <c r="L90" t="n">
-        <v>927</v>
+      <c r="M90" t="n">
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -13189,8 +13239,8 @@
       <c r="B91" t="n">
         <v>-0.32</v>
       </c>
-      <c r="L91" t="n">
-        <v>937</v>
+      <c r="M91" t="n">
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -13200,8 +13250,8 @@
       <c r="B92" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L92" t="n">
-        <v>948</v>
+      <c r="M92" t="n">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -13211,8 +13261,8 @@
       <c r="B93" t="n">
         <v>-0.19</v>
       </c>
-      <c r="L93" t="n">
-        <v>960</v>
+      <c r="M93" t="n">
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -13222,8 +13272,8 @@
       <c r="B94" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L94" t="n">
-        <v>972</v>
+      <c r="M94" t="n">
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -13233,8 +13283,8 @@
       <c r="B95" t="n">
         <v>-0.23</v>
       </c>
-      <c r="L95" t="n">
-        <v>982</v>
+      <c r="M95" t="n">
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -13244,8 +13294,8 @@
       <c r="B96" t="n">
         <v>0.05</v>
       </c>
-      <c r="L96" t="n">
-        <v>990</v>
+      <c r="M96" t="n">
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -13255,8 +13305,8 @@
       <c r="B97" t="n">
         <v>-0.1133</v>
       </c>
-      <c r="L97" t="n">
-        <v>996</v>
+      <c r="M97" t="n">
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -13266,8 +13316,8 @@
       <c r="B98" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L98" t="n">
-        <v>1003</v>
+      <c r="M98" t="n">
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -13277,8 +13327,8 @@
       <c r="B99" t="n">
         <v>0.06</v>
       </c>
-      <c r="L99" t="n">
-        <v>1012</v>
+      <c r="M99" t="n">
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -13288,8 +13338,8 @@
       <c r="B100" t="n">
         <v>0.11</v>
       </c>
-      <c r="L100" t="n">
-        <v>1026</v>
+      <c r="M100" t="n">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -13299,8 +13349,8 @@
       <c r="B101" t="n">
         <v>0.24</v>
       </c>
-      <c r="L101" t="n">
-        <v>1041</v>
+      <c r="M101" t="n">
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -13310,8 +13360,8 @@
       <c r="B102" t="n">
         <v>-0.065</v>
       </c>
-      <c r="L102" t="n">
-        <v>1052</v>
+      <c r="M102" t="n">
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -13321,8 +13371,8 @@
       <c r="B103" t="n">
         <v>-0.035</v>
       </c>
-      <c r="L103" t="n">
-        <v>1059</v>
+      <c r="M103" t="n">
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -13332,8 +13382,8 @@
       <c r="B104" t="n">
         <v>-0.12</v>
       </c>
-      <c r="L104" t="n">
-        <v>1075</v>
+      <c r="M104" t="n">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -13343,8 +13393,8 @@
       <c r="B105" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L105" t="n">
-        <v>1090</v>
+      <c r="M105" t="n">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -13354,8 +13404,8 @@
       <c r="B106" t="n">
         <v>-0.13</v>
       </c>
-      <c r="L106" t="n">
-        <v>1105</v>
+      <c r="M106" t="n">
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -13365,8 +13415,8 @@
       <c r="B107" t="n">
         <v>-0.31</v>
       </c>
-      <c r="L107" t="n">
-        <v>1117</v>
+      <c r="M107" t="n">
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -13376,8 +13426,8 @@
       <c r="B108" t="n">
         <v>-0.335</v>
       </c>
-      <c r="L108" t="n">
-        <v>1119</v>
+      <c r="M108" t="n">
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -13387,8 +13437,8 @@
       <c r="B109" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L109" t="n">
-        <v>1125</v>
+      <c r="M109" t="n">
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -13398,8 +13448,8 @@
       <c r="B110" t="n">
         <v>-0.33</v>
       </c>
-      <c r="L110" t="n">
-        <v>1137</v>
+      <c r="M110" t="n">
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -13409,8 +13459,8 @@
       <c r="B111" t="n">
         <v>-0.39</v>
       </c>
-      <c r="L111" t="n">
-        <v>1140</v>
+      <c r="M111" t="n">
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -13420,8 +13470,8 @@
       <c r="B112" t="n">
         <v>-0.19</v>
       </c>
-      <c r="L112" t="n">
-        <v>1146</v>
+      <c r="M112" t="n">
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -13431,8 +13481,8 @@
       <c r="B113" t="n">
         <v>-0.41</v>
       </c>
-      <c r="L113" t="n">
-        <v>1147</v>
+      <c r="M113" t="n">
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -13442,8 +13492,8 @@
       <c r="B114" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L114" t="n">
-        <v>1158</v>
+      <c r="M114" t="n">
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -13453,8 +13503,8 @@
       <c r="B115" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L115" t="n">
-        <v>1172</v>
+      <c r="M115" t="n">
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -13464,8 +13514,8 @@
       <c r="B116" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L116" t="n">
-        <v>1182</v>
+      <c r="M116" t="n">
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -13475,8 +13525,8 @@
       <c r="B117" t="n">
         <v>-0.08500000000000001</v>
       </c>
-      <c r="L117" t="n">
-        <v>1192</v>
+      <c r="M117" t="n">
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -13486,8 +13536,8 @@
       <c r="B118" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L118" t="n">
-        <v>1203</v>
+      <c r="M118" t="n">
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -13497,8 +13547,8 @@
       <c r="B119" t="n">
         <v>0.095</v>
       </c>
-      <c r="L119" t="n">
-        <v>1212</v>
+      <c r="M119" t="n">
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -13508,8 +13558,8 @@
       <c r="B120" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L120" t="n">
-        <v>1222</v>
+      <c r="M120" t="n">
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -13519,8 +13569,8 @@
       <c r="B121" t="n">
         <v>-0.025</v>
       </c>
-      <c r="L121" t="n">
-        <v>1232</v>
+      <c r="M121" t="n">
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -13530,8 +13580,8 @@
       <c r="B122" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="L122" t="n">
-        <v>1252</v>
+      <c r="M122" t="n">
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -13541,8 +13591,8 @@
       <c r="B123" t="n">
         <v>0.37</v>
       </c>
-      <c r="L123" t="n">
-        <v>1262</v>
+      <c r="M123" t="n">
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -13552,8 +13602,8 @@
       <c r="B124" t="n">
         <v>0.23</v>
       </c>
-      <c r="L124" t="n">
-        <v>1272</v>
+      <c r="M124" t="n">
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -13563,8 +13613,8 @@
       <c r="B125" t="n">
         <v>0.3</v>
       </c>
-      <c r="L125" t="n">
-        <v>1306</v>
+      <c r="M125" t="n">
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -13574,8 +13624,8 @@
       <c r="B126" t="n">
         <v>-0.39</v>
       </c>
-      <c r="L126" t="n">
-        <v>1328</v>
+      <c r="M126" t="n">
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -13585,8 +13635,8 @@
       <c r="B127" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L127" t="n">
-        <v>1358</v>
+      <c r="M127" t="n">
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -13596,8 +13646,8 @@
       <c r="B128" t="n">
         <v>-0.42</v>
       </c>
-      <c r="L128" t="n">
-        <v>1364</v>
+      <c r="M128" t="n">
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -13607,8 +13657,8 @@
       <c r="B129" t="n">
         <v>-0.315</v>
       </c>
-      <c r="L129" t="n">
-        <v>1369</v>
+      <c r="M129" t="n">
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -13618,8 +13668,8 @@
       <c r="B130" t="n">
         <v>-0.41</v>
       </c>
-      <c r="L130" t="n">
-        <v>1381</v>
+      <c r="M130" t="n">
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -13629,8 +13679,8 @@
       <c r="B131" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L131" t="n">
-        <v>1388</v>
+      <c r="M131" t="n">
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -13640,8 +13690,8 @@
       <c r="B132" t="n">
         <v>-0.31</v>
       </c>
-      <c r="L132" t="n">
-        <v>1395</v>
+      <c r="M132" t="n">
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -13651,8 +13701,8 @@
       <c r="B133" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L133" t="n">
-        <v>1403</v>
+      <c r="M133" t="n">
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -13662,8 +13712,8 @@
       <c r="B134" t="n">
         <v>-0.39</v>
       </c>
-      <c r="L134" t="n">
-        <v>1414</v>
+      <c r="M134" t="n">
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -13673,8 +13723,8 @@
       <c r="B135" t="n">
         <v>-0.21</v>
       </c>
-      <c r="L135" t="n">
-        <v>1436</v>
+      <c r="M135" t="n">
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -13684,8 +13734,8 @@
       <c r="B136" t="n">
         <v>-0.15</v>
       </c>
-      <c r="L136" t="n">
-        <v>1444</v>
+      <c r="M136" t="n">
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -13695,8 +13745,8 @@
       <c r="B137" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L137" t="n">
-        <v>1453</v>
+      <c r="M137" t="n">
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -13706,8 +13756,8 @@
       <c r="B138" t="n">
         <v>-0.21</v>
       </c>
-      <c r="L138" t="n">
-        <v>1464</v>
+      <c r="M138" t="n">
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -13717,8 +13767,8 @@
       <c r="B139" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L139" t="n">
-        <v>1475</v>
+      <c r="M139" t="n">
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -13728,8 +13778,8 @@
       <c r="B140" t="n">
         <v>0.34</v>
       </c>
-      <c r="L140" t="n">
-        <v>1487</v>
+      <c r="M140" t="n">
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -13739,8 +13789,8 @@
       <c r="B141" t="n">
         <v>0.3166</v>
       </c>
-      <c r="L141" t="n">
-        <v>1498</v>
+      <c r="M141" t="n">
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -13750,8 +13800,8 @@
       <c r="B142" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="L142" t="n">
-        <v>1518</v>
+      <c r="M142" t="n">
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -13761,8 +13811,8 @@
       <c r="B143" t="n">
         <v>0.38</v>
       </c>
-      <c r="L143" t="n">
-        <v>1527</v>
+      <c r="M143" t="n">
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -13772,8 +13822,8 @@
       <c r="B144" t="n">
         <v>0.33</v>
       </c>
-      <c r="L144" t="n">
-        <v>1537</v>
+      <c r="M144" t="n">
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -13783,8 +13833,8 @@
       <c r="B145" t="n">
         <v>0.285</v>
       </c>
-      <c r="L145" t="n">
-        <v>1547</v>
+      <c r="M145" t="n">
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -13794,8 +13844,8 @@
       <c r="B146" t="n">
         <v>0.16</v>
       </c>
-      <c r="L146" t="n">
-        <v>1557</v>
+      <c r="M146" t="n">
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -13805,8 +13855,8 @@
       <c r="B147" t="n">
         <v>0.31</v>
       </c>
-      <c r="L147" t="n">
-        <v>1567</v>
+      <c r="M147" t="n">
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -13816,8 +13866,8 @@
       <c r="B148" t="n">
         <v>0.29</v>
       </c>
-      <c r="L148" t="n">
-        <v>1577</v>
+      <c r="M148" t="n">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -13827,8 +13877,8 @@
       <c r="B149" t="n">
         <v>0.28</v>
       </c>
-      <c r="L149" t="n">
-        <v>1587</v>
+      <c r="M149" t="n">
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -13838,8 +13888,8 @@
       <c r="B150" t="n">
         <v>0.18</v>
       </c>
-      <c r="L150" t="n">
-        <v>1597</v>
+      <c r="M150" t="n">
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -13849,8 +13899,8 @@
       <c r="B151" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L151" t="n">
-        <v>1607</v>
+      <c r="M151" t="n">
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -13860,8 +13910,8 @@
       <c r="B152" t="n">
         <v>-0.1</v>
       </c>
-      <c r="L152" t="n">
-        <v>1617</v>
+      <c r="M152" t="n">
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -13871,8 +13921,8 @@
       <c r="B153" t="n">
         <v>-0.31</v>
       </c>
-      <c r="L153" t="n">
-        <v>1637</v>
+      <c r="M153" t="n">
+        <v/>
       </c>
     </row>
     <row r="154">
@@ -13882,8 +13932,8 @@
       <c r="B154" t="n">
         <v>-0.12</v>
       </c>
-      <c r="L154" t="n">
-        <v>1647</v>
+      <c r="M154" t="n">
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -13893,8 +13943,8 @@
       <c r="B155" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L155" t="n">
-        <v>1657</v>
+      <c r="M155" t="n">
+        <v/>
       </c>
     </row>
     <row r="156">
@@ -13904,8 +13954,8 @@
       <c r="B156" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L156" t="n">
-        <v>1667</v>
+      <c r="M156" t="n">
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -13915,8 +13965,8 @@
       <c r="B157" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L157" t="n">
-        <v>1677</v>
+      <c r="M157" t="n">
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -13926,8 +13976,8 @@
       <c r="B158" t="n">
         <v>-0.025</v>
       </c>
-      <c r="L158" t="n">
-        <v>1687</v>
+      <c r="M158" t="n">
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -13937,8 +13987,8 @@
       <c r="B159" t="n">
         <v>-0.18</v>
       </c>
-      <c r="L159" t="n">
-        <v>1697</v>
+      <c r="M159" t="n">
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -13948,8 +13998,8 @@
       <c r="B160" t="n">
         <v>0</v>
       </c>
-      <c r="L160" t="n">
-        <v>1707</v>
+      <c r="M160" t="n">
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -13959,8 +14009,8 @@
       <c r="B161" t="n">
         <v>-0.11</v>
       </c>
-      <c r="L161" t="n">
-        <v>1717</v>
+      <c r="M161" t="n">
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -13970,8 +14020,8 @@
       <c r="B162" t="n">
         <v>0.09</v>
       </c>
-      <c r="L162" t="n">
-        <v>1737</v>
+      <c r="M162" t="n">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -13981,8 +14031,8 @@
       <c r="B163" t="n">
         <v>0.0566</v>
       </c>
-      <c r="L163" t="n">
-        <v>1747</v>
+      <c r="M163" t="n">
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -13992,8 +14042,8 @@
       <c r="B164" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L164" t="n">
-        <v>1757</v>
+      <c r="M164" t="n">
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -14003,8 +14053,8 @@
       <c r="B165" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L165" t="n">
-        <v>1767</v>
+      <c r="M165" t="n">
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -14014,8 +14064,8 @@
       <c r="B166" t="n">
         <v>-0.05</v>
       </c>
-      <c r="L166" t="n">
-        <v>1777</v>
+      <c r="M166" t="n">
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -14025,8 +14075,8 @@
       <c r="B167" t="n">
         <v>-0.12</v>
       </c>
-      <c r="L167" t="n">
-        <v>1787</v>
+      <c r="M167" t="n">
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -14036,8 +14086,8 @@
       <c r="B168" t="n">
         <v>-0.35</v>
       </c>
-      <c r="L168" t="n">
-        <v>1797</v>
+      <c r="M168" t="n">
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -14047,8 +14097,8 @@
       <c r="B169" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L169" t="n">
-        <v>1807</v>
+      <c r="M169" t="n">
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -14058,8 +14108,8 @@
       <c r="B170" t="n">
         <v>0.01</v>
       </c>
-      <c r="L170" t="n">
-        <v>1817</v>
+      <c r="M170" t="n">
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -14069,8 +14119,8 @@
       <c r="B171" t="n">
         <v>0.06</v>
       </c>
-      <c r="L171" t="n">
-        <v>1827</v>
+      <c r="M171" t="n">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -14080,8 +14130,8 @@
       <c r="B172" t="n">
         <v>0.05</v>
       </c>
-      <c r="L172" t="n">
-        <v>1837</v>
+      <c r="M172" t="n">
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -14091,8 +14141,8 @@
       <c r="B173" t="n">
         <v>0.05</v>
       </c>
-      <c r="L173" t="n">
-        <v>1847</v>
+      <c r="M173" t="n">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -14102,8 +14152,8 @@
       <c r="B174" t="n">
         <v>-0.17</v>
       </c>
-      <c r="L174" t="n">
-        <v>1857</v>
+      <c r="M174" t="n">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -14113,8 +14163,8 @@
       <c r="B175" t="n">
         <v>-0.36</v>
       </c>
-      <c r="L175" t="n">
-        <v>1867</v>
+      <c r="M175" t="n">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -14124,8 +14174,8 @@
       <c r="B176" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L176" t="n">
-        <v>1887</v>
+      <c r="M176" t="n">
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -14135,8 +14185,8 @@
       <c r="B177" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L177" t="n">
-        <v>1897</v>
+      <c r="M177" t="n">
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -14146,8 +14196,8 @@
       <c r="B178" t="n">
         <v>-0.24</v>
       </c>
-      <c r="L178" t="n">
-        <v>1903</v>
+      <c r="M178" t="n">
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -14157,8 +14207,8 @@
       <c r="B179" t="n">
         <v>-0.05</v>
       </c>
-      <c r="L179" t="n">
-        <v>1907</v>
+      <c r="M179" t="n">
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -14168,8 +14218,8 @@
       <c r="B180" t="n">
         <v>-0.42</v>
       </c>
-      <c r="L180" t="n">
-        <v>1915</v>
+      <c r="M180" t="n">
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -14179,8 +14229,8 @@
       <c r="B181" t="n">
         <v>-0.39</v>
       </c>
-      <c r="L181" t="n">
-        <v>1927</v>
+      <c r="M181" t="n">
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -14190,8 +14240,8 @@
       <c r="B182" t="n">
         <v>-0.37</v>
       </c>
-      <c r="L182" t="n">
-        <v>1938</v>
+      <c r="M182" t="n">
+        <v/>
       </c>
     </row>
     <row r="183">
@@ -14201,8 +14251,8 @@
       <c r="B183" t="n">
         <v>-0.5</v>
       </c>
-      <c r="L183" t="n">
-        <v>1948</v>
+      <c r="M183" t="n">
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -14212,8 +14262,8 @@
       <c r="B184" t="n">
         <v>-0.63</v>
       </c>
-      <c r="L184" t="n">
-        <v>1957</v>
+      <c r="M184" t="n">
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -14223,8 +14273,8 @@
       <c r="B185" t="n">
         <v>-0.66</v>
       </c>
-      <c r="L185" t="n">
-        <v>1966</v>
+      <c r="M185" t="n">
+        <v/>
       </c>
     </row>
     <row r="186">
@@ -14234,8 +14284,8 @@
       <c r="B186" t="n">
         <v>-0.67</v>
       </c>
-      <c r="L186" t="n">
-        <v>1975</v>
+      <c r="M186" t="n">
+        <v/>
       </c>
     </row>
     <row r="187">
@@ -14245,8 +14295,8 @@
       <c r="B187" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="L187" t="n">
-        <v>1985</v>
+      <c r="M187" t="n">
+        <v/>
       </c>
     </row>
     <row r="188">
@@ -14256,8 +14306,8 @@
       <c r="B188" t="n">
         <v>-0.48</v>
       </c>
-      <c r="L188" t="n">
-        <v>1995</v>
+      <c r="M188" t="n">
+        <v/>
       </c>
     </row>
     <row r="189">
@@ -14267,8 +14317,8 @@
       <c r="B189" t="n">
         <v>-0.39</v>
       </c>
-      <c r="L189" t="n">
-        <v>2006</v>
+      <c r="M189" t="n">
+        <v/>
       </c>
     </row>
     <row r="190">
@@ -14278,8 +14328,8 @@
       <c r="B190" t="n">
         <v>-0.24</v>
       </c>
-      <c r="L190" t="n">
-        <v>2017</v>
+      <c r="M190" t="n">
+        <v/>
       </c>
     </row>
     <row r="191">
@@ -14289,8 +14339,8 @@
       <c r="B191" t="n">
         <v>-0.33</v>
       </c>
-      <c r="L191" t="n">
-        <v>2028</v>
+      <c r="M191" t="n">
+        <v/>
       </c>
     </row>
     <row r="192">
@@ -14300,8 +14350,8 @@
       <c r="B192" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L192" t="n">
-        <v>2038</v>
+      <c r="M192" t="n">
+        <v/>
       </c>
     </row>
     <row r="193">
@@ -14311,8 +14361,8 @@
       <c r="B193" t="n">
         <v>-0.1</v>
       </c>
-      <c r="L193" t="n">
-        <v>2047</v>
+      <c r="M193" t="n">
+        <v/>
       </c>
     </row>
     <row r="194">
@@ -14322,8 +14372,8 @@
       <c r="B194" t="n">
         <v>0.05</v>
       </c>
-      <c r="L194" t="n">
-        <v>2055</v>
+      <c r="M194" t="n">
+        <v/>
       </c>
     </row>
     <row r="195">
@@ -14333,8 +14383,8 @@
       <c r="B195" t="n">
         <v>0.24</v>
       </c>
-      <c r="L195" t="n">
-        <v>2063</v>
+      <c r="M195" t="n">
+        <v/>
       </c>
     </row>
     <row r="196">
@@ -14344,8 +14394,8 @@
       <c r="B196" t="n">
         <v>-0.11</v>
       </c>
-      <c r="L196" t="n">
-        <v>2070</v>
+      <c r="M196" t="n">
+        <v/>
       </c>
     </row>
     <row r="197">
@@ -14355,8 +14405,8 @@
       <c r="B197" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L197" t="n">
-        <v>2071</v>
+      <c r="M197" t="n">
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -14366,8 +14416,8 @@
       <c r="B198" t="n">
         <v>0.03</v>
       </c>
-      <c r="L198" t="n">
-        <v>2078</v>
+      <c r="M198" t="n">
+        <v/>
       </c>
     </row>
     <row r="199">
@@ -14377,8 +14427,8 @@
       <c r="B199" t="n">
         <v>-0.155</v>
       </c>
-      <c r="L199" t="n">
-        <v>2085</v>
+      <c r="M199" t="n">
+        <v/>
       </c>
     </row>
     <row r="200">
@@ -14388,8 +14438,8 @@
       <c r="B200" t="n">
         <v>-0.17</v>
       </c>
-      <c r="L200" t="n">
-        <v>2092</v>
+      <c r="M200" t="n">
+        <v/>
       </c>
     </row>
     <row r="201">
@@ -14399,8 +14449,8 @@
       <c r="B201" t="n">
         <v>-0.21</v>
       </c>
-      <c r="L201" t="n">
-        <v>2100</v>
+      <c r="M201" t="n">
+        <v/>
       </c>
     </row>
     <row r="202">
@@ -14410,8 +14460,8 @@
       <c r="B202" t="n">
         <v>-0.11</v>
       </c>
-      <c r="L202" t="n">
-        <v>2116</v>
+      <c r="M202" t="n">
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -14421,8 +14471,8 @@
       <c r="B203" t="n">
         <v>-0.33</v>
       </c>
-      <c r="L203" t="n">
-        <v>2123</v>
+      <c r="M203" t="n">
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -14432,8 +14482,8 @@
       <c r="B204" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L204" t="n">
-        <v>2124</v>
+      <c r="M204" t="n">
+        <v/>
       </c>
     </row>
     <row r="205">
@@ -14443,8 +14493,8 @@
       <c r="B205" t="n">
         <v>-0.31</v>
       </c>
-      <c r="L205" t="n">
-        <v>2133</v>
+      <c r="M205" t="n">
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -14454,8 +14504,8 @@
       <c r="B206" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L206" t="n">
-        <v>2141</v>
+      <c r="M206" t="n">
+        <v/>
       </c>
     </row>
     <row r="207">
@@ -14465,8 +14515,8 @@
       <c r="B207" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="L207" t="n">
-        <v>2142</v>
+      <c r="M207" t="n">
+        <v/>
       </c>
     </row>
     <row r="208">
@@ -14476,8 +14526,8 @@
       <c r="B208" t="n">
         <v>-0.23</v>
       </c>
-      <c r="L208" t="n">
-        <v>2150</v>
+      <c r="M208" t="n">
+        <v/>
       </c>
     </row>
     <row r="209">
@@ -14487,8 +14537,8 @@
       <c r="B209" t="n">
         <v>-0.27</v>
       </c>
-      <c r="L209" t="n">
-        <v>2159</v>
+      <c r="M209" t="n">
+        <v/>
       </c>
     </row>
     <row r="210">
@@ -14498,8 +14548,8 @@
       <c r="B210" t="n">
         <v>-0.41</v>
       </c>
-      <c r="L210" t="n">
-        <v>2167</v>
+      <c r="M210" t="n">
+        <v/>
       </c>
     </row>
     <row r="211">
@@ -14509,8 +14559,8 @@
       <c r="B211" t="n">
         <v>-0.445</v>
       </c>
-      <c r="L211" t="n">
-        <v>2175</v>
+      <c r="M211" t="n">
+        <v/>
       </c>
     </row>
     <row r="212">
@@ -14520,8 +14570,8 @@
       <c r="B212" t="n">
         <v>-0.41</v>
       </c>
-      <c r="L212" t="n">
-        <v>2184</v>
+      <c r="M212" t="n">
+        <v/>
       </c>
     </row>
     <row r="213">
@@ -14531,8 +14581,8 @@
       <c r="B213" t="n">
         <v>-0.475</v>
       </c>
-      <c r="L213" t="n">
-        <v>2193</v>
+      <c r="M213" t="n">
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -14542,8 +14592,8 @@
       <c r="B214" t="n">
         <v>-0.44</v>
       </c>
-      <c r="L214" t="n">
-        <v>2203</v>
+      <c r="M214" t="n">
+        <v/>
       </c>
     </row>
     <row r="215">
@@ -14553,8 +14603,8 @@
       <c r="B215" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L215" t="n">
-        <v>2213</v>
+      <c r="M215" t="n">
+        <v/>
       </c>
     </row>
     <row r="216">
@@ -14564,8 +14614,8 @@
       <c r="B216" t="n">
         <v>-0.205</v>
       </c>
-      <c r="L216" t="n">
-        <v>2224</v>
+      <c r="M216" t="n">
+        <v/>
       </c>
     </row>
     <row r="217">
@@ -14575,8 +14625,8 @@
       <c r="B217" t="n">
         <v>0.04</v>
       </c>
-      <c r="L217" t="n">
-        <v>2235</v>
+      <c r="M217" t="n">
+        <v/>
       </c>
     </row>
     <row r="218">
@@ -14586,8 +14636,8 @@
       <c r="B218" t="n">
         <v>0.09</v>
       </c>
-      <c r="L218" t="n">
-        <v>2246</v>
+      <c r="M218" t="n">
+        <v/>
       </c>
     </row>
     <row r="219">
@@ -14597,8 +14647,8 @@
       <c r="B219" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L219" t="n">
-        <v>2257</v>
+      <c r="M219" t="n">
+        <v/>
       </c>
     </row>
     <row r="220">
@@ -14608,8 +14658,8 @@
       <c r="B220" t="n">
         <v>-0.23</v>
       </c>
-      <c r="L220" t="n">
-        <v>2267</v>
+      <c r="M220" t="n">
+        <v/>
       </c>
     </row>
     <row r="221">
@@ -14619,8 +14669,8 @@
       <c r="B221" t="n">
         <v>-0.35</v>
       </c>
-      <c r="L221" t="n">
-        <v>2276</v>
+      <c r="M221" t="n">
+        <v/>
       </c>
     </row>
     <row r="222">
@@ -14630,8 +14680,8 @@
       <c r="B222" t="n">
         <v>-0.58</v>
       </c>
-      <c r="L222" t="n">
-        <v>2285</v>
+      <c r="M222" t="n">
+        <v/>
       </c>
     </row>
     <row r="223">
@@ -14641,8 +14691,8 @@
       <c r="B223" t="n">
         <v>-0.53</v>
       </c>
-      <c r="L223" t="n">
-        <v>2294</v>
+      <c r="M223" t="n">
+        <v/>
       </c>
     </row>
     <row r="224">
@@ -14652,8 +14702,8 @@
       <c r="B224" t="n">
         <v>-0.59</v>
       </c>
-      <c r="L224" t="n">
-        <v>2303</v>
+      <c r="M224" t="n">
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -14663,8 +14713,8 @@
       <c r="B225" t="n">
         <v>-0.3</v>
       </c>
-      <c r="L225" t="n">
-        <v>2312</v>
+      <c r="M225" t="n">
+        <v/>
       </c>
     </row>
     <row r="226">
@@ -14674,8 +14724,8 @@
       <c r="B226" t="n">
         <v>-0.245</v>
       </c>
-      <c r="L226" t="n">
-        <v>2322</v>
+      <c r="M226" t="n">
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -14685,8 +14735,8 @@
       <c r="B227" t="n">
         <v>-0.27</v>
       </c>
-      <c r="L227" t="n">
-        <v>2334</v>
+      <c r="M227" t="n">
+        <v/>
       </c>
     </row>
     <row r="228">
@@ -14696,8 +14746,8 @@
       <c r="B228" t="n">
         <v>-0.18</v>
       </c>
-      <c r="L228" t="n">
-        <v>2347</v>
+      <c r="M228" t="n">
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -14707,8 +14757,8 @@
       <c r="B229" t="n">
         <v>-0.245</v>
       </c>
-      <c r="L229" t="n">
-        <v>2361</v>
+      <c r="M229" t="n">
+        <v/>
       </c>
     </row>
     <row r="230">
@@ -14718,8 +14768,8 @@
       <c r="B230" t="n">
         <v>-0.405</v>
       </c>
-      <c r="L230" t="n">
-        <v>2375</v>
+      <c r="M230" t="n">
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -14729,8 +14779,8 @@
       <c r="B231" t="n">
         <v>-0.325</v>
       </c>
-      <c r="L231" t="n">
-        <v>2388</v>
+      <c r="M231" t="n">
+        <v/>
       </c>
     </row>
     <row r="232">
@@ -14740,8 +14790,8 @@
       <c r="B232" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L232" t="n">
-        <v>2399</v>
+      <c r="M232" t="n">
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -14751,8 +14801,8 @@
       <c r="B233" t="n">
         <v>-0.4</v>
       </c>
-      <c r="L233" t="n">
-        <v>2410</v>
+      <c r="M233" t="n">
+        <v/>
       </c>
     </row>
     <row r="234">
@@ -14762,8 +14812,8 @@
       <c r="B234" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L234" t="n">
-        <v>2420</v>
+      <c r="M234" t="n">
+        <v/>
       </c>
     </row>
     <row r="235">
@@ -14773,8 +14823,8 @@
       <c r="B235" t="n">
         <v>-0.2166</v>
       </c>
-      <c r="L235" t="n">
-        <v>2430</v>
+      <c r="M235" t="n">
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -14784,8 +14834,8 @@
       <c r="B236" t="n">
         <v>-0.125</v>
       </c>
-      <c r="L236" t="n">
-        <v>2440</v>
+      <c r="M236" t="n">
+        <v/>
       </c>
     </row>
     <row r="237">
@@ -14795,8 +14845,8 @@
       <c r="B237" t="n">
         <v>-0.48</v>
       </c>
-      <c r="L237" t="n">
-        <v>2450</v>
+      <c r="M237" t="n">
+        <v/>
       </c>
     </row>
     <row r="238">
@@ -14806,8 +14856,8 @@
       <c r="B238" t="n">
         <v>-0.47</v>
       </c>
-      <c r="L238" t="n">
-        <v>2461</v>
+      <c r="M238" t="n">
+        <v/>
       </c>
     </row>
     <row r="239">
@@ -14817,8 +14867,8 @@
       <c r="B239" t="n">
         <v>-0.27</v>
       </c>
-      <c r="L239" t="n">
-        <v>2472</v>
+      <c r="M239" t="n">
+        <v/>
       </c>
     </row>
     <row r="240">
@@ -14828,8 +14878,8 @@
       <c r="B240" t="n">
         <v>-0.65</v>
       </c>
-      <c r="L240" t="n">
-        <v>2484</v>
+      <c r="M240" t="n">
+        <v/>
       </c>
     </row>
     <row r="241">
@@ -14839,8 +14889,8 @@
       <c r="B241" t="n">
         <v>-0.7</v>
       </c>
-      <c r="L241" t="n">
-        <v>2495</v>
+      <c r="M241" t="n">
+        <v/>
       </c>
     </row>
     <row r="242">
@@ -14850,8 +14900,8 @@
       <c r="B242" t="n">
         <v>-0.58</v>
       </c>
-      <c r="L242" t="n">
-        <v>2506</v>
+      <c r="M242" t="n">
+        <v/>
       </c>
     </row>
     <row r="243">
@@ -14861,8 +14911,8 @@
       <c r="B243" t="n">
         <v>-0.79</v>
       </c>
-      <c r="L243" t="n">
-        <v>2514</v>
+      <c r="M243" t="n">
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -14872,8 +14922,8 @@
       <c r="B244" t="n">
         <v>-0.37</v>
       </c>
-      <c r="L244" t="n">
-        <v>2517</v>
+      <c r="M244" t="n">
+        <v/>
       </c>
     </row>
     <row r="245">
@@ -14883,8 +14933,8 @@
       <c r="B245" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L245" t="n">
-        <v>2527</v>
+      <c r="M245" t="n">
+        <v/>
       </c>
     </row>
     <row r="246">
@@ -14894,8 +14944,8 @@
       <c r="B246" t="n">
         <v>-0.595</v>
       </c>
-      <c r="L246" t="n">
-        <v>2537</v>
+      <c r="M246" t="n">
+        <v/>
       </c>
     </row>
     <row r="247">
@@ -14905,8 +14955,8 @@
       <c r="B247" t="n">
         <v>-0.64</v>
       </c>
-      <c r="L247" t="n">
-        <v>2542</v>
+      <c r="M247" t="n">
+        <v/>
       </c>
     </row>
     <row r="248">
@@ -14916,8 +14966,8 @@
       <c r="B248" t="n">
         <v>-0.44</v>
       </c>
-      <c r="L248" t="n">
-        <v>2546</v>
+      <c r="M248" t="n">
+        <v/>
       </c>
     </row>
     <row r="249">
@@ -14927,8 +14977,8 @@
       <c r="B249" t="n">
         <v>-0.51</v>
       </c>
-      <c r="L249" t="n">
-        <v>2552</v>
+      <c r="M249" t="n">
+        <v/>
       </c>
     </row>
     <row r="250">
@@ -14938,8 +14988,8 @@
       <c r="B250" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L250" t="n">
-        <v>2562</v>
+      <c r="M250" t="n">
+        <v/>
       </c>
     </row>
     <row r="251">
@@ -14949,8 +14999,8 @@
       <c r="B251" t="n">
         <v>-0.49</v>
       </c>
-      <c r="L251" t="n">
-        <v>2571</v>
+      <c r="M251" t="n">
+        <v/>
       </c>
     </row>
     <row r="252">
@@ -14960,8 +15010,8 @@
       <c r="B252" t="n">
         <v>-0.57</v>
       </c>
-      <c r="L252" t="n">
-        <v>2583</v>
+      <c r="M252" t="n">
+        <v/>
       </c>
     </row>
     <row r="253">
@@ -14971,8 +15021,8 @@
       <c r="B253" t="n">
         <v>-0.64</v>
       </c>
-      <c r="L253" t="n">
-        <v>2592</v>
+      <c r="M253" t="n">
+        <v/>
       </c>
     </row>
     <row r="254">
@@ -14982,8 +15032,8 @@
       <c r="B254" t="n">
         <v>-0.85</v>
       </c>
-      <c r="L254" t="n">
-        <v>2602</v>
+      <c r="M254" t="n">
+        <v/>
       </c>
     </row>
     <row r="255">
@@ -14993,8 +15043,8 @@
       <c r="B255" t="n">
         <v>-0.9</v>
       </c>
-      <c r="L255" t="n">
-        <v>2612</v>
+      <c r="M255" t="n">
+        <v/>
       </c>
     </row>
     <row r="256">
@@ -15004,8 +15054,8 @@
       <c r="B256" t="n">
         <v>-0.72</v>
       </c>
-      <c r="L256" t="n">
-        <v>2622</v>
+      <c r="M256" t="n">
+        <v/>
       </c>
     </row>
     <row r="257">
@@ -15015,8 +15065,8 @@
       <c r="B257" t="n">
         <v>-0.79</v>
       </c>
-      <c r="L257" t="n">
-        <v>2632</v>
+      <c r="M257" t="n">
+        <v/>
       </c>
     </row>
     <row r="258">
@@ -15026,8 +15076,8 @@
       <c r="B258" t="n">
         <v>-0.53</v>
       </c>
-      <c r="L258" t="n">
-        <v>2652</v>
+      <c r="M258" t="n">
+        <v/>
       </c>
     </row>
     <row r="259">
@@ -15037,8 +15087,8 @@
       <c r="B259" t="n">
         <v>-0.5</v>
       </c>
-      <c r="L259" t="n">
-        <v>2662</v>
+      <c r="M259" t="n">
+        <v/>
       </c>
     </row>
     <row r="260">
@@ -15048,8 +15098,8 @@
       <c r="B260" t="n">
         <v>-0.52</v>
       </c>
-      <c r="L260" t="n">
-        <v>2674</v>
+      <c r="M260" t="n">
+        <v/>
       </c>
     </row>
     <row r="261">
@@ -15059,8 +15109,8 @@
       <c r="B261" t="n">
         <v>-0.45</v>
       </c>
-      <c r="L261" t="n">
-        <v>2676</v>
+      <c r="M261" t="n">
+        <v/>
       </c>
     </row>
     <row r="262">
@@ -15070,8 +15120,8 @@
       <c r="B262" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L262" t="n">
-        <v>2681</v>
+      <c r="M262" t="n">
+        <v/>
       </c>
     </row>
     <row r="263">
@@ -15081,8 +15131,8 @@
       <c r="B263" t="n">
         <v>0.05</v>
       </c>
-      <c r="L263" t="n">
-        <v>2686</v>
+      <c r="M263" t="n">
+        <v/>
       </c>
     </row>
     <row r="264">
@@ -15092,8 +15142,8 @@
       <c r="B264" t="n">
         <v>0.09</v>
       </c>
-      <c r="L264" t="n">
-        <v>2696</v>
+      <c r="M264" t="n">
+        <v/>
       </c>
     </row>
     <row r="265">
@@ -15103,8 +15153,8 @@
       <c r="B265" t="n">
         <v>-0.37</v>
       </c>
-      <c r="L265" t="n">
-        <v>2706</v>
+      <c r="M265" t="n">
+        <v/>
       </c>
     </row>
     <row r="266">
@@ -15114,8 +15164,8 @@
       <c r="B266" t="n">
         <v>-0.57</v>
       </c>
-      <c r="L266" t="n">
-        <v>2726</v>
+      <c r="M266" t="n">
+        <v/>
       </c>
     </row>
     <row r="267">
@@ -15125,8 +15175,8 @@
       <c r="B267" t="n">
         <v>-0.5</v>
       </c>
-      <c r="L267" t="n">
-        <v>2736</v>
+      <c r="M267" t="n">
+        <v/>
       </c>
     </row>
     <row r="268">
@@ -15136,8 +15186,8 @@
       <c r="B268" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L268" t="n">
-        <v>2746</v>
+      <c r="M268" t="n">
+        <v/>
       </c>
     </row>
     <row r="269">
@@ -15147,8 +15197,8 @@
       <c r="B269" t="n">
         <v>-0.12</v>
       </c>
-      <c r="L269" t="n">
-        <v>2756</v>
+      <c r="M269" t="n">
+        <v/>
       </c>
     </row>
     <row r="270">
@@ -15158,8 +15208,8 @@
       <c r="B270" t="n">
         <v>-0.13</v>
       </c>
-      <c r="L270" t="n">
-        <v>2766</v>
+      <c r="M270" t="n">
+        <v/>
       </c>
     </row>
     <row r="271">
@@ -15169,8 +15219,8 @@
       <c r="B271" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L271" t="n">
-        <v>2776</v>
+      <c r="M271" t="n">
+        <v/>
       </c>
     </row>
     <row r="272">
@@ -15180,8 +15230,8 @@
       <c r="B272" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L272" t="n">
-        <v>2786</v>
+      <c r="M272" t="n">
+        <v/>
       </c>
     </row>
     <row r="273">
@@ -15191,8 +15241,8 @@
       <c r="B273" t="n">
         <v>-0.32</v>
       </c>
-      <c r="L273" t="n">
-        <v>2796</v>
+      <c r="M273" t="n">
+        <v/>
       </c>
     </row>
     <row r="274">
@@ -15202,8 +15252,8 @@
       <c r="B274" t="n">
         <v>-0.32</v>
       </c>
-      <c r="L274" t="n">
-        <v>2806</v>
+      <c r="M274" t="n">
+        <v/>
       </c>
     </row>
     <row r="275">
@@ -15213,8 +15263,8 @@
       <c r="B275" t="n">
         <v>0.03</v>
       </c>
-      <c r="L275" t="n">
-        <v>2815</v>
+      <c r="M275" t="n">
+        <v/>
       </c>
     </row>
     <row r="276">
@@ -15224,8 +15274,8 @@
       <c r="B276" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L276" t="n">
-        <v>2826</v>
+      <c r="M276" t="n">
+        <v/>
       </c>
     </row>
     <row r="277">
@@ -15235,8 +15285,8 @@
       <c r="B277" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L277" t="n">
-        <v>2837</v>
+      <c r="M277" t="n">
+        <v/>
       </c>
     </row>
     <row r="278">
@@ -15246,8 +15296,8 @@
       <c r="B278" t="n">
         <v>-0.23</v>
       </c>
-      <c r="L278" t="n">
-        <v>2847</v>
+      <c r="M278" t="n">
+        <v/>
       </c>
     </row>
     <row r="279">
@@ -15257,8 +15307,8 @@
       <c r="B279" t="n">
         <v>-0.11</v>
       </c>
-      <c r="L279" t="n">
-        <v>2856</v>
+      <c r="M279" t="n">
+        <v/>
       </c>
     </row>
     <row r="280">
@@ -15268,8 +15318,8 @@
       <c r="B280" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L280" t="n">
-        <v>2866</v>
+      <c r="M280" t="n">
+        <v/>
       </c>
     </row>
     <row r="281">
@@ -15279,8 +15329,8 @@
       <c r="B281" t="n">
         <v>0.02</v>
       </c>
-      <c r="L281" t="n">
-        <v>2875</v>
+      <c r="M281" t="n">
+        <v/>
       </c>
     </row>
     <row r="282">
@@ -15290,8 +15340,8 @@
       <c r="B282" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L282" t="n">
-        <v>2885</v>
+      <c r="M282" t="n">
+        <v/>
       </c>
     </row>
     <row r="283">
@@ -15301,8 +15351,8 @@
       <c r="B283" t="n">
         <v>0.05</v>
       </c>
-      <c r="L283" t="n">
-        <v>2896</v>
+      <c r="M283" t="n">
+        <v/>
       </c>
     </row>
     <row r="284">
@@ -15312,8 +15362,8 @@
       <c r="B284" t="n">
         <v>-0.12</v>
       </c>
-      <c r="L284" t="n">
-        <v>2906</v>
+      <c r="M284" t="n">
+        <v/>
       </c>
     </row>
     <row r="285">
@@ -15323,8 +15373,8 @@
       <c r="B285" t="n">
         <v>-0.14</v>
       </c>
-      <c r="L285" t="n">
-        <v>2916</v>
+      <c r="M285" t="n">
+        <v/>
       </c>
     </row>
     <row r="286">
@@ -15334,8 +15384,8 @@
       <c r="B286" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L286" t="n">
-        <v>2925</v>
+      <c r="M286" t="n">
+        <v/>
       </c>
     </row>
     <row r="287">
@@ -15345,8 +15395,8 @@
       <c r="B287" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L287" t="n">
-        <v>2936</v>
+      <c r="M287" t="n">
+        <v/>
       </c>
     </row>
     <row r="288">
@@ -15356,8 +15406,8 @@
       <c r="B288" t="n">
         <v>-0.58</v>
       </c>
-      <c r="L288" t="n">
-        <v>2953</v>
+      <c r="M288" t="n">
+        <v/>
       </c>
     </row>
     <row r="289">
@@ -15367,8 +15417,8 @@
       <c r="B289" t="n">
         <v>-0.53</v>
       </c>
-      <c r="L289" t="n">
-        <v>2956</v>
+      <c r="M289" t="n">
+        <v/>
       </c>
     </row>
     <row r="290">
@@ -15378,8 +15428,8 @@
       <c r="B290" t="n">
         <v>-0.45</v>
       </c>
-      <c r="L290" t="n">
-        <v>2968</v>
+      <c r="M290" t="n">
+        <v/>
       </c>
     </row>
     <row r="291">
@@ -15389,8 +15439,8 @@
       <c r="B291" t="n">
         <v>-0.24</v>
       </c>
-      <c r="L291" t="n">
-        <v>2979</v>
+      <c r="M291" t="n">
+        <v/>
       </c>
     </row>
     <row r="292">
@@ -15400,8 +15450,8 @@
       <c r="B292" t="n">
         <v>-0.1</v>
       </c>
-      <c r="L292" t="n">
-        <v>2989</v>
+      <c r="M292" t="n">
+        <v/>
       </c>
     </row>
     <row r="293">
@@ -15411,8 +15461,8 @@
       <c r="B293" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L293" t="n">
-        <v>2999</v>
+      <c r="M293" t="n">
+        <v/>
       </c>
     </row>
     <row r="294">
@@ -15422,8 +15472,8 @@
       <c r="B294" t="n">
         <v>0.025</v>
       </c>
-      <c r="L294" t="n">
-        <v>3010</v>
+      <c r="M294" t="n">
+        <v/>
       </c>
     </row>
     <row r="295">
@@ -15433,8 +15483,8 @@
       <c r="B295" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L295" t="n">
-        <v>3021</v>
+      <c r="M295" t="n">
+        <v/>
       </c>
     </row>
     <row r="296">
@@ -15444,8 +15494,8 @@
       <c r="B296" t="n">
         <v>0.2</v>
       </c>
-      <c r="L296" t="n">
-        <v>3031</v>
+      <c r="M296" t="n">
+        <v/>
       </c>
     </row>
     <row r="297">
@@ -15455,8 +15505,8 @@
       <c r="B297" t="n">
         <v>-0.015</v>
       </c>
-      <c r="L297" t="n">
-        <v>3040</v>
+      <c r="M297" t="n">
+        <v/>
       </c>
     </row>
     <row r="298">
@@ -15466,8 +15516,8 @@
       <c r="B298" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L298" t="n">
-        <v>3047</v>
+      <c r="M298" t="n">
+        <v/>
       </c>
     </row>
     <row r="299">
@@ -15477,8 +15527,8 @@
       <c r="B299" t="n">
         <v>-0.015</v>
       </c>
-      <c r="L299" t="n">
-        <v>3055</v>
+      <c r="M299" t="n">
+        <v/>
       </c>
     </row>
     <row r="300">
@@ -15488,8 +15538,8 @@
       <c r="B300" t="n">
         <v>-0.275</v>
       </c>
-      <c r="L300" t="n">
-        <v>3065</v>
+      <c r="M300" t="n">
+        <v/>
       </c>
     </row>
     <row r="301">
@@ -15499,8 +15549,8 @@
       <c r="B301" t="n">
         <v>-0.355</v>
       </c>
-      <c r="L301" t="n">
-        <v>3077</v>
+      <c r="M301" t="n">
+        <v/>
       </c>
     </row>
     <row r="302">
@@ -15510,8 +15560,8 @@
       <c r="B302" t="n">
         <v>-0.155</v>
       </c>
-      <c r="L302" t="n">
-        <v>3090</v>
+      <c r="M302" t="n">
+        <v/>
       </c>
     </row>
     <row r="303">
@@ -15521,8 +15571,8 @@
       <c r="B303" t="n">
         <v>0.01</v>
       </c>
-      <c r="L303" t="n">
-        <v>3103</v>
+      <c r="M303" t="n">
+        <v/>
       </c>
     </row>
     <row r="304">
@@ -15532,8 +15582,8 @@
       <c r="B304" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L304" t="n">
-        <v>3124</v>
+      <c r="M304" t="n">
+        <v/>
       </c>
     </row>
     <row r="305">
@@ -15543,8 +15593,8 @@
       <c r="B305" t="n">
         <v>-0.36</v>
       </c>
-      <c r="L305" t="n">
-        <v>3134</v>
+      <c r="M305" t="n">
+        <v/>
       </c>
     </row>
     <row r="306">
@@ -15554,8 +15604,8 @@
       <c r="B306" t="n">
         <v>-0.44</v>
       </c>
-      <c r="L306" t="n">
-        <v>3145</v>
+      <c r="M306" t="n">
+        <v/>
       </c>
     </row>
     <row r="307">
@@ -15565,8 +15615,8 @@
       <c r="B307" t="n">
         <v>-0.35</v>
       </c>
-      <c r="L307" t="n">
-        <v>3156</v>
+      <c r="M307" t="n">
+        <v/>
       </c>
     </row>
     <row r="308">
@@ -15576,8 +15626,8 @@
       <c r="B308" t="n">
         <v>-0.315</v>
       </c>
-      <c r="L308" t="n">
-        <v>3167</v>
+      <c r="M308" t="n">
+        <v/>
       </c>
     </row>
     <row r="309">
@@ -15587,8 +15637,8 @@
       <c r="B309" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L309" t="n">
-        <v>3177</v>
+      <c r="M309" t="n">
+        <v/>
       </c>
     </row>
     <row r="310">
@@ -15598,8 +15648,8 @@
       <c r="B310" t="n">
         <v>-0.39</v>
       </c>
-      <c r="L310" t="n">
-        <v>3188</v>
+      <c r="M310" t="n">
+        <v/>
       </c>
     </row>
     <row r="311">
@@ -15609,8 +15659,8 @@
       <c r="B311" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L311" t="n">
-        <v>3199</v>
+      <c r="M311" t="n">
+        <v/>
       </c>
     </row>
     <row r="312">
@@ -15620,8 +15670,8 @@
       <c r="B312" t="n">
         <v>-0.05</v>
       </c>
-      <c r="L312" t="n">
-        <v>3212</v>
+      <c r="M312" t="n">
+        <v/>
       </c>
     </row>
     <row r="313">
@@ -15631,8 +15681,8 @@
       <c r="B313" t="n">
         <v>-0.135</v>
       </c>
-      <c r="L313" t="n">
-        <v>3224</v>
+      <c r="M313" t="n">
+        <v/>
       </c>
     </row>
     <row r="314">
@@ -15642,8 +15692,8 @@
       <c r="B314" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L314" t="n">
-        <v>3234</v>
+      <c r="M314" t="n">
+        <v/>
       </c>
     </row>
     <row r="315">
@@ -15653,8 +15703,8 @@
       <c r="B315" t="n">
         <v>0.09</v>
       </c>
-      <c r="L315" t="n">
-        <v>3241</v>
+      <c r="M315" t="n">
+        <v/>
       </c>
     </row>
     <row r="316">
@@ -15664,8 +15714,8 @@
       <c r="B316" t="n">
         <v>0.08</v>
       </c>
-      <c r="L316" t="n">
-        <v>3247</v>
+      <c r="M316" t="n">
+        <v/>
       </c>
     </row>
     <row r="317">
@@ -15675,8 +15725,8 @@
       <c r="B317" t="n">
         <v>0.13</v>
       </c>
-      <c r="L317" t="n">
-        <v>3252</v>
+      <c r="M317" t="n">
+        <v/>
       </c>
     </row>
     <row r="318">
@@ -15686,8 +15736,8 @@
       <c r="B318" t="n">
         <v>0.14</v>
       </c>
-      <c r="L318" t="n">
-        <v>3258</v>
+      <c r="M318" t="n">
+        <v/>
       </c>
     </row>
     <row r="319">
@@ -15697,8 +15747,8 @@
       <c r="B319" t="n">
         <v>0.055</v>
       </c>
-      <c r="L319" t="n">
-        <v>3262</v>
+      <c r="M319" t="n">
+        <v/>
       </c>
     </row>
     <row r="320">
@@ -15708,8 +15758,8 @@
       <c r="B320" t="n">
         <v>0.11</v>
       </c>
-      <c r="L320" t="n">
-        <v>3269</v>
+      <c r="M320" t="n">
+        <v/>
       </c>
     </row>
     <row r="321">
@@ -15719,8 +15769,8 @@
       <c r="B321" t="n">
         <v>0.165</v>
       </c>
-      <c r="L321" t="n">
-        <v>3278</v>
+      <c r="M321" t="n">
+        <v/>
       </c>
     </row>
     <row r="322">
@@ -15730,8 +15780,8 @@
       <c r="B322" t="n">
         <v>-0.245</v>
       </c>
-      <c r="L322" t="n">
-        <v>3290</v>
+      <c r="M322" t="n">
+        <v/>
       </c>
     </row>
     <row r="323">
@@ -15741,8 +15791,8 @@
       <c r="B323" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L323" t="n">
-        <v>3307</v>
+      <c r="M323" t="n">
+        <v/>
       </c>
     </row>
     <row r="324">
@@ -15752,8 +15802,8 @@
       <c r="B324" t="n">
         <v>-0.295</v>
       </c>
-      <c r="L324" t="n">
-        <v>3328</v>
+      <c r="M324" t="n">
+        <v/>
       </c>
     </row>
     <row r="325">
@@ -15763,8 +15813,8 @@
       <c r="B325" t="n">
         <v>-0.44</v>
       </c>
-      <c r="L325" t="n">
-        <v>3344</v>
+      <c r="M325" t="n">
+        <v/>
       </c>
     </row>
     <row r="326">
@@ -15774,8 +15824,8 @@
       <c r="B326" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L326" t="n">
-        <v>3353</v>
+      <c r="M326" t="n">
+        <v/>
       </c>
     </row>
     <row r="327">
@@ -15785,8 +15835,8 @@
       <c r="B327" t="n">
         <v>-0.38</v>
       </c>
-      <c r="L327" t="n">
-        <v>3361</v>
+      <c r="M327" t="n">
+        <v/>
       </c>
     </row>
     <row r="328">
@@ -15796,8 +15846,8 @@
       <c r="B328" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L328" t="n">
-        <v>3367</v>
+      <c r="M328" t="n">
+        <v/>
       </c>
     </row>
     <row r="329">
@@ -15807,8 +15857,8 @@
       <c r="B329" t="n">
         <v>-0.385</v>
       </c>
-      <c r="L329" t="n">
-        <v>3373</v>
+      <c r="M329" t="n">
+        <v/>
       </c>
     </row>
     <row r="330">
@@ -15818,8 +15868,8 @@
       <c r="B330" t="n">
         <v>-0.215</v>
       </c>
-      <c r="L330" t="n">
-        <v>3380</v>
+      <c r="M330" t="n">
+        <v/>
       </c>
     </row>
     <row r="331">
@@ -15829,8 +15879,8 @@
       <c r="B331" t="n">
         <v>-0.205</v>
       </c>
-      <c r="L331" t="n">
-        <v>3388</v>
+      <c r="M331" t="n">
+        <v/>
       </c>
     </row>
     <row r="332">
@@ -15840,8 +15890,8 @@
       <c r="B332" t="n">
         <v>0.26</v>
       </c>
-      <c r="L332" t="n">
-        <v>3399</v>
+      <c r="M332" t="n">
+        <v/>
       </c>
     </row>
     <row r="333">
@@ -15851,8 +15901,8 @@
       <c r="B333" t="n">
         <v>0.22</v>
       </c>
-      <c r="L333" t="n">
-        <v>3415</v>
+      <c r="M333" t="n">
+        <v/>
       </c>
     </row>
     <row r="334">
@@ -15862,8 +15912,8 @@
       <c r="B334" t="n">
         <v>0.1</v>
       </c>
-      <c r="L334" t="n">
-        <v>3437</v>
+      <c r="M334" t="n">
+        <v/>
       </c>
     </row>
     <row r="335">
@@ -15873,8 +15923,8 @@
       <c r="B335" t="n">
         <v>0.15</v>
       </c>
-      <c r="L335" t="n">
-        <v>3463</v>
+      <c r="M335" t="n">
+        <v/>
       </c>
     </row>
     <row r="336">
@@ -15884,8 +15934,8 @@
       <c r="B336" t="n">
         <v>-0.15</v>
       </c>
-      <c r="L336" t="n">
-        <v>3478</v>
+      <c r="M336" t="n">
+        <v/>
       </c>
     </row>
     <row r="337">
@@ -15895,8 +15945,8 @@
       <c r="B337" t="n">
         <v>-0.42</v>
       </c>
-      <c r="L337" t="n">
-        <v>3485</v>
+      <c r="M337" t="n">
+        <v/>
       </c>
     </row>
     <row r="338">
@@ -15906,8 +15956,8 @@
       <c r="B338" t="n">
         <v>-0.475</v>
       </c>
-      <c r="L338" t="n">
-        <v>3489</v>
+      <c r="M338" t="n">
+        <v/>
       </c>
     </row>
     <row r="339">
@@ -15917,8 +15967,8 @@
       <c r="B339" t="n">
         <v>-0.545</v>
       </c>
-      <c r="L339" t="n">
-        <v>3493</v>
+      <c r="M339" t="n">
+        <v/>
       </c>
     </row>
     <row r="340">
@@ -15928,8 +15978,8 @@
       <c r="B340" t="n">
         <v>-0.65</v>
       </c>
-      <c r="L340" t="n">
-        <v>3497</v>
+      <c r="M340" t="n">
+        <v/>
       </c>
     </row>
     <row r="341">
@@ -15939,8 +15989,8 @@
       <c r="B341" t="n">
         <v>-0.59</v>
       </c>
-      <c r="L341" t="n">
-        <v>3501</v>
+      <c r="M341" t="n">
+        <v/>
       </c>
     </row>
     <row r="342">
@@ -15950,8 +16000,8 @@
       <c r="B342" t="n">
         <v>-0.24</v>
       </c>
-      <c r="L342" t="n">
-        <v>3506</v>
+      <c r="M342" t="n">
+        <v/>
       </c>
     </row>
     <row r="343">
@@ -15961,8 +16011,8 @@
       <c r="B343" t="n">
         <v>-0.465</v>
       </c>
-      <c r="L343" t="n">
-        <v>3513</v>
+      <c r="M343" t="n">
+        <v/>
       </c>
     </row>
     <row r="344">
@@ -15972,8 +16022,8 @@
       <c r="B344" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L344" t="n">
-        <v>3527</v>
+      <c r="M344" t="n">
+        <v/>
       </c>
     </row>
     <row r="345">
@@ -15983,8 +16033,8 @@
       <c r="B345" t="n">
         <v>-0.17</v>
       </c>
-      <c r="L345" t="n">
-        <v>3545</v>
+      <c r="M345" t="n">
+        <v/>
       </c>
     </row>
     <row r="346">
@@ -15994,8 +16044,8 @@
       <c r="B346" t="n">
         <v>-0.225</v>
       </c>
-      <c r="L346" t="n">
-        <v>3560</v>
+      <c r="M346" t="n">
+        <v/>
       </c>
     </row>
     <row r="347">
@@ -16005,8 +16055,8 @@
       <c r="B347" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L347" t="n">
-        <v>3571</v>
+      <c r="M347" t="n">
+        <v/>
       </c>
     </row>
     <row r="348">
@@ -16016,8 +16066,8 @@
       <c r="B348" t="n">
         <v>-0.13</v>
       </c>
-      <c r="L348" t="n">
-        <v>3578</v>
+      <c r="M348" t="n">
+        <v/>
       </c>
     </row>
     <row r="349">
@@ -16027,8 +16077,8 @@
       <c r="B349" t="n">
         <v>0.03</v>
       </c>
-      <c r="L349" t="n">
-        <v>3586</v>
+      <c r="M349" t="n">
+        <v/>
       </c>
     </row>
     <row r="350">
@@ -16038,8 +16088,8 @@
       <c r="B350" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L350" t="n">
-        <v>3593</v>
+      <c r="M350" t="n">
+        <v/>
       </c>
     </row>
     <row r="351">
@@ -16049,8 +16099,8 @@
       <c r="B351" t="n">
         <v>-0.095</v>
       </c>
-      <c r="L351" t="n">
-        <v>3601</v>
+      <c r="M351" t="n">
+        <v/>
       </c>
     </row>
     <row r="352">
@@ -16060,8 +16110,8 @@
       <c r="B352" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="L352" t="n">
-        <v>3611</v>
+      <c r="M352" t="n">
+        <v/>
       </c>
     </row>
     <row r="353">
@@ -16071,8 +16121,8 @@
       <c r="B353" t="n">
         <v>-0.235</v>
       </c>
-      <c r="L353" t="n">
-        <v>3622</v>
+      <c r="M353" t="n">
+        <v/>
       </c>
     </row>
     <row r="354">
@@ -16082,8 +16132,8 @@
       <c r="B354" t="n">
         <v>-0.26</v>
       </c>
-      <c r="L354" t="n">
-        <v>3635</v>
+      <c r="M354" t="n">
+        <v/>
       </c>
     </row>
     <row r="355">
@@ -16093,8 +16143,8 @@
       <c r="B355" t="n">
         <v>-0.45</v>
       </c>
-      <c r="L355" t="n">
-        <v>3651</v>
+      <c r="M355" t="n">
+        <v/>
       </c>
     </row>
     <row r="356">
@@ -16104,8 +16154,8 @@
       <c r="B356" t="n">
         <v>-0.425</v>
       </c>
-      <c r="L356" t="n">
-        <v>3652</v>
+      <c r="M356" t="n">
+        <v/>
       </c>
     </row>
     <row r="357">
@@ -16115,8 +16165,8 @@
       <c r="B357" t="n">
         <v>-0.4</v>
       </c>
-      <c r="L357" t="n">
-        <v>3674</v>
+      <c r="M357" t="n">
+        <v/>
       </c>
     </row>
     <row r="358">
@@ -16126,8 +16176,8 @@
       <c r="B358" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L358" t="n">
-        <v>3685</v>
+      <c r="M358" t="n">
+        <v/>
       </c>
     </row>
     <row r="359">
@@ -16137,8 +16187,8 @@
       <c r="B359" t="n">
         <v>0.09</v>
       </c>
-      <c r="L359" t="n">
-        <v>3696</v>
+      <c r="M359" t="n">
+        <v/>
       </c>
     </row>
     <row r="360">
@@ -16148,8 +16198,8 @@
       <c r="B360" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L360" t="n">
-        <v>3708</v>
+      <c r="M360" t="n">
+        <v/>
       </c>
     </row>
     <row r="361">
@@ -16159,8 +16209,8 @@
       <c r="B361" t="n">
         <v>0.06</v>
       </c>
-      <c r="L361" t="n">
-        <v>3720</v>
+      <c r="M361" t="n">
+        <v/>
       </c>
     </row>
     <row r="362">
@@ -16170,8 +16220,8 @@
       <c r="B362" t="n">
         <v>0.08</v>
       </c>
-      <c r="L362" t="n">
-        <v>3729</v>
+      <c r="M362" t="n">
+        <v/>
       </c>
     </row>
     <row r="363">
@@ -16181,8 +16231,8 @@
       <c r="B363" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L363" t="n">
-        <v>3738</v>
+      <c r="M363" t="n">
+        <v/>
       </c>
     </row>
     <row r="364">
@@ -16192,8 +16242,8 @@
       <c r="B364" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L364" t="n">
-        <v>3747</v>
+      <c r="M364" t="n">
+        <v/>
       </c>
     </row>
     <row r="365">
@@ -16203,8 +16253,8 @@
       <c r="B365" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="L365" t="n">
-        <v>3754</v>
+      <c r="M365" t="n">
+        <v/>
       </c>
     </row>
     <row r="366">
@@ -16214,8 +16264,8 @@
       <c r="B366" t="n">
         <v>-0.16</v>
       </c>
-      <c r="L366" t="n">
-        <v>3761</v>
+      <c r="M366" t="n">
+        <v/>
       </c>
     </row>
     <row r="367">
@@ -16225,8 +16275,8 @@
       <c r="B367" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L367" t="n">
-        <v>3767</v>
+      <c r="M367" t="n">
+        <v/>
       </c>
     </row>
     <row r="368">
@@ -16236,8 +16286,8 @@
       <c r="B368" t="n">
         <v>-0.46</v>
       </c>
-      <c r="L368" t="n">
-        <v>3773</v>
+      <c r="M368" t="n">
+        <v/>
       </c>
     </row>
     <row r="369">
@@ -16247,8 +16297,8 @@
       <c r="B369" t="n">
         <v>-0.49</v>
       </c>
-      <c r="L369" t="n">
-        <v>3780</v>
+      <c r="M369" t="n">
+        <v/>
       </c>
     </row>
     <row r="370">
@@ -16258,8 +16308,8 @@
       <c r="B370" t="n">
         <v>-0.49</v>
       </c>
-      <c r="L370" t="n">
-        <v>3789</v>
+      <c r="M370" t="n">
+        <v/>
       </c>
     </row>
     <row r="371">
@@ -16269,8 +16319,8 @@
       <c r="B371" t="n">
         <v>-0.48</v>
       </c>
-      <c r="L371" t="n">
-        <v>3804</v>
+      <c r="M371" t="n">
+        <v/>
       </c>
     </row>
     <row r="372">
@@ -16280,8 +16330,8 @@
       <c r="B372" t="n">
         <v>-0.4</v>
       </c>
-      <c r="L372" t="n">
-        <v>3822</v>
+      <c r="M372" t="n">
+        <v/>
       </c>
     </row>
     <row r="373">
@@ -16291,8 +16341,8 @@
       <c r="B373" t="n">
         <v>-0.22</v>
       </c>
-      <c r="L373" t="n">
-        <v>3836</v>
+      <c r="M373" t="n">
+        <v/>
       </c>
     </row>
     <row r="374">
@@ -16302,8 +16352,8 @@
       <c r="B374" t="n">
         <v>0.16</v>
       </c>
-      <c r="L374" t="n">
-        <v>3846</v>
+      <c r="M374" t="n">
+        <v/>
       </c>
     </row>
     <row r="375">
@@ -16313,8 +16363,8 @@
       <c r="B375" t="n">
         <v>0.15</v>
       </c>
-      <c r="L375" t="n">
-        <v>3856</v>
+      <c r="M375" t="n">
+        <v/>
       </c>
     </row>
     <row r="376">
@@ -16324,8 +16374,8 @@
       <c r="B376" t="n">
         <v>0.25</v>
       </c>
-      <c r="L376" t="n">
-        <v>3865</v>
+      <c r="M376" t="n">
+        <v/>
       </c>
     </row>
     <row r="377">
@@ -16335,8 +16385,8 @@
       <c r="B377" t="n">
         <v>0.04</v>
       </c>
-      <c r="L377" t="n">
-        <v>3874</v>
+      <c r="M377" t="n">
+        <v/>
       </c>
     </row>
     <row r="378">
@@ -16346,8 +16396,8 @@
       <c r="B378" t="n">
         <v>0.03</v>
       </c>
-      <c r="L378" t="n">
-        <v>3882</v>
+      <c r="M378" t="n">
+        <v/>
       </c>
     </row>
     <row r="379">
@@ -16357,8 +16407,8 @@
       <c r="B379" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L379" t="n">
-        <v>3890</v>
+      <c r="M379" t="n">
+        <v/>
       </c>
     </row>
     <row r="380">
@@ -16368,8 +16418,8 @@
       <c r="B380" t="n">
         <v>-0.17</v>
       </c>
-      <c r="L380" t="n">
-        <v>3898</v>
+      <c r="M380" t="n">
+        <v/>
       </c>
     </row>
     <row r="381">
@@ -16379,8 +16429,8 @@
       <c r="B381" t="n">
         <v>-0.28</v>
       </c>
-      <c r="L381" t="n">
-        <v>3908</v>
+      <c r="M381" t="n">
+        <v/>
       </c>
     </row>
     <row r="382">
@@ -16390,8 +16440,8 @@
       <c r="B382" t="n">
         <v>-0.38</v>
       </c>
-      <c r="L382" t="n">
-        <v>3915</v>
+      <c r="M382" t="n">
+        <v/>
       </c>
     </row>
     <row r="383">
@@ -16401,8 +16451,8 @@
       <c r="B383" t="n">
         <v>-0.34</v>
       </c>
-      <c r="L383" t="n">
-        <v>3918</v>
+      <c r="M383" t="n">
+        <v/>
       </c>
     </row>
     <row r="384">
@@ -16412,8 +16462,8 @@
       <c r="B384" t="n">
         <v>-0.29</v>
       </c>
-      <c r="L384" t="n">
-        <v>3922</v>
+      <c r="M384" t="n">
+        <v/>
       </c>
     </row>
     <row r="385">
@@ -16423,8 +16473,8 @@
       <c r="B385" t="n">
         <v>-0.21</v>
       </c>
-      <c r="L385" t="n">
-        <v>3928</v>
+      <c r="M385" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -16438,7 +16488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -16447,8 +16497,9 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="187" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="183" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16484,10 +16535,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -16519,9 +16575,10 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
-          <t>&lt;BR&gt;Serie &lt;i&gt;&lt;b&gt;Id-34AE56JH&lt;/i&gt;&lt;/b&gt; sampled every 50.0 and linear interpolation with integration at True with SAMPLE &lt;i&gt;&lt;b&gt;Id-4EA5A3B8&lt;/i&gt;&lt;/b&gt;&lt;BR&gt;---&gt; serie &lt;i&gt;&lt;b&gt;Id-E0961C19&lt;/b&gt;&lt;/i&gt;</t>
+          <t>Serie &lt;i&gt;&lt;b&gt;Id-34AE56JH&lt;/i&gt;&lt;/b&gt; sampled every 50.0 and linear interpolation with integration at True with SAMPLE &lt;i&gt;&lt;b&gt;Id-4EA5A3B8&lt;/i&gt;&lt;/b&gt;&lt;BR&gt;---&gt; serie &lt;i&gt;&lt;b&gt;Id-E0961C19&lt;/b&gt;&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:I385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17145,8 +17202,9 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17182,10 +17240,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -17218,6 +17281,7 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -20294,7 +20358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1002"/>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20303,8 +20367,9 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20340,10 +20405,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -20371,9 +20441,10 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
-          <t>&lt;BR&gt;Astronomical serie "Obliquity"</t>
+          <t>Astronomical serie "Obliquity"</t>
         </is>
       </c>
     </row>
@@ -28388,7 +28459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28397,8 +28468,9 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28434,10 +28506,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -28465,7 +28542,8 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Imported serie</t>
         </is>
@@ -28594,7 +28672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:I385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28603,8 +28681,9 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28640,10 +28719,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>History</t>
         </is>
@@ -28672,6 +28756,7 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">

--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -434,7 +434,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.43</t>
+          <t>Created with PyAnalyseries v5.44</t>
         </is>
       </c>
     </row>
@@ -457,7 +457,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2025/12/19 at 19:25:23</t>
+          <t>Saved 2026/01/05 at 12:17:56</t>
         </is>
       </c>
     </row>
@@ -45622,7 +45622,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -45687,7 +45687,11 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>a comment, to be completed</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">

--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -15,11 +15,13 @@
     <sheet name="Series Id-67GH89BG" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Series Id-000476B5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Series Id-A9AA9941" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Series Id-56TY87JG" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SAMPLE Id-4EA5A3B8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Series Id-B54E03C0" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="INTERPOLATION Id-20A10A97" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Series Id-AE86905A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Series Id-D81474CD" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Series Id-56TY87JG" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SAMPLE Id-4EA5A3B8" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Series Id-B54E03C0" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="INTERPOLATION Id-20A10A97" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Series Id-AE86905A" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="FILTER Id-C0561A76" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +436,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.44</t>
+          <t>Created with PyAnalyseries v6.06</t>
         </is>
       </c>
     </row>
@@ -457,7 +459,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2026/01/05 at 12:17:56</t>
+          <t>Saved 2026/03/02 at 17:58:49</t>
         </is>
       </c>
     </row>
@@ -467,6 +469,3162 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H385"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>18MD00-2374vsPDB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3.235</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#962cff</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>a comment, to be completed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>160</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>180</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>190</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>210</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>220</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>230</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>240</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>250</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>260</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>270</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>280</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>290</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>300</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>310</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>320</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>330</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>340</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>350</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>360</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>370</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>380</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>390</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>400</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>410</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>420</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>430</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>440</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>450</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>460</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>470</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>480</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>490</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>500</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>510</v>
+      </c>
+      <c r="B46" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>520</v>
+      </c>
+      <c r="B47" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>530</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>540</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>560</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>570</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>580</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>590</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>600</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>610</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>620</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>630</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>640</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>650</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>660</v>
+      </c>
+      <c r="B60" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>670</v>
+      </c>
+      <c r="B61" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>680</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>690</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>700</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>710</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>720</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>730</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>740</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>750</v>
+      </c>
+      <c r="B69" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>760</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>770</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>780</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>790</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>800</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>810</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>820</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>830</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>840</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3.395</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>850</v>
+      </c>
+      <c r="B79" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>860</v>
+      </c>
+      <c r="B80" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>870</v>
+      </c>
+      <c r="B81" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>880</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>890</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>900</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>910</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>920</v>
+      </c>
+      <c r="B86" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>930</v>
+      </c>
+      <c r="B87" t="n">
+        <v>3.835</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>940</v>
+      </c>
+      <c r="B88" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>950</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>960</v>
+      </c>
+      <c r="B90" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>970</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>980</v>
+      </c>
+      <c r="B92" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>990</v>
+      </c>
+      <c r="B93" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B96" t="n">
+        <v>3.365</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B99" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B101" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B102" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B103" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B104" t="n">
+        <v>3.5833</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B105" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B106" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B107" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B108" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B109" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B110" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B111" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B112" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B113" t="n">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B114" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B116" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B117" t="n">
+        <v>3.5333</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B118" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B119" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B120" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B121" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B122" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B123" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1317</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1367</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3.385</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3.345</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B148" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B149" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B151" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B153" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B154" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B155" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B156" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1565</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B162" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B163" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B164" t="n">
+        <v>3.1175</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B165" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B169" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B171" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B174" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B176" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>1665</v>
+      </c>
+      <c r="B177" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B179" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>1677</v>
+      </c>
+      <c r="B180" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B181" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B182" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B183" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>1761</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>1773</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B193" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1781</v>
+      </c>
+      <c r="B194" t="n">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>1785</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>1789</v>
+      </c>
+      <c r="B196" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>1793</v>
+      </c>
+      <c r="B197" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>1797</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B199" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B200" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B201" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B203" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2.705</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B209" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1888</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1892</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1896</v>
+      </c>
+      <c r="B212" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B214" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>1912</v>
+      </c>
+      <c r="B216" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B217" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B218" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B220" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B221" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B222" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B223" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B224" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B225" t="n">
+        <v>4.0733</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B229" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B230" t="n">
+        <v>3.9966</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B231" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B232" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2058</v>
+      </c>
+      <c r="B233" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2068</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2078</v>
+      </c>
+      <c r="B235" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2088</v>
+      </c>
+      <c r="B236" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2098</v>
+      </c>
+      <c r="B237" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2108</v>
+      </c>
+      <c r="B238" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2118</v>
+      </c>
+      <c r="B239" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2128</v>
+      </c>
+      <c r="B240" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2138</v>
+      </c>
+      <c r="B241" t="n">
+        <v>3.625</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2148</v>
+      </c>
+      <c r="B242" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2158</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2168</v>
+      </c>
+      <c r="B244" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2178</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2188</v>
+      </c>
+      <c r="B246" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2198</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2208</v>
+      </c>
+      <c r="B248" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2218</v>
+      </c>
+      <c r="B249" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2228</v>
+      </c>
+      <c r="B250" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2238</v>
+      </c>
+      <c r="B251" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2248</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2258</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2268</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2278</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2288</v>
+      </c>
+      <c r="B256" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2298</v>
+      </c>
+      <c r="B257" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2308</v>
+      </c>
+      <c r="B258" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2318</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2328</v>
+      </c>
+      <c r="B260" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2338</v>
+      </c>
+      <c r="B261" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2348</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2358</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2368</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2374</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2384</v>
+      </c>
+      <c r="B266" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2394</v>
+      </c>
+      <c r="B267" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2404</v>
+      </c>
+      <c r="B268" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2414</v>
+      </c>
+      <c r="B269" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2424</v>
+      </c>
+      <c r="B270" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2434</v>
+      </c>
+      <c r="B271" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2444</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2454</v>
+      </c>
+      <c r="B273" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2464</v>
+      </c>
+      <c r="B274" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2474</v>
+      </c>
+      <c r="B275" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2484</v>
+      </c>
+      <c r="B276" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>2494</v>
+      </c>
+      <c r="B277" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>2504</v>
+      </c>
+      <c r="B278" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>2514</v>
+      </c>
+      <c r="B279" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2524</v>
+      </c>
+      <c r="B280" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2534</v>
+      </c>
+      <c r="B281" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2544</v>
+      </c>
+      <c r="B282" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>2554</v>
+      </c>
+      <c r="B283" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2564</v>
+      </c>
+      <c r="B284" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>2574</v>
+      </c>
+      <c r="B285" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>2584</v>
+      </c>
+      <c r="B286" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>2594</v>
+      </c>
+      <c r="B287" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2604</v>
+      </c>
+      <c r="B288" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>2614</v>
+      </c>
+      <c r="B289" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>2624</v>
+      </c>
+      <c r="B290" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2634</v>
+      </c>
+      <c r="B291" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2644</v>
+      </c>
+      <c r="B292" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2654</v>
+      </c>
+      <c r="B293" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2664</v>
+      </c>
+      <c r="B294" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2674</v>
+      </c>
+      <c r="B295" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2684</v>
+      </c>
+      <c r="B296" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2694</v>
+      </c>
+      <c r="B297" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2704</v>
+      </c>
+      <c r="B298" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2714</v>
+      </c>
+      <c r="B299" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>2724</v>
+      </c>
+      <c r="B300" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>2734</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>2735</v>
+      </c>
+      <c r="B302" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>2744</v>
+      </c>
+      <c r="B303" t="n">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>2754</v>
+      </c>
+      <c r="B304" t="n">
+        <v>2.995</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>2764</v>
+      </c>
+      <c r="B305" t="n">
+        <v>3.455</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>2774</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>2775</v>
+      </c>
+      <c r="B307" t="n">
+        <v>3.3466</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>2784</v>
+      </c>
+      <c r="B308" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>2794</v>
+      </c>
+      <c r="B309" t="n">
+        <v>3.045</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>2804</v>
+      </c>
+      <c r="B310" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>2814</v>
+      </c>
+      <c r="B311" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>2824</v>
+      </c>
+      <c r="B312" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>2834</v>
+      </c>
+      <c r="B313" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>2844</v>
+      </c>
+      <c r="B314" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>2854</v>
+      </c>
+      <c r="B315" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>2864</v>
+      </c>
+      <c r="B316" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2868</v>
+      </c>
+      <c r="B317" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>2872</v>
+      </c>
+      <c r="B318" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>2876</v>
+      </c>
+      <c r="B319" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>2880</v>
+      </c>
+      <c r="B320" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>2884</v>
+      </c>
+      <c r="B321" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2888</v>
+      </c>
+      <c r="B322" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>2892</v>
+      </c>
+      <c r="B323" t="n">
+        <v>3.185</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2896</v>
+      </c>
+      <c r="B324" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B325" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2904</v>
+      </c>
+      <c r="B326" t="n">
+        <v>2.905</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2908</v>
+      </c>
+      <c r="B327" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2912</v>
+      </c>
+      <c r="B328" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>2916</v>
+      </c>
+      <c r="B329" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2920</v>
+      </c>
+      <c r="B330" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2924</v>
+      </c>
+      <c r="B331" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2928</v>
+      </c>
+      <c r="B332" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2932</v>
+      </c>
+      <c r="B333" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2936</v>
+      </c>
+      <c r="B334" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2940</v>
+      </c>
+      <c r="B335" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>2968</v>
+      </c>
+      <c r="B336" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>2972</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>2976</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>2980</v>
+      </c>
+      <c r="B339" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>2984</v>
+      </c>
+      <c r="B340" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>2988</v>
+      </c>
+      <c r="B341" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>2992</v>
+      </c>
+      <c r="B342" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>2996</v>
+      </c>
+      <c r="B343" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3004</v>
+      </c>
+      <c r="B345" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3008</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3012</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3020</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3024</v>
+      </c>
+      <c r="B349" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3068</v>
+      </c>
+      <c r="B350" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3072</v>
+      </c>
+      <c r="B351" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3076</v>
+      </c>
+      <c r="B352" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>3080</v>
+      </c>
+      <c r="B353" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>3084</v>
+      </c>
+      <c r="B354" t="n">
+        <v>3.215</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>3088</v>
+      </c>
+      <c r="B355" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>3092</v>
+      </c>
+      <c r="B356" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>3096</v>
+      </c>
+      <c r="B357" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B358" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>3104</v>
+      </c>
+      <c r="B359" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>3114</v>
+      </c>
+      <c r="B360" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3124</v>
+      </c>
+      <c r="B361" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B362" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3144</v>
+      </c>
+      <c r="B363" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>3154</v>
+      </c>
+      <c r="B364" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>3164</v>
+      </c>
+      <c r="B365" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B366" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>3184</v>
+      </c>
+      <c r="B367" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>3194</v>
+      </c>
+      <c r="B368" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B369" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B370" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B371" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B372" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>3220</v>
+      </c>
+      <c r="B373" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>3224</v>
+      </c>
+      <c r="B374" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>3228</v>
+      </c>
+      <c r="B375" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>3232</v>
+      </c>
+      <c r="B376" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>3236</v>
+      </c>
+      <c r="B377" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>3240</v>
+      </c>
+      <c r="B378" t="n">
+        <v>3.065</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>3244</v>
+      </c>
+      <c r="B379" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>3248</v>
+      </c>
+      <c r="B380" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>3252</v>
+      </c>
+      <c r="B381" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>3256</v>
+      </c>
+      <c r="B382" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>3284</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>3288</v>
+      </c>
+      <c r="B384" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>3292</v>
+      </c>
+      <c r="B385" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -544,7 +3702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -732,7 +3890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -840,7 +3998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17845,6 +21003,88 @@
       </c>
       <c r="B2116" t="n">
         <v>2.91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="91" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Moving average 3 pts</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Created 2026/02/23 at 18:12:48</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FILTER &lt;i&gt;&lt;b&gt;Id-C0561A76&lt;/i&gt;&lt;/b&gt; with parameters :&lt;ul&gt;&lt;li&gt;Moving average size : 3&lt;/ul&gt;</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -45613,17 +48853,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="176" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45673,33 +48913,37 @@
         <v>100</v>
       </c>
       <c r="B2" t="n">
-        <v>3.235</v>
+        <v/>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Series</t>
+          <t>Series filtered</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#962cff</t>
+          <t>#7f7f7f</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
-          <t>a comment, to be completed</t>
+          <t>Created 2026/02/23 at 18:12:48</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Imported series&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-A9AA9941&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-C0561A76&lt;/i&gt;&lt;/b&gt; with a moving average of size 3&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-D81474CD&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>104</v>
       </c>
       <c r="B3" t="n">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="4">
@@ -45707,7 +48951,7 @@
         <v>108</v>
       </c>
       <c r="B4" t="n">
-        <v>3.535</v>
+        <v>3.543333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -45715,7 +48959,7 @@
         <v>112</v>
       </c>
       <c r="B5" t="n">
-        <v>3.605</v>
+        <v>3.598333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -45723,7 +48967,7 @@
         <v>116</v>
       </c>
       <c r="B6" t="n">
-        <v>3.655</v>
+        <v>3.683333333333334</v>
       </c>
     </row>
     <row r="7">
@@ -45731,7 +48975,7 @@
         <v>120</v>
       </c>
       <c r="B7" t="n">
-        <v>3.79</v>
+        <v>3.558333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -45739,7 +48983,7 @@
         <v>130</v>
       </c>
       <c r="B8" t="n">
-        <v>3.23</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="9">
@@ -45747,7 +48991,7 @@
         <v>140</v>
       </c>
       <c r="B9" t="n">
-        <v>3.99</v>
+        <v>3.700000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -45755,7 +48999,7 @@
         <v>150</v>
       </c>
       <c r="B10" t="n">
-        <v>3.88</v>
+        <v>3.963333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -45763,7 +49007,7 @@
         <v>160</v>
       </c>
       <c r="B11" t="n">
-        <v>3.95</v>
+        <v>3.906666666666666</v>
       </c>
     </row>
     <row r="12">
@@ -45771,7 +49015,7 @@
         <v>160</v>
       </c>
       <c r="B12" t="n">
-        <v>4.09</v>
+        <v>3.906666666666666</v>
       </c>
     </row>
     <row r="13">
@@ -45779,7 +49023,7 @@
         <v>180</v>
       </c>
       <c r="B13" t="n">
-        <v>3.82</v>
+        <v>3.883333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -45787,7 +49031,7 @@
         <v>190</v>
       </c>
       <c r="B14" t="n">
-        <v>3.81</v>
+        <v>3.843333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -45795,7 +49039,7 @@
         <v>200</v>
       </c>
       <c r="B15" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="16">
@@ -45803,2959 +49047,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>220</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>230</v>
-      </c>
-      <c r="B18" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>240</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>250</v>
-      </c>
-      <c r="B20" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>260</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>270</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>280</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>290</v>
-      </c>
-      <c r="B24" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>300</v>
-      </c>
-      <c r="B25" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>310</v>
-      </c>
-      <c r="B26" t="n">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>320</v>
-      </c>
-      <c r="B27" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>330</v>
-      </c>
-      <c r="B28" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>340</v>
-      </c>
-      <c r="B29" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>350</v>
-      </c>
-      <c r="B30" t="n">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>360</v>
-      </c>
-      <c r="B31" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>370</v>
-      </c>
-      <c r="B32" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>380</v>
-      </c>
-      <c r="B33" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>390</v>
-      </c>
-      <c r="B34" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>400</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>410</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>420</v>
-      </c>
-      <c r="B37" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>430</v>
-      </c>
-      <c r="B38" t="n">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>440</v>
-      </c>
-      <c r="B39" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>450</v>
-      </c>
-      <c r="B40" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>460</v>
-      </c>
-      <c r="B41" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>470</v>
-      </c>
-      <c r="B42" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>480</v>
-      </c>
-      <c r="B43" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>490</v>
-      </c>
-      <c r="B44" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>500</v>
-      </c>
-      <c r="B45" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>510</v>
-      </c>
-      <c r="B46" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>520</v>
-      </c>
-      <c r="B47" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>530</v>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>540</v>
-      </c>
-      <c r="B49" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>560</v>
-      </c>
-      <c r="B50" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>570</v>
-      </c>
-      <c r="B51" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>580</v>
-      </c>
-      <c r="B52" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>590</v>
-      </c>
-      <c r="B53" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>600</v>
-      </c>
-      <c r="B54" t="n">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>610</v>
-      </c>
-      <c r="B55" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>620</v>
-      </c>
-      <c r="B56" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>630</v>
-      </c>
-      <c r="B57" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>640</v>
-      </c>
-      <c r="B58" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>650</v>
-      </c>
-      <c r="B59" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>660</v>
-      </c>
-      <c r="B60" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>670</v>
-      </c>
-      <c r="B61" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>680</v>
-      </c>
-      <c r="B62" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>690</v>
-      </c>
-      <c r="B63" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>700</v>
-      </c>
-      <c r="B64" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>710</v>
-      </c>
-      <c r="B65" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>720</v>
-      </c>
-      <c r="B66" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>730</v>
-      </c>
-      <c r="B67" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>740</v>
-      </c>
-      <c r="B68" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>750</v>
-      </c>
-      <c r="B69" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>760</v>
-      </c>
-      <c r="B70" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>770</v>
-      </c>
-      <c r="B71" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>780</v>
-      </c>
-      <c r="B72" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>790</v>
-      </c>
-      <c r="B73" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>800</v>
-      </c>
-      <c r="B74" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>810</v>
-      </c>
-      <c r="B75" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>820</v>
-      </c>
-      <c r="B76" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>830</v>
-      </c>
-      <c r="B77" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>840</v>
-      </c>
-      <c r="B78" t="n">
-        <v>3.395</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>850</v>
-      </c>
-      <c r="B79" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>860</v>
-      </c>
-      <c r="B80" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>870</v>
-      </c>
-      <c r="B81" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>880</v>
-      </c>
-      <c r="B82" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>890</v>
-      </c>
-      <c r="B83" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>900</v>
-      </c>
-      <c r="B84" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>910</v>
-      </c>
-      <c r="B85" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>920</v>
-      </c>
-      <c r="B86" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>930</v>
-      </c>
-      <c r="B87" t="n">
-        <v>3.835</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>940</v>
-      </c>
-      <c r="B88" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>950</v>
-      </c>
-      <c r="B89" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>960</v>
-      </c>
-      <c r="B90" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>970</v>
-      </c>
-      <c r="B91" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>980</v>
-      </c>
-      <c r="B92" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>990</v>
-      </c>
-      <c r="B93" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B94" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>1010</v>
-      </c>
-      <c r="B95" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>1020</v>
-      </c>
-      <c r="B96" t="n">
-        <v>3.365</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>1030</v>
-      </c>
-      <c r="B97" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>1040</v>
-      </c>
-      <c r="B98" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>1050</v>
-      </c>
-      <c r="B99" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>1060</v>
-      </c>
-      <c r="B100" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>1070</v>
-      </c>
-      <c r="B101" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>1080</v>
-      </c>
-      <c r="B102" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>1087</v>
-      </c>
-      <c r="B103" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>1097</v>
-      </c>
-      <c r="B104" t="n">
-        <v>3.5833</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>1107</v>
-      </c>
-      <c r="B105" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>1117</v>
-      </c>
-      <c r="B106" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>1127</v>
-      </c>
-      <c r="B107" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>1137</v>
-      </c>
-      <c r="B108" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>1147</v>
-      </c>
-      <c r="B109" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>1157</v>
-      </c>
-      <c r="B110" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>1167</v>
-      </c>
-      <c r="B111" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>1177</v>
-      </c>
-      <c r="B112" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>1187</v>
-      </c>
-      <c r="B113" t="n">
-        <v>3.355</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>1197</v>
-      </c>
-      <c r="B114" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>1207</v>
-      </c>
-      <c r="B115" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>1217</v>
-      </c>
-      <c r="B116" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>1227</v>
-      </c>
-      <c r="B117" t="n">
-        <v>3.5333</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>1237</v>
-      </c>
-      <c r="B118" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>1247</v>
-      </c>
-      <c r="B119" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>1257</v>
-      </c>
-      <c r="B120" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>1267</v>
-      </c>
-      <c r="B121" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>1277</v>
-      </c>
-      <c r="B122" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>1287</v>
-      </c>
-      <c r="B123" t="n">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>1297</v>
-      </c>
-      <c r="B124" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>1307</v>
-      </c>
-      <c r="B125" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>1317</v>
-      </c>
-      <c r="B126" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>1327</v>
-      </c>
-      <c r="B127" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>1337</v>
-      </c>
-      <c r="B128" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>1347</v>
-      </c>
-      <c r="B129" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>1357</v>
-      </c>
-      <c r="B130" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>1367</v>
-      </c>
-      <c r="B131" t="n">
-        <v>3.385</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B132" t="n">
-        <v>3.345</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>1387</v>
-      </c>
-      <c r="B133" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>1397</v>
-      </c>
-      <c r="B134" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>1407</v>
-      </c>
-      <c r="B135" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>1417</v>
-      </c>
-      <c r="B136" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>1427</v>
-      </c>
-      <c r="B137" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>1437</v>
-      </c>
-      <c r="B138" t="n">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>1447</v>
-      </c>
-      <c r="B139" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>1457</v>
-      </c>
-      <c r="B140" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>1467</v>
-      </c>
-      <c r="B141" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>1477</v>
-      </c>
-      <c r="B142" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>1487</v>
-      </c>
-      <c r="B143" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>1497</v>
-      </c>
-      <c r="B144" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>1507</v>
-      </c>
-      <c r="B145" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>1511</v>
-      </c>
-      <c r="B146" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>1515</v>
-      </c>
-      <c r="B147" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>1519</v>
-      </c>
-      <c r="B148" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>1523</v>
-      </c>
-      <c r="B149" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>1527</v>
-      </c>
-      <c r="B150" t="n">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>1531</v>
-      </c>
-      <c r="B151" t="n">
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>1535</v>
-      </c>
-      <c r="B152" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>1537</v>
-      </c>
-      <c r="B153" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>1541</v>
-      </c>
-      <c r="B154" t="n">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>1545</v>
-      </c>
-      <c r="B155" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>1549</v>
-      </c>
-      <c r="B156" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>1553</v>
-      </c>
-      <c r="B157" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>1557</v>
-      </c>
-      <c r="B158" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>1561</v>
-      </c>
-      <c r="B159" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>1565</v>
-      </c>
-      <c r="B160" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>1569</v>
-      </c>
-      <c r="B161" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>1573</v>
-      </c>
-      <c r="B162" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>1577</v>
-      </c>
-      <c r="B163" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>1581</v>
-      </c>
-      <c r="B164" t="n">
-        <v>3.1175</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>1585</v>
-      </c>
-      <c r="B165" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>1589</v>
-      </c>
-      <c r="B166" t="n">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>1593</v>
-      </c>
-      <c r="B167" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>1597</v>
-      </c>
-      <c r="B168" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>1601</v>
-      </c>
-      <c r="B169" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>1605</v>
-      </c>
-      <c r="B170" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>1609</v>
-      </c>
-      <c r="B171" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>1645</v>
-      </c>
-      <c r="B172" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>1649</v>
-      </c>
-      <c r="B173" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>1653</v>
-      </c>
-      <c r="B174" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>1657</v>
-      </c>
-      <c r="B175" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>1661</v>
-      </c>
-      <c r="B176" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>1665</v>
-      </c>
-      <c r="B177" t="n">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>1669</v>
-      </c>
-      <c r="B178" t="n">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>1673</v>
-      </c>
-      <c r="B179" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>1677</v>
-      </c>
-      <c r="B180" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>1681</v>
-      </c>
-      <c r="B181" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>1685</v>
-      </c>
-      <c r="B182" t="n">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>1689</v>
-      </c>
-      <c r="B183" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>1693</v>
-      </c>
-      <c r="B184" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>1697</v>
-      </c>
-      <c r="B185" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>1701</v>
-      </c>
-      <c r="B186" t="n">
-        <v>2.67</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>1705</v>
-      </c>
-      <c r="B187" t="n">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>1709</v>
-      </c>
-      <c r="B188" t="n">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>1761</v>
-      </c>
-      <c r="B189" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>1765</v>
-      </c>
-      <c r="B190" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>1769</v>
-      </c>
-      <c r="B191" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>1773</v>
-      </c>
-      <c r="B192" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>1777</v>
-      </c>
-      <c r="B193" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>1781</v>
-      </c>
-      <c r="B194" t="n">
-        <v>3.355</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>1785</v>
-      </c>
-      <c r="B195" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>1789</v>
-      </c>
-      <c r="B196" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>1793</v>
-      </c>
-      <c r="B197" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>1797</v>
-      </c>
-      <c r="B198" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>1801</v>
-      </c>
-      <c r="B199" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B200" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>1809</v>
-      </c>
-      <c r="B201" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>1813</v>
-      </c>
-      <c r="B202" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>1817</v>
-      </c>
-      <c r="B203" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>1821</v>
-      </c>
-      <c r="B204" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>1825</v>
-      </c>
-      <c r="B205" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>1829</v>
-      </c>
-      <c r="B206" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>1833</v>
-      </c>
-      <c r="B207" t="n">
-        <v>2.705</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>1837</v>
-      </c>
-      <c r="B208" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>1884</v>
-      </c>
-      <c r="B209" t="n">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>1888</v>
-      </c>
-      <c r="B210" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>1892</v>
-      </c>
-      <c r="B211" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>1896</v>
-      </c>
-      <c r="B212" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>1900</v>
-      </c>
-      <c r="B213" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>1904</v>
-      </c>
-      <c r="B214" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B215" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>1912</v>
-      </c>
-      <c r="B216" t="n">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>1916</v>
-      </c>
-      <c r="B217" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>1920</v>
-      </c>
-      <c r="B218" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B219" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>1928</v>
-      </c>
-      <c r="B220" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B221" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>1948</v>
-      </c>
-      <c r="B222" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B223" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B224" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B225" t="n">
-        <v>4.0733</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B226" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B227" t="n">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B228" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B229" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B230" t="n">
-        <v>3.9966</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B231" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>2048</v>
-      </c>
-      <c r="B232" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>2058</v>
-      </c>
-      <c r="B233" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>2068</v>
-      </c>
-      <c r="B234" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>2078</v>
-      </c>
-      <c r="B235" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>2088</v>
-      </c>
-      <c r="B236" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>2098</v>
-      </c>
-      <c r="B237" t="n">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>2108</v>
-      </c>
-      <c r="B238" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>2118</v>
-      </c>
-      <c r="B239" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>2128</v>
-      </c>
-      <c r="B240" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>2138</v>
-      </c>
-      <c r="B241" t="n">
-        <v>3.625</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>2148</v>
-      </c>
-      <c r="B242" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>2158</v>
-      </c>
-      <c r="B243" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>2168</v>
-      </c>
-      <c r="B244" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>2178</v>
-      </c>
-      <c r="B245" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>2188</v>
-      </c>
-      <c r="B246" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>2198</v>
-      </c>
-      <c r="B247" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>2208</v>
-      </c>
-      <c r="B248" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>2218</v>
-      </c>
-      <c r="B249" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>2228</v>
-      </c>
-      <c r="B250" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>2238</v>
-      </c>
-      <c r="B251" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>2248</v>
-      </c>
-      <c r="B252" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>2258</v>
-      </c>
-      <c r="B253" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>2268</v>
-      </c>
-      <c r="B254" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>2278</v>
-      </c>
-      <c r="B255" t="n">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>2288</v>
-      </c>
-      <c r="B256" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>2298</v>
-      </c>
-      <c r="B257" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>2308</v>
-      </c>
-      <c r="B258" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>2318</v>
-      </c>
-      <c r="B259" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>2328</v>
-      </c>
-      <c r="B260" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>2338</v>
-      </c>
-      <c r="B261" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>2348</v>
-      </c>
-      <c r="B262" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>2358</v>
-      </c>
-      <c r="B263" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>2368</v>
-      </c>
-      <c r="B264" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>2374</v>
-      </c>
-      <c r="B265" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>2384</v>
-      </c>
-      <c r="B266" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>2394</v>
-      </c>
-      <c r="B267" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>2404</v>
-      </c>
-      <c r="B268" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>2414</v>
-      </c>
-      <c r="B269" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>2424</v>
-      </c>
-      <c r="B270" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>2434</v>
-      </c>
-      <c r="B271" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>2444</v>
-      </c>
-      <c r="B272" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>2454</v>
-      </c>
-      <c r="B273" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>2464</v>
-      </c>
-      <c r="B274" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>2474</v>
-      </c>
-      <c r="B275" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>2484</v>
-      </c>
-      <c r="B276" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>2494</v>
-      </c>
-      <c r="B277" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>2504</v>
-      </c>
-      <c r="B278" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>2514</v>
-      </c>
-      <c r="B279" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>2524</v>
-      </c>
-      <c r="B280" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>2534</v>
-      </c>
-      <c r="B281" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>2544</v>
-      </c>
-      <c r="B282" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>2554</v>
-      </c>
-      <c r="B283" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>2564</v>
-      </c>
-      <c r="B284" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>2574</v>
-      </c>
-      <c r="B285" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>2584</v>
-      </c>
-      <c r="B286" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>2594</v>
-      </c>
-      <c r="B287" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>2604</v>
-      </c>
-      <c r="B288" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>2614</v>
-      </c>
-      <c r="B289" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>2624</v>
-      </c>
-      <c r="B290" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>2634</v>
-      </c>
-      <c r="B291" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>2644</v>
-      </c>
-      <c r="B292" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>2654</v>
-      </c>
-      <c r="B293" t="n">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>2664</v>
-      </c>
-      <c r="B294" t="n">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>2674</v>
-      </c>
-      <c r="B295" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>2684</v>
-      </c>
-      <c r="B296" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>2694</v>
-      </c>
-      <c r="B297" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>2704</v>
-      </c>
-      <c r="B298" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>2714</v>
-      </c>
-      <c r="B299" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>2724</v>
-      </c>
-      <c r="B300" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>2734</v>
-      </c>
-      <c r="B301" t="n">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>2735</v>
-      </c>
-      <c r="B302" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>2744</v>
-      </c>
-      <c r="B303" t="n">
-        <v>3.535</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>2754</v>
-      </c>
-      <c r="B304" t="n">
-        <v>2.995</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>2764</v>
-      </c>
-      <c r="B305" t="n">
-        <v>3.455</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>2774</v>
-      </c>
-      <c r="B306" t="n">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>2775</v>
-      </c>
-      <c r="B307" t="n">
-        <v>3.3466</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>2784</v>
-      </c>
-      <c r="B308" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>2794</v>
-      </c>
-      <c r="B309" t="n">
-        <v>3.045</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>2804</v>
-      </c>
-      <c r="B310" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>2814</v>
-      </c>
-      <c r="B311" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>2824</v>
-      </c>
-      <c r="B312" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>2834</v>
-      </c>
-      <c r="B313" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>2844</v>
-      </c>
-      <c r="B314" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>2854</v>
-      </c>
-      <c r="B315" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>2864</v>
-      </c>
-      <c r="B316" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>2868</v>
-      </c>
-      <c r="B317" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>2872</v>
-      </c>
-      <c r="B318" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>2876</v>
-      </c>
-      <c r="B319" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>2880</v>
-      </c>
-      <c r="B320" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>2884</v>
-      </c>
-      <c r="B321" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>2888</v>
-      </c>
-      <c r="B322" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>2892</v>
-      </c>
-      <c r="B323" t="n">
-        <v>3.185</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>2896</v>
-      </c>
-      <c r="B324" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>2900</v>
-      </c>
-      <c r="B325" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>2904</v>
-      </c>
-      <c r="B326" t="n">
-        <v>2.905</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>2908</v>
-      </c>
-      <c r="B327" t="n">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>2912</v>
-      </c>
-      <c r="B328" t="n">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>2916</v>
-      </c>
-      <c r="B329" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>2920</v>
-      </c>
-      <c r="B330" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>2924</v>
-      </c>
-      <c r="B331" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>2928</v>
-      </c>
-      <c r="B332" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>2932</v>
-      </c>
-      <c r="B333" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>2936</v>
-      </c>
-      <c r="B334" t="n">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>2940</v>
-      </c>
-      <c r="B335" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>2968</v>
-      </c>
-      <c r="B336" t="n">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>2972</v>
-      </c>
-      <c r="B337" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>2976</v>
-      </c>
-      <c r="B338" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>2980</v>
-      </c>
-      <c r="B339" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>2984</v>
-      </c>
-      <c r="B340" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>2988</v>
-      </c>
-      <c r="B341" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>2992</v>
-      </c>
-      <c r="B342" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>2996</v>
-      </c>
-      <c r="B343" t="n">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B344" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>3004</v>
-      </c>
-      <c r="B345" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>3008</v>
-      </c>
-      <c r="B346" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>3012</v>
-      </c>
-      <c r="B347" t="n">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>3020</v>
-      </c>
-      <c r="B348" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>3024</v>
-      </c>
-      <c r="B349" t="n">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>3068</v>
-      </c>
-      <c r="B350" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>3072</v>
-      </c>
-      <c r="B351" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>3076</v>
-      </c>
-      <c r="B352" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>3080</v>
-      </c>
-      <c r="B353" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>3084</v>
-      </c>
-      <c r="B354" t="n">
-        <v>3.215</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>3088</v>
-      </c>
-      <c r="B355" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>3092</v>
-      </c>
-      <c r="B356" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>3096</v>
-      </c>
-      <c r="B357" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>3100</v>
-      </c>
-      <c r="B358" t="n">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>3104</v>
-      </c>
-      <c r="B359" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>3114</v>
-      </c>
-      <c r="B360" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>3124</v>
-      </c>
-      <c r="B361" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>3134</v>
-      </c>
-      <c r="B362" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>3144</v>
-      </c>
-      <c r="B363" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>3154</v>
-      </c>
-      <c r="B364" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>3164</v>
-      </c>
-      <c r="B365" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>3174</v>
-      </c>
-      <c r="B366" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
-        <v>3184</v>
-      </c>
-      <c r="B367" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="n">
-        <v>3194</v>
-      </c>
-      <c r="B368" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="n">
-        <v>3204</v>
-      </c>
-      <c r="B369" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="n">
-        <v>3208</v>
-      </c>
-      <c r="B370" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="n">
-        <v>3212</v>
-      </c>
-      <c r="B371" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
-        <v>3216</v>
-      </c>
-      <c r="B372" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="n">
-        <v>3220</v>
-      </c>
-      <c r="B373" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="n">
-        <v>3224</v>
-      </c>
-      <c r="B374" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="n">
-        <v>3228</v>
-      </c>
-      <c r="B375" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="n">
-        <v>3232</v>
-      </c>
-      <c r="B376" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="n">
-        <v>3236</v>
-      </c>
-      <c r="B377" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="n">
-        <v>3240</v>
-      </c>
-      <c r="B378" t="n">
-        <v>3.065</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="n">
-        <v>3244</v>
-      </c>
-      <c r="B379" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="n">
-        <v>3248</v>
-      </c>
-      <c r="B380" t="n">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="n">
-        <v>3252</v>
-      </c>
-      <c r="B381" t="n">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="n">
-        <v>3256</v>
-      </c>
-      <c r="B382" t="n">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="n">
-        <v>3284</v>
-      </c>
-      <c r="B383" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="n">
-        <v>3288</v>
-      </c>
-      <c r="B384" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="n">
-        <v>3292</v>
-      </c>
-      <c r="B385" t="n">
-        <v>3.35</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -12,10 +12,10 @@
     <sheet name="Series Id-34AE56JH" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Series Id-B19318ED" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Series Id-E0961C19" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Series Id-67GH89BG" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Series Id-000476B5" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Series Id-A9AA9941" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Series Id-D81474CD" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Series Id-D81474CD" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Series Id-67GH89BG" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Series Id-000476B5" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Series Id-A9AA9941" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Series Id-56TY87JG" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="SAMPLING Id-4EA5A3B8" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Series Id-B54E03C0" sheetId="12" state="visible" r:id="rId12"/>
@@ -468,7 +468,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v6.20</t>
+          <t>Created with PyAnalyseries v6.24</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2026/03/23 at 18:38:27</t>
+          <t>Saved 2026/03/27 at 19:07:11</t>
         </is>
       </c>
     </row>
@@ -54603,6 +54603,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="21" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="35" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="1" min="7" max="7"/>
+    <col width="176" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>18MD00-2374vsPDB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v/>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series filtered</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#4cca09</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Created 2026/02/23 at 18:12:48</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Imported series&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-A9AA9941&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-C0561A76&lt;/i&gt;&lt;/b&gt; with a moving average of size 3&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-D81474CD&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.54333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.59833333333333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.68333333333333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.55833333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.96333333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.90666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>160</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3.90666666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>180</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.88333333333333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>190</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.84333333333333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>210</v>
+      </c>
+      <c r="B16" t="n">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -57753,7 +57961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -65845,7 +66053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -66055,212 +66263,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="1" min="1" max="1"/>
-    <col width="21" customWidth="1" style="1" min="2" max="2"/>
-    <col width="20" customWidth="1" style="1" min="3" max="3"/>
-    <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="35" customWidth="1" style="1" min="6" max="6"/>
-    <col width="12" customWidth="1" style="1" min="7" max="7"/>
-    <col width="176" customWidth="1" style="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>depth</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>18MD00-2374vsPDB</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B2" t="n">
-        <v/>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Series filtered</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>#4cca09</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Created 2026/02/23 at 18:12:48</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Imported series&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-A9AA9941&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-C0561A76&lt;/i&gt;&lt;/b&gt; with a moving average of size 3&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-D81474CD&lt;/b&gt;&lt;/i&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>104</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>108</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3.54333333333333</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3.59833333333333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>116</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3.68333333333333</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>120</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3.55833333333333</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>140</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>150</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3.96333333333333</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>160</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3.90666666666667</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>160</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3.90666666666667</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>180</v>
-      </c>
-      <c r="B13" t="n">
-        <v>3.88333333333333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>190</v>
-      </c>
-      <c r="B14" t="n">
-        <v>3.84333333333333</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>200</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3.93</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>210</v>
-      </c>
-      <c r="B16" t="n">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -11,19 +11,23 @@
     <sheet name="Series Id-0CF20BB2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Series Id-34AE56JH" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Series Id-E0961C19" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Series Id-D81474CD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Series Id-67GH89BG" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Series Id-000476B5" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Series Id-A9AA9941" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Series Id-56TY87JG" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SAMPLING Id-4EA5A3B8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Series Id-B54E03C0" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="INTERPOLATION Id-20A10A97" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Series Id-AE86905A" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Series Id-1AEAF37E" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Series Id-313FFF47" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="FILTER Id-C0561A76" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SAMPLING Id-CCE4304B" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Series Id-47590D59" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Series Id-B576A3C8" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Series Id-D81474CD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Series Id-67GH89BG" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Series Id-000476B5" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Series Id-A9AA9941" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Series Id-56TY87JG" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SAMPLING Id-4EA5A3B8" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Series Id-B54E03C0" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="INTERPOLATION Id-20A10A97" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Series Id-AE86905A" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Series Id-1AEAF37E" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Series Id-313FFF47" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="FILTER Id-C0561A76" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SAMPLING Id-CCE4304B" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="FILTER Id-BE8DFFAA" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="FILTER Id-1C0CFC46" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -467,7 +471,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v6.25</t>
+          <t>Created with PyAnalyseries v6.26</t>
         </is>
       </c>
     </row>
@@ -490,7 +494,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2026/03/30 at 14:38:19</t>
+          <t>Saved 2026/04/02 at 11:44:20</t>
         </is>
       </c>
     </row>
@@ -500,6 +504,3374 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="21" customWidth="1" style="1" min="2" max="2"/>
+    <col width="11" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="9" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="1" min="7" max="7"/>
+    <col width="20" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>18MD00-2374vsPDB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3.235</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#ff9896</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Imported series</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>160</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>160</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>180</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>190</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>200</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>210</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H385"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="21" customWidth="1" style="1" min="2" max="2"/>
+    <col width="11" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="9" customWidth="1" style="1" min="6" max="6"/>
+    <col width="31" customWidth="1" style="1" min="7" max="7"/>
+    <col width="12" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>18MD00-2374vsPDB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3.235</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#962cff</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>a comment, to be completed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>160</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>180</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>190</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>210</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>220</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>230</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>240</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>250</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>260</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>270</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>280</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>290</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>300</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>310</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>320</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>330</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>340</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>350</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>360</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>370</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>380</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>390</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>400</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>410</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>420</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>430</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>440</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>450</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>460</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>470</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>480</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>490</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>500</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>510</v>
+      </c>
+      <c r="B46" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>520</v>
+      </c>
+      <c r="B47" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>530</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>540</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>560</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>570</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>580</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>590</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>600</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>610</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>620</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>630</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>640</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>650</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>660</v>
+      </c>
+      <c r="B60" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>670</v>
+      </c>
+      <c r="B61" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>680</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>690</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>700</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>710</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>720</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>730</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>740</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>750</v>
+      </c>
+      <c r="B69" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>760</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>770</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>780</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>790</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>800</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>810</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>820</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>830</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>840</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3.395</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>850</v>
+      </c>
+      <c r="B79" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>860</v>
+      </c>
+      <c r="B80" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>870</v>
+      </c>
+      <c r="B81" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>880</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>890</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>900</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>910</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>920</v>
+      </c>
+      <c r="B86" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>930</v>
+      </c>
+      <c r="B87" t="n">
+        <v>3.835</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>940</v>
+      </c>
+      <c r="B88" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>950</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>960</v>
+      </c>
+      <c r="B90" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>970</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>980</v>
+      </c>
+      <c r="B92" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>990</v>
+      </c>
+      <c r="B93" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B96" t="n">
+        <v>3.365</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B99" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B101" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B102" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B103" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B104" t="n">
+        <v>3.5833</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B105" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B106" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B107" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B108" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B109" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B110" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B111" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B112" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B113" t="n">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B114" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B116" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B117" t="n">
+        <v>3.5333</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B118" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B119" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B120" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B121" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B122" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B123" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1317</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1367</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3.385</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3.345</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B148" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B149" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B151" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B153" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B154" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B155" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B156" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1565</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B162" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B163" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B164" t="n">
+        <v>3.1175</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B165" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B169" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B171" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B174" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B176" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>1665</v>
+      </c>
+      <c r="B177" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B179" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>1677</v>
+      </c>
+      <c r="B180" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B181" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B182" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B183" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>1761</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>1773</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B193" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1781</v>
+      </c>
+      <c r="B194" t="n">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>1785</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>1789</v>
+      </c>
+      <c r="B196" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>1793</v>
+      </c>
+      <c r="B197" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>1797</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B199" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B200" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B201" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B203" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2.705</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B209" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1888</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1892</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1896</v>
+      </c>
+      <c r="B212" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B214" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>1912</v>
+      </c>
+      <c r="B216" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B217" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B218" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B220" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B221" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B222" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B223" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B224" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B225" t="n">
+        <v>4.0733</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B229" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B230" t="n">
+        <v>3.9966</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B231" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B232" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2058</v>
+      </c>
+      <c r="B233" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2068</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2078</v>
+      </c>
+      <c r="B235" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2088</v>
+      </c>
+      <c r="B236" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2098</v>
+      </c>
+      <c r="B237" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2108</v>
+      </c>
+      <c r="B238" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2118</v>
+      </c>
+      <c r="B239" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2128</v>
+      </c>
+      <c r="B240" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2138</v>
+      </c>
+      <c r="B241" t="n">
+        <v>3.625</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2148</v>
+      </c>
+      <c r="B242" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2158</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2168</v>
+      </c>
+      <c r="B244" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2178</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2188</v>
+      </c>
+      <c r="B246" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2198</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2208</v>
+      </c>
+      <c r="B248" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2218</v>
+      </c>
+      <c r="B249" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2228</v>
+      </c>
+      <c r="B250" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2238</v>
+      </c>
+      <c r="B251" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2248</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2258</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2268</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2278</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2288</v>
+      </c>
+      <c r="B256" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2298</v>
+      </c>
+      <c r="B257" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2308</v>
+      </c>
+      <c r="B258" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2318</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2328</v>
+      </c>
+      <c r="B260" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2338</v>
+      </c>
+      <c r="B261" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2348</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2358</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2368</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2374</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2384</v>
+      </c>
+      <c r="B266" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2394</v>
+      </c>
+      <c r="B267" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2404</v>
+      </c>
+      <c r="B268" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2414</v>
+      </c>
+      <c r="B269" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2424</v>
+      </c>
+      <c r="B270" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2434</v>
+      </c>
+      <c r="B271" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2444</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2454</v>
+      </c>
+      <c r="B273" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2464</v>
+      </c>
+      <c r="B274" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2474</v>
+      </c>
+      <c r="B275" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2484</v>
+      </c>
+      <c r="B276" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>2494</v>
+      </c>
+      <c r="B277" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>2504</v>
+      </c>
+      <c r="B278" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>2514</v>
+      </c>
+      <c r="B279" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2524</v>
+      </c>
+      <c r="B280" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2534</v>
+      </c>
+      <c r="B281" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2544</v>
+      </c>
+      <c r="B282" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>2554</v>
+      </c>
+      <c r="B283" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2564</v>
+      </c>
+      <c r="B284" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>2574</v>
+      </c>
+      <c r="B285" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>2584</v>
+      </c>
+      <c r="B286" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>2594</v>
+      </c>
+      <c r="B287" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2604</v>
+      </c>
+      <c r="B288" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>2614</v>
+      </c>
+      <c r="B289" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>2624</v>
+      </c>
+      <c r="B290" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2634</v>
+      </c>
+      <c r="B291" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2644</v>
+      </c>
+      <c r="B292" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2654</v>
+      </c>
+      <c r="B293" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2664</v>
+      </c>
+      <c r="B294" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2674</v>
+      </c>
+      <c r="B295" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2684</v>
+      </c>
+      <c r="B296" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2694</v>
+      </c>
+      <c r="B297" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2704</v>
+      </c>
+      <c r="B298" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2714</v>
+      </c>
+      <c r="B299" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>2724</v>
+      </c>
+      <c r="B300" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>2734</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>2735</v>
+      </c>
+      <c r="B302" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>2744</v>
+      </c>
+      <c r="B303" t="n">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>2754</v>
+      </c>
+      <c r="B304" t="n">
+        <v>2.995</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>2764</v>
+      </c>
+      <c r="B305" t="n">
+        <v>3.455</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>2774</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>2775</v>
+      </c>
+      <c r="B307" t="n">
+        <v>3.3466</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>2784</v>
+      </c>
+      <c r="B308" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>2794</v>
+      </c>
+      <c r="B309" t="n">
+        <v>3.045</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>2804</v>
+      </c>
+      <c r="B310" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>2814</v>
+      </c>
+      <c r="B311" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>2824</v>
+      </c>
+      <c r="B312" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>2834</v>
+      </c>
+      <c r="B313" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>2844</v>
+      </c>
+      <c r="B314" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>2854</v>
+      </c>
+      <c r="B315" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>2864</v>
+      </c>
+      <c r="B316" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2868</v>
+      </c>
+      <c r="B317" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>2872</v>
+      </c>
+      <c r="B318" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>2876</v>
+      </c>
+      <c r="B319" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>2880</v>
+      </c>
+      <c r="B320" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>2884</v>
+      </c>
+      <c r="B321" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2888</v>
+      </c>
+      <c r="B322" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>2892</v>
+      </c>
+      <c r="B323" t="n">
+        <v>3.185</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2896</v>
+      </c>
+      <c r="B324" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B325" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2904</v>
+      </c>
+      <c r="B326" t="n">
+        <v>2.905</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2908</v>
+      </c>
+      <c r="B327" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2912</v>
+      </c>
+      <c r="B328" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>2916</v>
+      </c>
+      <c r="B329" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2920</v>
+      </c>
+      <c r="B330" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2924</v>
+      </c>
+      <c r="B331" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2928</v>
+      </c>
+      <c r="B332" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2932</v>
+      </c>
+      <c r="B333" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2936</v>
+      </c>
+      <c r="B334" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2940</v>
+      </c>
+      <c r="B335" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>2968</v>
+      </c>
+      <c r="B336" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>2972</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>2976</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>2980</v>
+      </c>
+      <c r="B339" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>2984</v>
+      </c>
+      <c r="B340" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>2988</v>
+      </c>
+      <c r="B341" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>2992</v>
+      </c>
+      <c r="B342" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>2996</v>
+      </c>
+      <c r="B343" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3004</v>
+      </c>
+      <c r="B345" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3008</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3012</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3020</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3024</v>
+      </c>
+      <c r="B349" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3068</v>
+      </c>
+      <c r="B350" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3072</v>
+      </c>
+      <c r="B351" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3076</v>
+      </c>
+      <c r="B352" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>3080</v>
+      </c>
+      <c r="B353" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>3084</v>
+      </c>
+      <c r="B354" t="n">
+        <v>3.215</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>3088</v>
+      </c>
+      <c r="B355" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>3092</v>
+      </c>
+      <c r="B356" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>3096</v>
+      </c>
+      <c r="B357" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B358" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>3104</v>
+      </c>
+      <c r="B359" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>3114</v>
+      </c>
+      <c r="B360" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3124</v>
+      </c>
+      <c r="B361" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B362" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3144</v>
+      </c>
+      <c r="B363" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>3154</v>
+      </c>
+      <c r="B364" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>3164</v>
+      </c>
+      <c r="B365" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B366" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>3184</v>
+      </c>
+      <c r="B367" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>3194</v>
+      </c>
+      <c r="B368" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B369" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B370" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B371" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B372" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>3220</v>
+      </c>
+      <c r="B373" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>3224</v>
+      </c>
+      <c r="B374" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>3228</v>
+      </c>
+      <c r="B375" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>3232</v>
+      </c>
+      <c r="B376" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>3236</v>
+      </c>
+      <c r="B377" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>3240</v>
+      </c>
+      <c r="B378" t="n">
+        <v>3.065</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>3244</v>
+      </c>
+      <c r="B379" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>3248</v>
+      </c>
+      <c r="B380" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>3252</v>
+      </c>
+      <c r="B381" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>3256</v>
+      </c>
+      <c r="B382" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>3284</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>3288</v>
+      </c>
+      <c r="B384" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>3292</v>
+      </c>
+      <c r="B385" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -577,7 +3949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -765,7 +4137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -873,7 +4245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17885,7 +21257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26429,7 +29801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34973,7 +38345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35055,7 +38427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43229,6 +46601,170 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="1" min="1" max="1"/>
+    <col width="25" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15" customWidth="1" style="1" min="3" max="3"/>
+    <col width="35" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="91" customWidth="1" style="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Moving average 9 pts</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Created 2026/04/02 at 11:43:27</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FILTER &lt;i&gt;&lt;b&gt;Id-BE8DFFAA&lt;/i&gt;&lt;/b&gt; with parameters :&lt;ul&gt;&lt;li&gt;Moving average size : 9&lt;/ul&gt;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="1" min="1" max="1"/>
+    <col width="25" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15" customWidth="1" style="1" min="3" max="3"/>
+    <col width="35" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="91" customWidth="1" style="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Moving average 9 pts</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Created 2026/04/02 at 11:43:57</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FILTER &lt;i&gt;&lt;b&gt;Id-1C0CFC46&lt;/i&gt;&lt;/b&gt; with parameters :&lt;ul&gt;&lt;li&gt;Moving average size : 9&lt;/ul&gt;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -47087,6 +50623,1406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" style="1" min="1" max="1"/>
+    <col width="27" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20" customWidth="1" style="1" min="3" max="3"/>
+    <col width="21" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="35" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="1" min="7" max="7"/>
+    <col width="341" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depthODP849 [cm]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>d13Cforams-b</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v/>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series filtered</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>My serie sampled</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#c5b0d5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Created 2026/04/02 at 11:43:27</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Series &lt;i&gt;&lt;b&gt;Id-34AE56JH&lt;/i&gt;&lt;/b&gt; sampled every 50.0 and linear interpolation with integration at True with SAMPLE &lt;i&gt;&lt;b&gt;Id-4EA5A3B8&lt;/i&gt;&lt;/b&gt;&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-E0961C19&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-E0961C19&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-BE8DFFAA&lt;/i&gt;&lt;/b&gt; with a moving average of size 9&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-47590D59&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>250</v>
+      </c>
+      <c r="B5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>300</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.05968040193082172</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>350</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.08615864248404627</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>400</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.1308330147747418</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>450</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.1331379980791808</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.1464137382012981</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>550</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.195218656152176</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>600</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.2191401115954814</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>650</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.2488916909285301</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>700</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.2484516607964616</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>750</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.2411711975300602</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>800</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.2110127356847231</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>850</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.1657069843698022</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>900</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.1793346766089438</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>950</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.2083123675650069</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.1881770761641514</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.1642147109617823</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.1039510507456236</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.1055114771546929</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.1097098599575426</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1250</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.1316500631578827</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.0946593605725225</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1350</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.0384403036885505</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.003867063135945441</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1450</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.006554202639197339</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.02258661188731818</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.04322679168162775</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.01850033459999119</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.002247464544674999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.004722545546414331</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.1045601675433115</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.1850904104397549</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.203098824831748</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.1981582381438153</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.220314147699544</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.260395917080792</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.2560576525463312</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.2942956607606835</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2150</v>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.2913633346873847</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B44" t="n">
+        <v>-0.2680742985779777</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2250</v>
+      </c>
+      <c r="B45" t="n">
+        <v>-0.2553991721115292</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B46" t="n">
+        <v>-0.3120672401520165</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2350</v>
+      </c>
+      <c r="B47" t="n">
+        <v>-0.3457890673653144</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B48" t="n">
+        <v>-0.3969226425150905</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2450</v>
+      </c>
+      <c r="B49" t="n">
+        <v>-0.4221808163158047</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B50" t="n">
+        <v>-0.4373582746278811</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2550</v>
+      </c>
+      <c r="B51" t="n">
+        <v>-0.418995515784823</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2600</v>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.4125224108090079</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2650</v>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.3911482065946774</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2700</v>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.3606270683165219</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2750</v>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.3424839345978551</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.2971112488716991</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2850</v>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.2237208568018217</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B58" t="n">
+        <v>-0.1722638671342867</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2950</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.1846479693031896</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.1810042000303155</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3050</v>
+      </c>
+      <c r="B61" t="n">
+        <v>-0.1516388028665038</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.1599470536339232</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3150</v>
+      </c>
+      <c r="B63" t="n">
+        <v>-0.1926652015005252</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3200</v>
+      </c>
+      <c r="B64" t="n">
+        <v>-0.1401330646053738</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3250</v>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.1230347086930034</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3300</v>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.1580713814657319</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3350</v>
+      </c>
+      <c r="B67" t="n">
+        <v>-0.1579038239353874</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3400</v>
+      </c>
+      <c r="B68" t="n">
+        <v>-0.1312427364984007</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3450</v>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.1444494194605686</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B70" t="n">
+        <v>-0.1542784642115958</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3550</v>
+      </c>
+      <c r="B71" t="n">
+        <v>-0.1478849606790214</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3600</v>
+      </c>
+      <c r="B72" t="n">
+        <v>-0.1613571105138993</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3650</v>
+      </c>
+      <c r="B73" t="n">
+        <v>-0.1654418651848227</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3700</v>
+      </c>
+      <c r="B74" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3750</v>
+      </c>
+      <c r="B75" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B76" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3850</v>
+      </c>
+      <c r="B77" t="n">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" style="1" min="1" max="1"/>
+    <col width="26" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20" customWidth="1" style="1" min="3" max="3"/>
+    <col width="21" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="35" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="1" min="7" max="7"/>
+    <col width="497" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depthODP849 [cm]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>d13Cforams-b</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v/>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series filtered</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>My serie sampled</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#9467bd</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Created 2026/04/02 at 11:43:57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Series &lt;i&gt;&lt;b&gt;Id-34AE56JH&lt;/i&gt;&lt;/b&gt; sampled every 50.0 and linear interpolation with integration at True with SAMPLE &lt;i&gt;&lt;b&gt;Id-4EA5A3B8&lt;/i&gt;&lt;/b&gt;&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-E0961C19&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-E0961C19&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-BE8DFFAA&lt;/i&gt;&lt;/b&gt; with a moving average of size 9&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-47590D59&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-47590D59&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-1C0CFC46&lt;/i&gt;&lt;/b&gt; with a moving average of size 9&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-B576A3C8&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>250</v>
+      </c>
+      <c r="B5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>300</v>
+      </c>
+      <c r="B6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>350</v>
+      </c>
+      <c r="B7" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>400</v>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>450</v>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.1631028794380819</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>550</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.1832685233935529</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>600</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.1971412004158503</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>650</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.2010160859264126</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>700</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.2061490502074974</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>750</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.2130266756923539</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>800</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.2122442779159067</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>850</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.2061414556232735</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>900</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.190036940047395</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>950</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.1741546974205318</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.1595478821346966</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.1507298074094921</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.1428356269875721</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.127180696663084</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.1036052043629781</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1250</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.08342488508242768</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.06768842962970946</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1350</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.06094128973370991</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.05127338500540971</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1450</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.03883368228294108</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.02473062477055571</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.02583071443397671</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.04212517073966608</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.06512138051385424</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.08641071779214511</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.1083804439935036</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.1325103468156329</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.1589056043652262</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.1918548405102661</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.223703817081485</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.2418720538631146</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.2496841384933117</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.2617917401955638</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2150</v>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.2781951656646193</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B44" t="n">
+        <v>-0.2978183317552355</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2250</v>
+      </c>
+      <c r="B45" t="n">
+        <v>-0.315794431670237</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B46" t="n">
+        <v>-0.3359389452348535</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2350</v>
+      </c>
+      <c r="B47" t="n">
+        <v>-0.3497944846819802</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B48" t="n">
+        <v>-0.3632566042510494</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2450</v>
+      </c>
+      <c r="B49" t="n">
+        <v>-0.3769314829195716</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B50" t="n">
+        <v>-0.388623471386793</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2550</v>
+      </c>
+      <c r="B51" t="n">
+        <v>-0.3920031041029973</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2600</v>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.3865944576037067</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2650</v>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.3673498147466769</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2700</v>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.3395812648376193</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2750</v>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.3115023420237647</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.2850588624954862</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2850</v>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.256071794946319</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B58" t="n">
+        <v>-0.2303827779506797</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2950</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.2117203483044578</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.1892369183052932</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3050</v>
+      </c>
+      <c r="B61" t="n">
+        <v>-0.1698950805076603</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.1626006943592059</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3150</v>
+      </c>
+      <c r="B63" t="n">
+        <v>-0.1610051340037726</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3200</v>
+      </c>
+      <c r="B64" t="n">
+        <v>-0.155071219247685</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3250</v>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.1510095769621576</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3300</v>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.1513028726671678</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3350</v>
+      </c>
+      <c r="B67" t="n">
+        <v>-0.1499626401166231</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3400</v>
+      </c>
+      <c r="B68" t="n">
+        <v>-0.1464839633403313</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3450</v>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.1492960522936034</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B70" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3550</v>
+      </c>
+      <c r="B71" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3600</v>
+      </c>
+      <c r="B72" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3650</v>
+      </c>
+      <c r="B73" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3700</v>
+      </c>
+      <c r="B74" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3750</v>
+      </c>
+      <c r="B75" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B76" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3850</v>
+      </c>
+      <c r="B77" t="n">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -47289,7 +52225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -50445,7 +55381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -58539,3372 +63475,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="1" min="1" max="1"/>
-    <col width="21" customWidth="1" style="1" min="2" max="2"/>
-    <col width="11" customWidth="1" style="1" min="3" max="3"/>
-    <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="9" customWidth="1" style="1" min="6" max="6"/>
-    <col width="12" customWidth="1" style="1" min="7" max="7"/>
-    <col width="20" customWidth="1" style="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>depth</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>18MD00-2374vsPDB</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B2" t="n">
-        <v>3.235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Series</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>#ff9896</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Imported series</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>104</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>108</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3.535</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3.605</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>116</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3.655</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>120</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>140</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>150</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>160</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>160</v>
-      </c>
-      <c r="B12" t="n">
-        <v>5.03</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>160</v>
-      </c>
-      <c r="B13" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>180</v>
-      </c>
-      <c r="B14" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>190</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>200</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>210</v>
-      </c>
-      <c r="B17" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H385"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="1" min="1" max="1"/>
-    <col width="21" customWidth="1" style="1" min="2" max="2"/>
-    <col width="11" customWidth="1" style="1" min="3" max="3"/>
-    <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="9" customWidth="1" style="1" min="6" max="6"/>
-    <col width="31" customWidth="1" style="1" min="7" max="7"/>
-    <col width="12" customWidth="1" style="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>depth</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>18MD00-2374vsPDB</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B2" t="n">
-        <v>3.235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Series</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>#962cff</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>a comment, to be completed</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>104</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>108</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3.535</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3.605</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>116</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3.655</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>120</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>140</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>150</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>160</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>160</v>
-      </c>
-      <c r="B12" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>180</v>
-      </c>
-      <c r="B13" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>190</v>
-      </c>
-      <c r="B14" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>200</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>210</v>
-      </c>
-      <c r="B16" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>220</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>230</v>
-      </c>
-      <c r="B18" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>240</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>250</v>
-      </c>
-      <c r="B20" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>260</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>270</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>280</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>290</v>
-      </c>
-      <c r="B24" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>300</v>
-      </c>
-      <c r="B25" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>310</v>
-      </c>
-      <c r="B26" t="n">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>320</v>
-      </c>
-      <c r="B27" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>330</v>
-      </c>
-      <c r="B28" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>340</v>
-      </c>
-      <c r="B29" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>350</v>
-      </c>
-      <c r="B30" t="n">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>360</v>
-      </c>
-      <c r="B31" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>370</v>
-      </c>
-      <c r="B32" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>380</v>
-      </c>
-      <c r="B33" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>390</v>
-      </c>
-      <c r="B34" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>400</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>410</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>420</v>
-      </c>
-      <c r="B37" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>430</v>
-      </c>
-      <c r="B38" t="n">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>440</v>
-      </c>
-      <c r="B39" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>450</v>
-      </c>
-      <c r="B40" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>460</v>
-      </c>
-      <c r="B41" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>470</v>
-      </c>
-      <c r="B42" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>480</v>
-      </c>
-      <c r="B43" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>490</v>
-      </c>
-      <c r="B44" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>500</v>
-      </c>
-      <c r="B45" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>510</v>
-      </c>
-      <c r="B46" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>520</v>
-      </c>
-      <c r="B47" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>530</v>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>540</v>
-      </c>
-      <c r="B49" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>560</v>
-      </c>
-      <c r="B50" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>570</v>
-      </c>
-      <c r="B51" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>580</v>
-      </c>
-      <c r="B52" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>590</v>
-      </c>
-      <c r="B53" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>600</v>
-      </c>
-      <c r="B54" t="n">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>610</v>
-      </c>
-      <c r="B55" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>620</v>
-      </c>
-      <c r="B56" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>630</v>
-      </c>
-      <c r="B57" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>640</v>
-      </c>
-      <c r="B58" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>650</v>
-      </c>
-      <c r="B59" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>660</v>
-      </c>
-      <c r="B60" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>670</v>
-      </c>
-      <c r="B61" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>680</v>
-      </c>
-      <c r="B62" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>690</v>
-      </c>
-      <c r="B63" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>700</v>
-      </c>
-      <c r="B64" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>710</v>
-      </c>
-      <c r="B65" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>720</v>
-      </c>
-      <c r="B66" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>730</v>
-      </c>
-      <c r="B67" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>740</v>
-      </c>
-      <c r="B68" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>750</v>
-      </c>
-      <c r="B69" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>760</v>
-      </c>
-      <c r="B70" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>770</v>
-      </c>
-      <c r="B71" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>780</v>
-      </c>
-      <c r="B72" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>790</v>
-      </c>
-      <c r="B73" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>800</v>
-      </c>
-      <c r="B74" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>810</v>
-      </c>
-      <c r="B75" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>820</v>
-      </c>
-      <c r="B76" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>830</v>
-      </c>
-      <c r="B77" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>840</v>
-      </c>
-      <c r="B78" t="n">
-        <v>3.395</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>850</v>
-      </c>
-      <c r="B79" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>860</v>
-      </c>
-      <c r="B80" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>870</v>
-      </c>
-      <c r="B81" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>880</v>
-      </c>
-      <c r="B82" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>890</v>
-      </c>
-      <c r="B83" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>900</v>
-      </c>
-      <c r="B84" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>910</v>
-      </c>
-      <c r="B85" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>920</v>
-      </c>
-      <c r="B86" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>930</v>
-      </c>
-      <c r="B87" t="n">
-        <v>3.835</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>940</v>
-      </c>
-      <c r="B88" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>950</v>
-      </c>
-      <c r="B89" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>960</v>
-      </c>
-      <c r="B90" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>970</v>
-      </c>
-      <c r="B91" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>980</v>
-      </c>
-      <c r="B92" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>990</v>
-      </c>
-      <c r="B93" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B94" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>1010</v>
-      </c>
-      <c r="B95" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>1020</v>
-      </c>
-      <c r="B96" t="n">
-        <v>3.365</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>1030</v>
-      </c>
-      <c r="B97" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>1040</v>
-      </c>
-      <c r="B98" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>1050</v>
-      </c>
-      <c r="B99" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>1060</v>
-      </c>
-      <c r="B100" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>1070</v>
-      </c>
-      <c r="B101" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>1080</v>
-      </c>
-      <c r="B102" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>1087</v>
-      </c>
-      <c r="B103" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>1097</v>
-      </c>
-      <c r="B104" t="n">
-        <v>3.5833</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>1107</v>
-      </c>
-      <c r="B105" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>1117</v>
-      </c>
-      <c r="B106" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>1127</v>
-      </c>
-      <c r="B107" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>1137</v>
-      </c>
-      <c r="B108" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>1147</v>
-      </c>
-      <c r="B109" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>1157</v>
-      </c>
-      <c r="B110" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>1167</v>
-      </c>
-      <c r="B111" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>1177</v>
-      </c>
-      <c r="B112" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>1187</v>
-      </c>
-      <c r="B113" t="n">
-        <v>3.355</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>1197</v>
-      </c>
-      <c r="B114" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>1207</v>
-      </c>
-      <c r="B115" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>1217</v>
-      </c>
-      <c r="B116" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>1227</v>
-      </c>
-      <c r="B117" t="n">
-        <v>3.5333</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>1237</v>
-      </c>
-      <c r="B118" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>1247</v>
-      </c>
-      <c r="B119" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>1257</v>
-      </c>
-      <c r="B120" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>1267</v>
-      </c>
-      <c r="B121" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>1277</v>
-      </c>
-      <c r="B122" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>1287</v>
-      </c>
-      <c r="B123" t="n">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>1297</v>
-      </c>
-      <c r="B124" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>1307</v>
-      </c>
-      <c r="B125" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>1317</v>
-      </c>
-      <c r="B126" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>1327</v>
-      </c>
-      <c r="B127" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>1337</v>
-      </c>
-      <c r="B128" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>1347</v>
-      </c>
-      <c r="B129" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>1357</v>
-      </c>
-      <c r="B130" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>1367</v>
-      </c>
-      <c r="B131" t="n">
-        <v>3.385</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B132" t="n">
-        <v>3.345</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>1387</v>
-      </c>
-      <c r="B133" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>1397</v>
-      </c>
-      <c r="B134" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>1407</v>
-      </c>
-      <c r="B135" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>1417</v>
-      </c>
-      <c r="B136" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>1427</v>
-      </c>
-      <c r="B137" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>1437</v>
-      </c>
-      <c r="B138" t="n">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>1447</v>
-      </c>
-      <c r="B139" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>1457</v>
-      </c>
-      <c r="B140" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>1467</v>
-      </c>
-      <c r="B141" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>1477</v>
-      </c>
-      <c r="B142" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>1487</v>
-      </c>
-      <c r="B143" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>1497</v>
-      </c>
-      <c r="B144" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>1507</v>
-      </c>
-      <c r="B145" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>1511</v>
-      </c>
-      <c r="B146" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>1515</v>
-      </c>
-      <c r="B147" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>1519</v>
-      </c>
-      <c r="B148" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>1523</v>
-      </c>
-      <c r="B149" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>1527</v>
-      </c>
-      <c r="B150" t="n">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>1531</v>
-      </c>
-      <c r="B151" t="n">
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>1535</v>
-      </c>
-      <c r="B152" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>1537</v>
-      </c>
-      <c r="B153" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>1541</v>
-      </c>
-      <c r="B154" t="n">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>1545</v>
-      </c>
-      <c r="B155" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>1549</v>
-      </c>
-      <c r="B156" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>1553</v>
-      </c>
-      <c r="B157" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>1557</v>
-      </c>
-      <c r="B158" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>1561</v>
-      </c>
-      <c r="B159" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>1565</v>
-      </c>
-      <c r="B160" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>1569</v>
-      </c>
-      <c r="B161" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>1573</v>
-      </c>
-      <c r="B162" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>1577</v>
-      </c>
-      <c r="B163" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>1581</v>
-      </c>
-      <c r="B164" t="n">
-        <v>3.1175</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>1585</v>
-      </c>
-      <c r="B165" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>1589</v>
-      </c>
-      <c r="B166" t="n">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>1593</v>
-      </c>
-      <c r="B167" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>1597</v>
-      </c>
-      <c r="B168" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>1601</v>
-      </c>
-      <c r="B169" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>1605</v>
-      </c>
-      <c r="B170" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>1609</v>
-      </c>
-      <c r="B171" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>1645</v>
-      </c>
-      <c r="B172" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>1649</v>
-      </c>
-      <c r="B173" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>1653</v>
-      </c>
-      <c r="B174" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>1657</v>
-      </c>
-      <c r="B175" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>1661</v>
-      </c>
-      <c r="B176" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>1665</v>
-      </c>
-      <c r="B177" t="n">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>1669</v>
-      </c>
-      <c r="B178" t="n">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>1673</v>
-      </c>
-      <c r="B179" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>1677</v>
-      </c>
-      <c r="B180" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>1681</v>
-      </c>
-      <c r="B181" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>1685</v>
-      </c>
-      <c r="B182" t="n">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>1689</v>
-      </c>
-      <c r="B183" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>1693</v>
-      </c>
-      <c r="B184" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>1697</v>
-      </c>
-      <c r="B185" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>1701</v>
-      </c>
-      <c r="B186" t="n">
-        <v>2.67</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>1705</v>
-      </c>
-      <c r="B187" t="n">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>1709</v>
-      </c>
-      <c r="B188" t="n">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>1761</v>
-      </c>
-      <c r="B189" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>1765</v>
-      </c>
-      <c r="B190" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>1769</v>
-      </c>
-      <c r="B191" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>1773</v>
-      </c>
-      <c r="B192" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>1777</v>
-      </c>
-      <c r="B193" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>1781</v>
-      </c>
-      <c r="B194" t="n">
-        <v>3.355</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>1785</v>
-      </c>
-      <c r="B195" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>1789</v>
-      </c>
-      <c r="B196" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>1793</v>
-      </c>
-      <c r="B197" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>1797</v>
-      </c>
-      <c r="B198" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>1801</v>
-      </c>
-      <c r="B199" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B200" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>1809</v>
-      </c>
-      <c r="B201" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>1813</v>
-      </c>
-      <c r="B202" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>1817</v>
-      </c>
-      <c r="B203" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>1821</v>
-      </c>
-      <c r="B204" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>1825</v>
-      </c>
-      <c r="B205" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>1829</v>
-      </c>
-      <c r="B206" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>1833</v>
-      </c>
-      <c r="B207" t="n">
-        <v>2.705</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>1837</v>
-      </c>
-      <c r="B208" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>1884</v>
-      </c>
-      <c r="B209" t="n">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>1888</v>
-      </c>
-      <c r="B210" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>1892</v>
-      </c>
-      <c r="B211" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>1896</v>
-      </c>
-      <c r="B212" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>1900</v>
-      </c>
-      <c r="B213" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>1904</v>
-      </c>
-      <c r="B214" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B215" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>1912</v>
-      </c>
-      <c r="B216" t="n">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>1916</v>
-      </c>
-      <c r="B217" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>1920</v>
-      </c>
-      <c r="B218" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B219" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>1928</v>
-      </c>
-      <c r="B220" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B221" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>1948</v>
-      </c>
-      <c r="B222" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B223" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B224" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B225" t="n">
-        <v>4.0733</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B226" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B227" t="n">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B228" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B229" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B230" t="n">
-        <v>3.9966</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B231" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>2048</v>
-      </c>
-      <c r="B232" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>2058</v>
-      </c>
-      <c r="B233" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>2068</v>
-      </c>
-      <c r="B234" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>2078</v>
-      </c>
-      <c r="B235" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>2088</v>
-      </c>
-      <c r="B236" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>2098</v>
-      </c>
-      <c r="B237" t="n">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>2108</v>
-      </c>
-      <c r="B238" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>2118</v>
-      </c>
-      <c r="B239" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>2128</v>
-      </c>
-      <c r="B240" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>2138</v>
-      </c>
-      <c r="B241" t="n">
-        <v>3.625</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>2148</v>
-      </c>
-      <c r="B242" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>2158</v>
-      </c>
-      <c r="B243" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>2168</v>
-      </c>
-      <c r="B244" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>2178</v>
-      </c>
-      <c r="B245" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>2188</v>
-      </c>
-      <c r="B246" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>2198</v>
-      </c>
-      <c r="B247" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>2208</v>
-      </c>
-      <c r="B248" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>2218</v>
-      </c>
-      <c r="B249" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>2228</v>
-      </c>
-      <c r="B250" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>2238</v>
-      </c>
-      <c r="B251" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>2248</v>
-      </c>
-      <c r="B252" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>2258</v>
-      </c>
-      <c r="B253" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>2268</v>
-      </c>
-      <c r="B254" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>2278</v>
-      </c>
-      <c r="B255" t="n">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>2288</v>
-      </c>
-      <c r="B256" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>2298</v>
-      </c>
-      <c r="B257" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>2308</v>
-      </c>
-      <c r="B258" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>2318</v>
-      </c>
-      <c r="B259" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>2328</v>
-      </c>
-      <c r="B260" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>2338</v>
-      </c>
-      <c r="B261" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>2348</v>
-      </c>
-      <c r="B262" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>2358</v>
-      </c>
-      <c r="B263" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>2368</v>
-      </c>
-      <c r="B264" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>2374</v>
-      </c>
-      <c r="B265" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>2384</v>
-      </c>
-      <c r="B266" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>2394</v>
-      </c>
-      <c r="B267" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>2404</v>
-      </c>
-      <c r="B268" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>2414</v>
-      </c>
-      <c r="B269" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>2424</v>
-      </c>
-      <c r="B270" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>2434</v>
-      </c>
-      <c r="B271" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>2444</v>
-      </c>
-      <c r="B272" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>2454</v>
-      </c>
-      <c r="B273" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>2464</v>
-      </c>
-      <c r="B274" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>2474</v>
-      </c>
-      <c r="B275" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>2484</v>
-      </c>
-      <c r="B276" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>2494</v>
-      </c>
-      <c r="B277" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>2504</v>
-      </c>
-      <c r="B278" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>2514</v>
-      </c>
-      <c r="B279" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>2524</v>
-      </c>
-      <c r="B280" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>2534</v>
-      </c>
-      <c r="B281" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>2544</v>
-      </c>
-      <c r="B282" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>2554</v>
-      </c>
-      <c r="B283" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>2564</v>
-      </c>
-      <c r="B284" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>2574</v>
-      </c>
-      <c r="B285" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>2584</v>
-      </c>
-      <c r="B286" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>2594</v>
-      </c>
-      <c r="B287" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>2604</v>
-      </c>
-      <c r="B288" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>2614</v>
-      </c>
-      <c r="B289" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>2624</v>
-      </c>
-      <c r="B290" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>2634</v>
-      </c>
-      <c r="B291" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>2644</v>
-      </c>
-      <c r="B292" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>2654</v>
-      </c>
-      <c r="B293" t="n">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>2664</v>
-      </c>
-      <c r="B294" t="n">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>2674</v>
-      </c>
-      <c r="B295" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>2684</v>
-      </c>
-      <c r="B296" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>2694</v>
-      </c>
-      <c r="B297" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>2704</v>
-      </c>
-      <c r="B298" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>2714</v>
-      </c>
-      <c r="B299" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>2724</v>
-      </c>
-      <c r="B300" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>2734</v>
-      </c>
-      <c r="B301" t="n">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>2735</v>
-      </c>
-      <c r="B302" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>2744</v>
-      </c>
-      <c r="B303" t="n">
-        <v>3.535</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>2754</v>
-      </c>
-      <c r="B304" t="n">
-        <v>2.995</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>2764</v>
-      </c>
-      <c r="B305" t="n">
-        <v>3.455</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>2774</v>
-      </c>
-      <c r="B306" t="n">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>2775</v>
-      </c>
-      <c r="B307" t="n">
-        <v>3.3466</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>2784</v>
-      </c>
-      <c r="B308" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>2794</v>
-      </c>
-      <c r="B309" t="n">
-        <v>3.045</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>2804</v>
-      </c>
-      <c r="B310" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>2814</v>
-      </c>
-      <c r="B311" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>2824</v>
-      </c>
-      <c r="B312" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>2834</v>
-      </c>
-      <c r="B313" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>2844</v>
-      </c>
-      <c r="B314" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>2854</v>
-      </c>
-      <c r="B315" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>2864</v>
-      </c>
-      <c r="B316" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>2868</v>
-      </c>
-      <c r="B317" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>2872</v>
-      </c>
-      <c r="B318" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>2876</v>
-      </c>
-      <c r="B319" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>2880</v>
-      </c>
-      <c r="B320" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>2884</v>
-      </c>
-      <c r="B321" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>2888</v>
-      </c>
-      <c r="B322" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>2892</v>
-      </c>
-      <c r="B323" t="n">
-        <v>3.185</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>2896</v>
-      </c>
-      <c r="B324" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>2900</v>
-      </c>
-      <c r="B325" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>2904</v>
-      </c>
-      <c r="B326" t="n">
-        <v>2.905</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>2908</v>
-      </c>
-      <c r="B327" t="n">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>2912</v>
-      </c>
-      <c r="B328" t="n">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>2916</v>
-      </c>
-      <c r="B329" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>2920</v>
-      </c>
-      <c r="B330" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>2924</v>
-      </c>
-      <c r="B331" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>2928</v>
-      </c>
-      <c r="B332" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>2932</v>
-      </c>
-      <c r="B333" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>2936</v>
-      </c>
-      <c r="B334" t="n">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>2940</v>
-      </c>
-      <c r="B335" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>2968</v>
-      </c>
-      <c r="B336" t="n">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>2972</v>
-      </c>
-      <c r="B337" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>2976</v>
-      </c>
-      <c r="B338" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>2980</v>
-      </c>
-      <c r="B339" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>2984</v>
-      </c>
-      <c r="B340" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>2988</v>
-      </c>
-      <c r="B341" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>2992</v>
-      </c>
-      <c r="B342" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>2996</v>
-      </c>
-      <c r="B343" t="n">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B344" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>3004</v>
-      </c>
-      <c r="B345" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>3008</v>
-      </c>
-      <c r="B346" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>3012</v>
-      </c>
-      <c r="B347" t="n">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>3020</v>
-      </c>
-      <c r="B348" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>3024</v>
-      </c>
-      <c r="B349" t="n">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>3068</v>
-      </c>
-      <c r="B350" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>3072</v>
-      </c>
-      <c r="B351" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>3076</v>
-      </c>
-      <c r="B352" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>3080</v>
-      </c>
-      <c r="B353" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>3084</v>
-      </c>
-      <c r="B354" t="n">
-        <v>3.215</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>3088</v>
-      </c>
-      <c r="B355" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>3092</v>
-      </c>
-      <c r="B356" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>3096</v>
-      </c>
-      <c r="B357" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>3100</v>
-      </c>
-      <c r="B358" t="n">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>3104</v>
-      </c>
-      <c r="B359" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>3114</v>
-      </c>
-      <c r="B360" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>3124</v>
-      </c>
-      <c r="B361" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>3134</v>
-      </c>
-      <c r="B362" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>3144</v>
-      </c>
-      <c r="B363" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>3154</v>
-      </c>
-      <c r="B364" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>3164</v>
-      </c>
-      <c r="B365" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>3174</v>
-      </c>
-      <c r="B366" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
-        <v>3184</v>
-      </c>
-      <c r="B367" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="n">
-        <v>3194</v>
-      </c>
-      <c r="B368" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="n">
-        <v>3204</v>
-      </c>
-      <c r="B369" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="n">
-        <v>3208</v>
-      </c>
-      <c r="B370" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="n">
-        <v>3212</v>
-      </c>
-      <c r="B371" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
-        <v>3216</v>
-      </c>
-      <c r="B372" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="n">
-        <v>3220</v>
-      </c>
-      <c r="B373" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="n">
-        <v>3224</v>
-      </c>
-      <c r="B374" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="n">
-        <v>3228</v>
-      </c>
-      <c r="B375" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="n">
-        <v>3232</v>
-      </c>
-      <c r="B376" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="n">
-        <v>3236</v>
-      </c>
-      <c r="B377" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="n">
-        <v>3240</v>
-      </c>
-      <c r="B378" t="n">
-        <v>3.065</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="n">
-        <v>3244</v>
-      </c>
-      <c r="B379" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="n">
-        <v>3248</v>
-      </c>
-      <c r="B380" t="n">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="n">
-        <v>3252</v>
-      </c>
-      <c r="B381" t="n">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="n">
-        <v>3256</v>
-      </c>
-      <c r="B382" t="n">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="n">
-        <v>3284</v>
-      </c>
-      <c r="B383" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="n">
-        <v>3288</v>
-      </c>
-      <c r="B384" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="n">
-        <v>3292</v>
-      </c>
-      <c r="B385" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -15,16 +15,17 @@
     <sheet name="Series Id-67GH89BG" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Series Id-000476B5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Series Id-A9AA9941" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Series Id-56TY87JG" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SAMPLING Id-4EA5A3B8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Series Id-B54E03C0" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="INTERPOLATION Id-20A10A97" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Series Id-AE86905A" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Series Id-1AEAF37E" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Series Id-313FFF47" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="FILTER Id-C0561A76" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SAMPLING Id-CCE4304B" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="FILTER Id-BE8DFFAA" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Series Id-1D838C92" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Series Id-56TY87JG" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SAMPLING Id-4EA5A3B8" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Series Id-B54E03C0" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="INTERPOLATION Id-20A10A97" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Series Id-AE86905A" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Series Id-1AEAF37E" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Series Id-313FFF47" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="FILTER Id-C0561A76" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SAMPLING Id-CCE4304B" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FILTER Id-BE8DFFAA" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -468,7 +469,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v6.30</t>
+          <t>Created with PyAnalyseries v6.34</t>
         </is>
       </c>
     </row>
@@ -491,7 +492,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2026/04/16 at 17:51:29</t>
+          <t>Saved 2026/06/08 at 18:01:44</t>
         </is>
       </c>
     </row>
@@ -501,6 +502,3162 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H385"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="21" customWidth="1" style="1" min="2" max="2"/>
+    <col width="11" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="5"/>
+    <col width="9" customWidth="1" style="1" min="6" max="6"/>
+    <col width="31" customWidth="1" style="1" min="7" max="7"/>
+    <col width="12" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>18MD00-2374vsPDB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3.235</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#962cff</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>a comment, to be completed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>160</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>180</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>190</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>210</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>220</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>230</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>240</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>250</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>260</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>270</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>280</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>290</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>300</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>310</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>320</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>330</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>340</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>350</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>360</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>370</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>380</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>390</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>400</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>410</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>420</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>430</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>440</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>450</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>460</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>470</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>480</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>490</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>500</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>510</v>
+      </c>
+      <c r="B46" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>520</v>
+      </c>
+      <c r="B47" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>530</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>540</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>560</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>570</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>580</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>590</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>600</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>610</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>620</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>630</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>640</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>650</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>660</v>
+      </c>
+      <c r="B60" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>670</v>
+      </c>
+      <c r="B61" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>680</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>690</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>700</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>710</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>720</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>730</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>740</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>750</v>
+      </c>
+      <c r="B69" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>760</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>770</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>780</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>790</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>800</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>810</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>820</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>830</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>840</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3.395</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>850</v>
+      </c>
+      <c r="B79" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>860</v>
+      </c>
+      <c r="B80" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>870</v>
+      </c>
+      <c r="B81" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>880</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>890</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>900</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>910</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>920</v>
+      </c>
+      <c r="B86" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>930</v>
+      </c>
+      <c r="B87" t="n">
+        <v>3.835</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>940</v>
+      </c>
+      <c r="B88" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>950</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>960</v>
+      </c>
+      <c r="B90" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>970</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>980</v>
+      </c>
+      <c r="B92" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>990</v>
+      </c>
+      <c r="B93" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B96" t="n">
+        <v>3.365</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B99" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B101" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B102" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B103" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B104" t="n">
+        <v>3.5833</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B105" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B106" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B107" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B108" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B109" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B110" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B111" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B112" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B113" t="n">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B114" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B116" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B117" t="n">
+        <v>3.5333</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B118" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B119" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B120" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B121" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B122" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B123" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1317</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1367</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3.385</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3.345</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B148" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B149" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B151" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B153" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B154" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B155" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B156" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1565</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B162" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B163" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B164" t="n">
+        <v>3.1175</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B165" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B169" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B171" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B174" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B176" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>1665</v>
+      </c>
+      <c r="B177" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B179" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>1677</v>
+      </c>
+      <c r="B180" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B181" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B182" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B183" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>1761</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>1773</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B193" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1781</v>
+      </c>
+      <c r="B194" t="n">
+        <v>3.355</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>1785</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>1789</v>
+      </c>
+      <c r="B196" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>1793</v>
+      </c>
+      <c r="B197" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>1797</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B199" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B200" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B201" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B203" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2.705</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B209" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1888</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1892</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1896</v>
+      </c>
+      <c r="B212" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B214" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>1912</v>
+      </c>
+      <c r="B216" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>1916</v>
+      </c>
+      <c r="B217" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B218" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>1928</v>
+      </c>
+      <c r="B220" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B221" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B222" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B223" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B224" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B225" t="n">
+        <v>4.0733</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B229" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B230" t="n">
+        <v>3.9966</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B231" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B232" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2058</v>
+      </c>
+      <c r="B233" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2068</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2078</v>
+      </c>
+      <c r="B235" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2088</v>
+      </c>
+      <c r="B236" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2098</v>
+      </c>
+      <c r="B237" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2108</v>
+      </c>
+      <c r="B238" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2118</v>
+      </c>
+      <c r="B239" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2128</v>
+      </c>
+      <c r="B240" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2138</v>
+      </c>
+      <c r="B241" t="n">
+        <v>3.625</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2148</v>
+      </c>
+      <c r="B242" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2158</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2168</v>
+      </c>
+      <c r="B244" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2178</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2188</v>
+      </c>
+      <c r="B246" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2198</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2208</v>
+      </c>
+      <c r="B248" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2218</v>
+      </c>
+      <c r="B249" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2228</v>
+      </c>
+      <c r="B250" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2238</v>
+      </c>
+      <c r="B251" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2248</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2258</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2268</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2278</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2288</v>
+      </c>
+      <c r="B256" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2298</v>
+      </c>
+      <c r="B257" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2308</v>
+      </c>
+      <c r="B258" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2318</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2328</v>
+      </c>
+      <c r="B260" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2338</v>
+      </c>
+      <c r="B261" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2348</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2358</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2368</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2374</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2384</v>
+      </c>
+      <c r="B266" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2394</v>
+      </c>
+      <c r="B267" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2404</v>
+      </c>
+      <c r="B268" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2414</v>
+      </c>
+      <c r="B269" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2424</v>
+      </c>
+      <c r="B270" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2434</v>
+      </c>
+      <c r="B271" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2444</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2454</v>
+      </c>
+      <c r="B273" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2464</v>
+      </c>
+      <c r="B274" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2474</v>
+      </c>
+      <c r="B275" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2484</v>
+      </c>
+      <c r="B276" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>2494</v>
+      </c>
+      <c r="B277" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>2504</v>
+      </c>
+      <c r="B278" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>2514</v>
+      </c>
+      <c r="B279" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2524</v>
+      </c>
+      <c r="B280" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2534</v>
+      </c>
+      <c r="B281" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2544</v>
+      </c>
+      <c r="B282" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>2554</v>
+      </c>
+      <c r="B283" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2564</v>
+      </c>
+      <c r="B284" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>2574</v>
+      </c>
+      <c r="B285" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>2584</v>
+      </c>
+      <c r="B286" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>2594</v>
+      </c>
+      <c r="B287" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2604</v>
+      </c>
+      <c r="B288" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>2614</v>
+      </c>
+      <c r="B289" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>2624</v>
+      </c>
+      <c r="B290" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2634</v>
+      </c>
+      <c r="B291" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2644</v>
+      </c>
+      <c r="B292" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2654</v>
+      </c>
+      <c r="B293" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2664</v>
+      </c>
+      <c r="B294" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2674</v>
+      </c>
+      <c r="B295" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2684</v>
+      </c>
+      <c r="B296" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2694</v>
+      </c>
+      <c r="B297" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2704</v>
+      </c>
+      <c r="B298" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2714</v>
+      </c>
+      <c r="B299" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>2724</v>
+      </c>
+      <c r="B300" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>2734</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>2735</v>
+      </c>
+      <c r="B302" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>2744</v>
+      </c>
+      <c r="B303" t="n">
+        <v>3.535</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>2754</v>
+      </c>
+      <c r="B304" t="n">
+        <v>2.995</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>2764</v>
+      </c>
+      <c r="B305" t="n">
+        <v>3.455</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>2774</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>2775</v>
+      </c>
+      <c r="B307" t="n">
+        <v>3.3466</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>2784</v>
+      </c>
+      <c r="B308" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>2794</v>
+      </c>
+      <c r="B309" t="n">
+        <v>3.045</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>2804</v>
+      </c>
+      <c r="B310" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>2814</v>
+      </c>
+      <c r="B311" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>2824</v>
+      </c>
+      <c r="B312" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>2834</v>
+      </c>
+      <c r="B313" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>2844</v>
+      </c>
+      <c r="B314" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>2854</v>
+      </c>
+      <c r="B315" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>2864</v>
+      </c>
+      <c r="B316" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2868</v>
+      </c>
+      <c r="B317" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>2872</v>
+      </c>
+      <c r="B318" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>2876</v>
+      </c>
+      <c r="B319" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>2880</v>
+      </c>
+      <c r="B320" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>2884</v>
+      </c>
+      <c r="B321" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2888</v>
+      </c>
+      <c r="B322" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>2892</v>
+      </c>
+      <c r="B323" t="n">
+        <v>3.185</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2896</v>
+      </c>
+      <c r="B324" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B325" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2904</v>
+      </c>
+      <c r="B326" t="n">
+        <v>2.905</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2908</v>
+      </c>
+      <c r="B327" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2912</v>
+      </c>
+      <c r="B328" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>2916</v>
+      </c>
+      <c r="B329" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2920</v>
+      </c>
+      <c r="B330" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2924</v>
+      </c>
+      <c r="B331" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2928</v>
+      </c>
+      <c r="B332" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2932</v>
+      </c>
+      <c r="B333" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2936</v>
+      </c>
+      <c r="B334" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2940</v>
+      </c>
+      <c r="B335" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>2968</v>
+      </c>
+      <c r="B336" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>2972</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>2976</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>2980</v>
+      </c>
+      <c r="B339" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>2984</v>
+      </c>
+      <c r="B340" t="n">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>2988</v>
+      </c>
+      <c r="B341" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>2992</v>
+      </c>
+      <c r="B342" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>2996</v>
+      </c>
+      <c r="B343" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3004</v>
+      </c>
+      <c r="B345" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3008</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3012</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3020</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3024</v>
+      </c>
+      <c r="B349" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3068</v>
+      </c>
+      <c r="B350" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3072</v>
+      </c>
+      <c r="B351" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3076</v>
+      </c>
+      <c r="B352" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>3080</v>
+      </c>
+      <c r="B353" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>3084</v>
+      </c>
+      <c r="B354" t="n">
+        <v>3.215</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>3088</v>
+      </c>
+      <c r="B355" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>3092</v>
+      </c>
+      <c r="B356" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>3096</v>
+      </c>
+      <c r="B357" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B358" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>3104</v>
+      </c>
+      <c r="B359" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>3114</v>
+      </c>
+      <c r="B360" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3124</v>
+      </c>
+      <c r="B361" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B362" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3144</v>
+      </c>
+      <c r="B363" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>3154</v>
+      </c>
+      <c r="B364" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>3164</v>
+      </c>
+      <c r="B365" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B366" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>3184</v>
+      </c>
+      <c r="B367" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>3194</v>
+      </c>
+      <c r="B368" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B369" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B370" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B371" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B372" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>3220</v>
+      </c>
+      <c r="B373" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>3224</v>
+      </c>
+      <c r="B374" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>3228</v>
+      </c>
+      <c r="B375" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>3232</v>
+      </c>
+      <c r="B376" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>3236</v>
+      </c>
+      <c r="B377" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>3240</v>
+      </c>
+      <c r="B378" t="n">
+        <v>3.065</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>3244</v>
+      </c>
+      <c r="B379" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>3248</v>
+      </c>
+      <c r="B380" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>3252</v>
+      </c>
+      <c r="B381" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>3256</v>
+      </c>
+      <c r="B382" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>3284</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>3288</v>
+      </c>
+      <c r="B384" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>3292</v>
+      </c>
+      <c r="B385" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -578,7 +3735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -766,7 +3923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -874,7 +4031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17886,7 +21043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26430,7 +29587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34974,7 +38131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35056,7 +38213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35138,7 +38295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -58842,23 +61999,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="24" customWidth="1" style="1" min="1" max="1"/>
     <col width="21" customWidth="1" style="1" min="2" max="2"/>
-    <col width="11" customWidth="1" style="1" min="3" max="3"/>
+    <col width="24" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
-    <col width="9" customWidth="1" style="1" min="6" max="6"/>
-    <col width="31" customWidth="1" style="1" min="7" max="7"/>
-    <col width="12" customWidth="1" style="1" min="8" max="8"/>
+    <col width="35" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="1" min="7" max="7"/>
+    <col width="172" customWidth="1" style="1" min="8" max="8"/>
+    <col width="22" customWidth="1" style="1" min="9" max="9"/>
+    <col width="21" customWidth="1" style="1" min="10" max="10"/>
+    <col width="21" customWidth="1" style="1" min="11" max="11"/>
+    <col width="10" customWidth="1" style="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>depth</t>
+          <t>years</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -58896,3095 +62057,246 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>InterpolationMode</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>X1Coords</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>X2Coords</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100</v>
+        <v>-446.9554739211987</v>
       </c>
       <c r="B2" t="n">
         <v>3.235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Series</t>
+          <t>Series interpolated</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>#962cff</t>
+          <t>#7f7f7f</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
-          <t>a comment, to be completed</t>
+          <t>Created 2026/06/08 at 18:01:33</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Imported series&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-A9AA9941&lt;/i&gt;&lt;/b&gt; interpolated with INTERPOLATION &lt;i&gt;&lt;b&gt;Id-20A10A97&lt;/i&gt;&lt;/b&gt; with mode Linear&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-1D838C92&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>124.834437086093</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1391.4678807947</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104</v>
+        <v>-445.184497129564</v>
       </c>
       <c r="B3" t="n">
         <v>3.49</v>
       </c>
+      <c r="J3" t="n">
+        <v>388.300220750552</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1986.54238410596</v>
+      </c>
+      <c r="L3" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108</v>
+        <v>-443.4135203379292</v>
       </c>
       <c r="B4" t="n">
         <v>3.535</v>
       </c>
+      <c r="J4" t="n">
+        <v>582.211037527594</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3467.08774834437</v>
+      </c>
+      <c r="L4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112</v>
+        <v>-441.6425435462944</v>
       </c>
       <c r="B5" t="n">
         <v>3.605</v>
       </c>
+      <c r="L5" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116</v>
+        <v>-439.8715667546596</v>
       </c>
       <c r="B6" t="n">
         <v>3.655</v>
       </c>
+      <c r="L6" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120</v>
+        <v>-438.1005899630248</v>
       </c>
       <c r="B7" t="n">
         <v>3.79</v>
       </c>
+      <c r="L7" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130</v>
+        <v>-433.673147983938</v>
       </c>
       <c r="B8" t="n">
         <v>3.23</v>
       </c>
+      <c r="L8" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>140</v>
+        <v>-429.2457060048509</v>
       </c>
       <c r="B9" t="n">
         <v>3.99</v>
       </c>
+      <c r="L9" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>150</v>
+        <v>-424.8182640257641</v>
       </c>
       <c r="B10" t="n">
         <v>3.88</v>
       </c>
+      <c r="L10" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>160</v>
+        <v>-420.390822046677</v>
       </c>
       <c r="B11" t="n">
         <v>3.95</v>
       </c>
+      <c r="L11" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>-420.390822046677</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="L12" t="n">
         <v>160</v>
-      </c>
-      <c r="B12" t="n">
-        <v>4.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>180</v>
+        <v>-420.390822046677</v>
       </c>
       <c r="B13" t="n">
-        <v>3.82</v>
+        <v>4.09</v>
+      </c>
+      <c r="L13" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>190</v>
+        <v>-411.5359380885031</v>
       </c>
       <c r="B14" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
+      </c>
+      <c r="L14" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>200</v>
+        <v>-407.1084961094163</v>
       </c>
       <c r="B15" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
+      </c>
+      <c r="L15" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>210</v>
+        <v>-402.6810541303292</v>
       </c>
       <c r="B16" t="n">
-        <v>4.08</v>
+        <v>3.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>220</v>
+        <v>-398.2536121512424</v>
       </c>
       <c r="B17" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>230</v>
-      </c>
-      <c r="B18" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>240</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>250</v>
-      </c>
-      <c r="B20" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>260</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>270</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>280</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>290</v>
-      </c>
-      <c r="B24" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>300</v>
-      </c>
-      <c r="B25" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>310</v>
-      </c>
-      <c r="B26" t="n">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>320</v>
-      </c>
-      <c r="B27" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>330</v>
-      </c>
-      <c r="B28" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>340</v>
-      </c>
-      <c r="B29" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>350</v>
-      </c>
-      <c r="B30" t="n">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>360</v>
-      </c>
-      <c r="B31" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>370</v>
-      </c>
-      <c r="B32" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>380</v>
-      </c>
-      <c r="B33" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>390</v>
-      </c>
-      <c r="B34" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>400</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>410</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>420</v>
-      </c>
-      <c r="B37" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>430</v>
-      </c>
-      <c r="B38" t="n">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>440</v>
-      </c>
-      <c r="B39" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>450</v>
-      </c>
-      <c r="B40" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>460</v>
-      </c>
-      <c r="B41" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>470</v>
-      </c>
-      <c r="B42" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>480</v>
-      </c>
-      <c r="B43" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>490</v>
-      </c>
-      <c r="B44" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>500</v>
-      </c>
-      <c r="B45" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>510</v>
-      </c>
-      <c r="B46" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>520</v>
-      </c>
-      <c r="B47" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>530</v>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>540</v>
-      </c>
-      <c r="B49" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>560</v>
-      </c>
-      <c r="B50" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>570</v>
-      </c>
-      <c r="B51" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>580</v>
-      </c>
-      <c r="B52" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>590</v>
-      </c>
-      <c r="B53" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>600</v>
-      </c>
-      <c r="B54" t="n">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>610</v>
-      </c>
-      <c r="B55" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>620</v>
-      </c>
-      <c r="B56" t="n">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>630</v>
-      </c>
-      <c r="B57" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>640</v>
-      </c>
-      <c r="B58" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>650</v>
-      </c>
-      <c r="B59" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>660</v>
-      </c>
-      <c r="B60" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>670</v>
-      </c>
-      <c r="B61" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>680</v>
-      </c>
-      <c r="B62" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>690</v>
-      </c>
-      <c r="B63" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>700</v>
-      </c>
-      <c r="B64" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>710</v>
-      </c>
-      <c r="B65" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>720</v>
-      </c>
-      <c r="B66" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>730</v>
-      </c>
-      <c r="B67" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>740</v>
-      </c>
-      <c r="B68" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>750</v>
-      </c>
-      <c r="B69" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>760</v>
-      </c>
-      <c r="B70" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>770</v>
-      </c>
-      <c r="B71" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>780</v>
-      </c>
-      <c r="B72" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>790</v>
-      </c>
-      <c r="B73" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>800</v>
-      </c>
-      <c r="B74" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>810</v>
-      </c>
-      <c r="B75" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>820</v>
-      </c>
-      <c r="B76" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>830</v>
-      </c>
-      <c r="B77" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>840</v>
-      </c>
-      <c r="B78" t="n">
-        <v>3.395</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>850</v>
-      </c>
-      <c r="B79" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>860</v>
-      </c>
-      <c r="B80" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>870</v>
-      </c>
-      <c r="B81" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>880</v>
-      </c>
-      <c r="B82" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>890</v>
-      </c>
-      <c r="B83" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>900</v>
-      </c>
-      <c r="B84" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>910</v>
-      </c>
-      <c r="B85" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>920</v>
-      </c>
-      <c r="B86" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>930</v>
-      </c>
-      <c r="B87" t="n">
-        <v>3.835</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>940</v>
-      </c>
-      <c r="B88" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>950</v>
-      </c>
-      <c r="B89" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>960</v>
-      </c>
-      <c r="B90" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>970</v>
-      </c>
-      <c r="B91" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>980</v>
-      </c>
-      <c r="B92" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>990</v>
-      </c>
-      <c r="B93" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B94" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>1010</v>
-      </c>
-      <c r="B95" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>1020</v>
-      </c>
-      <c r="B96" t="n">
-        <v>3.365</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>1030</v>
-      </c>
-      <c r="B97" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>1040</v>
-      </c>
-      <c r="B98" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>1050</v>
-      </c>
-      <c r="B99" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>1060</v>
-      </c>
-      <c r="B100" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>1070</v>
-      </c>
-      <c r="B101" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>1080</v>
-      </c>
-      <c r="B102" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>1087</v>
-      </c>
-      <c r="B103" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>1097</v>
-      </c>
-      <c r="B104" t="n">
-        <v>3.5833</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>1107</v>
-      </c>
-      <c r="B105" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>1117</v>
-      </c>
-      <c r="B106" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>1127</v>
-      </c>
-      <c r="B107" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>1137</v>
-      </c>
-      <c r="B108" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>1147</v>
-      </c>
-      <c r="B109" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>1157</v>
-      </c>
-      <c r="B110" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>1167</v>
-      </c>
-      <c r="B111" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>1177</v>
-      </c>
-      <c r="B112" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>1187</v>
-      </c>
-      <c r="B113" t="n">
-        <v>3.355</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>1197</v>
-      </c>
-      <c r="B114" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>1207</v>
-      </c>
-      <c r="B115" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>1217</v>
-      </c>
-      <c r="B116" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>1227</v>
-      </c>
-      <c r="B117" t="n">
-        <v>3.5333</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>1237</v>
-      </c>
-      <c r="B118" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>1247</v>
-      </c>
-      <c r="B119" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>1257</v>
-      </c>
-      <c r="B120" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>1267</v>
-      </c>
-      <c r="B121" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>1277</v>
-      </c>
-      <c r="B122" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>1287</v>
-      </c>
-      <c r="B123" t="n">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>1297</v>
-      </c>
-      <c r="B124" t="n">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>1307</v>
-      </c>
-      <c r="B125" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>1317</v>
-      </c>
-      <c r="B126" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>1327</v>
-      </c>
-      <c r="B127" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>1337</v>
-      </c>
-      <c r="B128" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>1347</v>
-      </c>
-      <c r="B129" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>1357</v>
-      </c>
-      <c r="B130" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>1367</v>
-      </c>
-      <c r="B131" t="n">
-        <v>3.385</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B132" t="n">
-        <v>3.345</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>1387</v>
-      </c>
-      <c r="B133" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>1397</v>
-      </c>
-      <c r="B134" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>1407</v>
-      </c>
-      <c r="B135" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>1417</v>
-      </c>
-      <c r="B136" t="n">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>1427</v>
-      </c>
-      <c r="B137" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>1437</v>
-      </c>
-      <c r="B138" t="n">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>1447</v>
-      </c>
-      <c r="B139" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>1457</v>
-      </c>
-      <c r="B140" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>1467</v>
-      </c>
-      <c r="B141" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>1477</v>
-      </c>
-      <c r="B142" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>1487</v>
-      </c>
-      <c r="B143" t="n">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>1497</v>
-      </c>
-      <c r="B144" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>1507</v>
-      </c>
-      <c r="B145" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>1511</v>
-      </c>
-      <c r="B146" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>1515</v>
-      </c>
-      <c r="B147" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>1519</v>
-      </c>
-      <c r="B148" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>1523</v>
-      </c>
-      <c r="B149" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>1527</v>
-      </c>
-      <c r="B150" t="n">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>1531</v>
-      </c>
-      <c r="B151" t="n">
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>1535</v>
-      </c>
-      <c r="B152" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>1537</v>
-      </c>
-      <c r="B153" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>1541</v>
-      </c>
-      <c r="B154" t="n">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>1545</v>
-      </c>
-      <c r="B155" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>1549</v>
-      </c>
-      <c r="B156" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>1553</v>
-      </c>
-      <c r="B157" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>1557</v>
-      </c>
-      <c r="B158" t="n">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>1561</v>
-      </c>
-      <c r="B159" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>1565</v>
-      </c>
-      <c r="B160" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>1569</v>
-      </c>
-      <c r="B161" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>1573</v>
-      </c>
-      <c r="B162" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>1577</v>
-      </c>
-      <c r="B163" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>1581</v>
-      </c>
-      <c r="B164" t="n">
-        <v>3.1175</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>1585</v>
-      </c>
-      <c r="B165" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>1589</v>
-      </c>
-      <c r="B166" t="n">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>1593</v>
-      </c>
-      <c r="B167" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>1597</v>
-      </c>
-      <c r="B168" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>1601</v>
-      </c>
-      <c r="B169" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>1605</v>
-      </c>
-      <c r="B170" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>1609</v>
-      </c>
-      <c r="B171" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>1645</v>
-      </c>
-      <c r="B172" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>1649</v>
-      </c>
-      <c r="B173" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>1653</v>
-      </c>
-      <c r="B174" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>1657</v>
-      </c>
-      <c r="B175" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>1661</v>
-      </c>
-      <c r="B176" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>1665</v>
-      </c>
-      <c r="B177" t="n">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>1669</v>
-      </c>
-      <c r="B178" t="n">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>1673</v>
-      </c>
-      <c r="B179" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>1677</v>
-      </c>
-      <c r="B180" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>1681</v>
-      </c>
-      <c r="B181" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>1685</v>
-      </c>
-      <c r="B182" t="n">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>1689</v>
-      </c>
-      <c r="B183" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>1693</v>
-      </c>
-      <c r="B184" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>1697</v>
-      </c>
-      <c r="B185" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>1701</v>
-      </c>
-      <c r="B186" t="n">
-        <v>2.67</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>1705</v>
-      </c>
-      <c r="B187" t="n">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>1709</v>
-      </c>
-      <c r="B188" t="n">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>1761</v>
-      </c>
-      <c r="B189" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>1765</v>
-      </c>
-      <c r="B190" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>1769</v>
-      </c>
-      <c r="B191" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>1773</v>
-      </c>
-      <c r="B192" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>1777</v>
-      </c>
-      <c r="B193" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>1781</v>
-      </c>
-      <c r="B194" t="n">
-        <v>3.355</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>1785</v>
-      </c>
-      <c r="B195" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>1789</v>
-      </c>
-      <c r="B196" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>1793</v>
-      </c>
-      <c r="B197" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>1797</v>
-      </c>
-      <c r="B198" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>1801</v>
-      </c>
-      <c r="B199" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B200" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>1809</v>
-      </c>
-      <c r="B201" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>1813</v>
-      </c>
-      <c r="B202" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>1817</v>
-      </c>
-      <c r="B203" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>1821</v>
-      </c>
-      <c r="B204" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>1825</v>
-      </c>
-      <c r="B205" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>1829</v>
-      </c>
-      <c r="B206" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>1833</v>
-      </c>
-      <c r="B207" t="n">
-        <v>2.705</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>1837</v>
-      </c>
-      <c r="B208" t="n">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>1884</v>
-      </c>
-      <c r="B209" t="n">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>1888</v>
-      </c>
-      <c r="B210" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>1892</v>
-      </c>
-      <c r="B211" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>1896</v>
-      </c>
-      <c r="B212" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>1900</v>
-      </c>
-      <c r="B213" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>1904</v>
-      </c>
-      <c r="B214" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B215" t="n">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>1912</v>
-      </c>
-      <c r="B216" t="n">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>1916</v>
-      </c>
-      <c r="B217" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>1920</v>
-      </c>
-      <c r="B218" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B219" t="n">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>1928</v>
-      </c>
-      <c r="B220" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B221" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>1948</v>
-      </c>
-      <c r="B222" t="n">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B223" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B224" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B225" t="n">
-        <v>4.0733</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B226" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B227" t="n">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B228" t="n">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B229" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B230" t="n">
-        <v>3.9966</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B231" t="n">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>2048</v>
-      </c>
-      <c r="B232" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>2058</v>
-      </c>
-      <c r="B233" t="n">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>2068</v>
-      </c>
-      <c r="B234" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>2078</v>
-      </c>
-      <c r="B235" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>2088</v>
-      </c>
-      <c r="B236" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>2098</v>
-      </c>
-      <c r="B237" t="n">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>2108</v>
-      </c>
-      <c r="B238" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>2118</v>
-      </c>
-      <c r="B239" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>2128</v>
-      </c>
-      <c r="B240" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>2138</v>
-      </c>
-      <c r="B241" t="n">
-        <v>3.625</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>2148</v>
-      </c>
-      <c r="B242" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>2158</v>
-      </c>
-      <c r="B243" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>2168</v>
-      </c>
-      <c r="B244" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>2178</v>
-      </c>
-      <c r="B245" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>2188</v>
-      </c>
-      <c r="B246" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>2198</v>
-      </c>
-      <c r="B247" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>2208</v>
-      </c>
-      <c r="B248" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>2218</v>
-      </c>
-      <c r="B249" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>2228</v>
-      </c>
-      <c r="B250" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>2238</v>
-      </c>
-      <c r="B251" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>2248</v>
-      </c>
-      <c r="B252" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>2258</v>
-      </c>
-      <c r="B253" t="n">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>2268</v>
-      </c>
-      <c r="B254" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>2278</v>
-      </c>
-      <c r="B255" t="n">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>2288</v>
-      </c>
-      <c r="B256" t="n">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>2298</v>
-      </c>
-      <c r="B257" t="n">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>2308</v>
-      </c>
-      <c r="B258" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>2318</v>
-      </c>
-      <c r="B259" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>2328</v>
-      </c>
-      <c r="B260" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>2338</v>
-      </c>
-      <c r="B261" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>2348</v>
-      </c>
-      <c r="B262" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>2358</v>
-      </c>
-      <c r="B263" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>2368</v>
-      </c>
-      <c r="B264" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>2374</v>
-      </c>
-      <c r="B265" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>2384</v>
-      </c>
-      <c r="B266" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>2394</v>
-      </c>
-      <c r="B267" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>2404</v>
-      </c>
-      <c r="B268" t="n">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>2414</v>
-      </c>
-      <c r="B269" t="n">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>2424</v>
-      </c>
-      <c r="B270" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>2434</v>
-      </c>
-      <c r="B271" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>2444</v>
-      </c>
-      <c r="B272" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>2454</v>
-      </c>
-      <c r="B273" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>2464</v>
-      </c>
-      <c r="B274" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>2474</v>
-      </c>
-      <c r="B275" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>2484</v>
-      </c>
-      <c r="B276" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>2494</v>
-      </c>
-      <c r="B277" t="n">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>2504</v>
-      </c>
-      <c r="B278" t="n">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>2514</v>
-      </c>
-      <c r="B279" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>2524</v>
-      </c>
-      <c r="B280" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>2534</v>
-      </c>
-      <c r="B281" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>2544</v>
-      </c>
-      <c r="B282" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>2554</v>
-      </c>
-      <c r="B283" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>2564</v>
-      </c>
-      <c r="B284" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>2574</v>
-      </c>
-      <c r="B285" t="n">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>2584</v>
-      </c>
-      <c r="B286" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>2594</v>
-      </c>
-      <c r="B287" t="n">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>2604</v>
-      </c>
-      <c r="B288" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>2614</v>
-      </c>
-      <c r="B289" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>2624</v>
-      </c>
-      <c r="B290" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>2634</v>
-      </c>
-      <c r="B291" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>2644</v>
-      </c>
-      <c r="B292" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>2654</v>
-      </c>
-      <c r="B293" t="n">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>2664</v>
-      </c>
-      <c r="B294" t="n">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>2674</v>
-      </c>
-      <c r="B295" t="n">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>2684</v>
-      </c>
-      <c r="B296" t="n">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>2694</v>
-      </c>
-      <c r="B297" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>2704</v>
-      </c>
-      <c r="B298" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>2714</v>
-      </c>
-      <c r="B299" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>2724</v>
-      </c>
-      <c r="B300" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>2734</v>
-      </c>
-      <c r="B301" t="n">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>2735</v>
-      </c>
-      <c r="B302" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>2744</v>
-      </c>
-      <c r="B303" t="n">
-        <v>3.535</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>2754</v>
-      </c>
-      <c r="B304" t="n">
-        <v>2.995</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>2764</v>
-      </c>
-      <c r="B305" t="n">
-        <v>3.455</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>2774</v>
-      </c>
-      <c r="B306" t="n">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>2775</v>
-      </c>
-      <c r="B307" t="n">
-        <v>3.3466</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>2784</v>
-      </c>
-      <c r="B308" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>2794</v>
-      </c>
-      <c r="B309" t="n">
-        <v>3.045</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>2804</v>
-      </c>
-      <c r="B310" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>2814</v>
-      </c>
-      <c r="B311" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>2824</v>
-      </c>
-      <c r="B312" t="n">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>2834</v>
-      </c>
-      <c r="B313" t="n">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>2844</v>
-      </c>
-      <c r="B314" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>2854</v>
-      </c>
-      <c r="B315" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>2864</v>
-      </c>
-      <c r="B316" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>2868</v>
-      </c>
-      <c r="B317" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>2872</v>
-      </c>
-      <c r="B318" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>2876</v>
-      </c>
-      <c r="B319" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>2880</v>
-      </c>
-      <c r="B320" t="n">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>2884</v>
-      </c>
-      <c r="B321" t="n">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>2888</v>
-      </c>
-      <c r="B322" t="n">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>2892</v>
-      </c>
-      <c r="B323" t="n">
-        <v>3.185</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>2896</v>
-      </c>
-      <c r="B324" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>2900</v>
-      </c>
-      <c r="B325" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>2904</v>
-      </c>
-      <c r="B326" t="n">
-        <v>2.905</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>2908</v>
-      </c>
-      <c r="B327" t="n">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>2912</v>
-      </c>
-      <c r="B328" t="n">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>2916</v>
-      </c>
-      <c r="B329" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>2920</v>
-      </c>
-      <c r="B330" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>2924</v>
-      </c>
-      <c r="B331" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>2928</v>
-      </c>
-      <c r="B332" t="n">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>2932</v>
-      </c>
-      <c r="B333" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>2936</v>
-      </c>
-      <c r="B334" t="n">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>2940</v>
-      </c>
-      <c r="B335" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>2968</v>
-      </c>
-      <c r="B336" t="n">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>2972</v>
-      </c>
-      <c r="B337" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>2976</v>
-      </c>
-      <c r="B338" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>2980</v>
-      </c>
-      <c r="B339" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>2984</v>
-      </c>
-      <c r="B340" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>2988</v>
-      </c>
-      <c r="B341" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>2992</v>
-      </c>
-      <c r="B342" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>2996</v>
-      </c>
-      <c r="B343" t="n">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B344" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>3004</v>
-      </c>
-      <c r="B345" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>3008</v>
-      </c>
-      <c r="B346" t="n">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>3012</v>
-      </c>
-      <c r="B347" t="n">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>3020</v>
-      </c>
-      <c r="B348" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>3024</v>
-      </c>
-      <c r="B349" t="n">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>3068</v>
-      </c>
-      <c r="B350" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>3072</v>
-      </c>
-      <c r="B351" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>3076</v>
-      </c>
-      <c r="B352" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>3080</v>
-      </c>
-      <c r="B353" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>3084</v>
-      </c>
-      <c r="B354" t="n">
-        <v>3.215</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>3088</v>
-      </c>
-      <c r="B355" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>3092</v>
-      </c>
-      <c r="B356" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>3096</v>
-      </c>
-      <c r="B357" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>3100</v>
-      </c>
-      <c r="B358" t="n">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>3104</v>
-      </c>
-      <c r="B359" t="n">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>3114</v>
-      </c>
-      <c r="B360" t="n">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>3124</v>
-      </c>
-      <c r="B361" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>3134</v>
-      </c>
-      <c r="B362" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>3144</v>
-      </c>
-      <c r="B363" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>3154</v>
-      </c>
-      <c r="B364" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>3164</v>
-      </c>
-      <c r="B365" t="n">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>3174</v>
-      </c>
-      <c r="B366" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
-        <v>3184</v>
-      </c>
-      <c r="B367" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="n">
-        <v>3194</v>
-      </c>
-      <c r="B368" t="n">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="n">
-        <v>3204</v>
-      </c>
-      <c r="B369" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="n">
-        <v>3208</v>
-      </c>
-      <c r="B370" t="n">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="n">
-        <v>3212</v>
-      </c>
-      <c r="B371" t="n">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
-        <v>3216</v>
-      </c>
-      <c r="B372" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="n">
-        <v>3220</v>
-      </c>
-      <c r="B373" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="n">
-        <v>3224</v>
-      </c>
-      <c r="B374" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="n">
-        <v>3228</v>
-      </c>
-      <c r="B375" t="n">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="n">
-        <v>3232</v>
-      </c>
-      <c r="B376" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="n">
-        <v>3236</v>
-      </c>
-      <c r="B377" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="n">
-        <v>3240</v>
-      </c>
-      <c r="B378" t="n">
-        <v>3.065</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="n">
-        <v>3244</v>
-      </c>
-      <c r="B379" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="n">
-        <v>3248</v>
-      </c>
-      <c r="B380" t="n">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="n">
-        <v>3252</v>
-      </c>
-      <c r="B381" t="n">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="n">
-        <v>3256</v>
-      </c>
-      <c r="B382" t="n">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="n">
-        <v>3284</v>
-      </c>
-      <c r="B383" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="n">
-        <v>3288</v>
-      </c>
-      <c r="B384" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="n">
-        <v>3292</v>
-      </c>
-      <c r="B385" t="n">
-        <v>3.35</v>
+        <v>4.08</v>
+      </c>
+      <c r="L17" t="n">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/test/ws_ex.xlsx
+++ b/test/ws_ex.xlsx
@@ -469,7 +469,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v6.34</t>
+          <t>Created with PyAnalyseries v6.35</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2026/06/08 at 18:01:44</t>
+          <t>Saved 2026/06/23 at 16:12:18</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:I385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -518,6 +518,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="31" customWidth="1" style="1" min="7" max="7"/>
     <col width="12" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,6 +562,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -587,6 +593,11 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3741,7 +3752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -3752,6 +3763,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="20" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3795,6 +3807,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3819,6 +3836,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Imported series</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2116"/>
+  <dimension ref="A1:I2116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="1" min="1" max="1"/>
@@ -4048,6 +4070,7 @@
     <col width="35" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="61" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4091,6 +4114,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4123,6 +4151,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Imported series&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-AE86905A&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1058"/>
+  <dimension ref="A1:I1058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -21060,6 +21093,7 @@
     <col width="35" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="82" customWidth="1" style="1" min="8" max="8"/>
+    <col width="88" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21103,6 +21137,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -21131,6 +21170,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Spectral estimation: method=MTM; NW=4.0 ---&gt; series &lt;i&gt;&lt;b&gt;Id-1AEAF37E&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{"xaxis":{"invert":true,"type":"log1-2-5"},"yaxis":{"invert":false,"type":"log10"}}</t>
         </is>
       </c>
     </row>
@@ -29593,7 +29637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1058"/>
+  <dimension ref="A1:I1058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -29604,6 +29648,7 @@
     <col width="35" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="95" customWidth="1" style="1" min="8" max="8"/>
+    <col width="88" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29647,6 +29692,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -29675,6 +29725,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Spectral estimation: method=Periodogram; window=hann ---&gt; series &lt;i&gt;&lt;b&gt;Id-313FFF47&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{"xaxis":{"invert":true,"type":"log1-2-5"},"yaxis":{"invert":false,"type":"log10"}}</t>
         </is>
       </c>
     </row>
@@ -38383,7 +38438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1002"/>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -38394,6 +38449,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="144" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38437,6 +38493,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -38461,6 +38522,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Insolation series "Daily insolation" with parameters:&lt;ul&gt;&lt;li&gt;Solar constant [W/m2]: 1365&lt;li&gt;Latitude [°]: 65&lt;li&gt;True longitude [°]: 90&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -46475,7 +46541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:I385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -46486,6 +46552,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="12" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46529,6 +46596,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -46555,6 +46627,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -49631,7 +49708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -49642,6 +49719,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="185" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49685,6 +49763,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -49713,6 +49796,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Series &lt;i&gt;&lt;b&gt;Id-34AE56JH&lt;/i&gt;&lt;/b&gt; sampled every 50.0 and linear interpolation with integration at True with SAMPLE &lt;i&gt;&lt;b&gt;Id-4EA5A3B8&lt;/i&gt;&lt;/b&gt;&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-E0961C19&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -50327,7 +50415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -50338,6 +50426,7 @@
     <col width="35" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="176" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -50381,6 +50470,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -50409,6 +50503,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Imported series&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-A9AA9941&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-C0561A76&lt;/i&gt;&lt;/b&gt; with a moving average of size 3&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-D81474CD&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -50535,7 +50634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:I385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -50546,6 +50645,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="12" customWidth="1" style="1" min="8" max="8"/>
+    <col width="135" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -50589,6 +50689,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -50615,6 +50720,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{"xaxis":{"invert":false,"lim1":null,"lim2":null,"type":"linear"},"yaxis":{"invert":false,"lim1":0.0,"lim2":10.0,"type":"linear"}}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -53691,7 +53801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1002"/>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" style="1" min="1" max="1"/>
@@ -53702,6 +53812,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="36" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -53745,6 +53856,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -53773,6 +53889,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Astronomical series "Obliquity"</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -61787,7 +61908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="1" min="1" max="1"/>
@@ -61798,6 +61919,7 @@
     <col width="9" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="20" customWidth="1" style="1" min="8" max="8"/>
+    <col width="133" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -61841,6 +61963,11 @@
           <t>History</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -61865,6 +61992,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Imported series</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{"xaxis":{"invert":false,"lim1":null,"lim2":null,"type":"linear"},"yaxis":{"invert":true,"lim1":0.0,"lim2":7.0,"type":"linear"}}</t>
         </is>
       </c>
     </row>
@@ -61999,10 +62131,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="1" min="1" max="1"/>
+    <col width="23" customWidth="1" style="1" min="1" max="1"/>
     <col width="21" customWidth="1" style="1" min="2" max="2"/>
     <col width="24" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
@@ -62010,10 +62142,11 @@
     <col width="35" customWidth="1" style="1" min="6" max="6"/>
     <col width="12" customWidth="1" style="1" min="7" max="7"/>
     <col width="172" customWidth="1" style="1" min="8" max="8"/>
-    <col width="22" customWidth="1" style="1" min="9" max="9"/>
-    <col width="21" customWidth="1" style="1" min="10" max="10"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
+    <col width="22" customWidth="1" style="1" min="10" max="10"/>
     <col width="21" customWidth="1" style="1" min="11" max="11"/>
-    <col width="10" customWidth="1" style="1" min="12" max="12"/>
+    <col width="21" customWidth="1" style="1" min="12" max="12"/>
+    <col width="10" customWidth="1" style="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -62059,20 +62192,25 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>AxisSettings</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>InterpolationMode</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>X1Coords</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>X2Coords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
@@ -62109,16 +62247,21 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Linear</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>124.834437086093</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1391.4678807947</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -62129,13 +62272,13 @@
       <c r="B3" t="n">
         <v>3.49</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>388.300220750552</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1986.54238410596</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>104</v>
       </c>
     </row>
@@ -62146,13 +62289,13 @@
       <c r="B4" t="n">
         <v>3.535</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>582.211037527594</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>3467.08774834437</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>108</v>
       </c>
     </row>
@@ -62163,7 +62306,7 @@
       <c r="B5" t="n">
         <v>3.605</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>112</v>
       </c>
     </row>
@@ -62174,7 +62317,7 @@
       <c r="B6" t="n">
         <v>3.655</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>116</v>
       </c>
     </row>
@@ -62185,7 +62328,7 @@
       <c r="B7" t="n">
         <v>3.79</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>120</v>
       </c>
     </row>
@@ -62196,7 +62339,7 @@
       <c r="B8" t="n">
         <v>3.23</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>130</v>
       </c>
     </row>
@@ -62207,7 +62350,7 @@
       <c r="B9" t="n">
         <v>3.99</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>140</v>
       </c>
     </row>
@@ -62218,7 +62361,7 @@
       <c r="B10" t="n">
         <v>3.88</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>150</v>
       </c>
     </row>
@@ -62229,7 +62372,7 @@
       <c r="B11" t="n">
         <v>3.95</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>160</v>
       </c>
     </row>
@@ -62240,7 +62383,7 @@
       <c r="B12" t="n">
         <v>5.03</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>160</v>
       </c>
     </row>
@@ -62251,7 +62394,7 @@
       <c r="B13" t="n">
         <v>4.09</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>160</v>
       </c>
     </row>
@@ -62262,7 +62405,7 @@
       <c r="B14" t="n">
         <v>3.82</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>180</v>
       </c>
     </row>
@@ -62273,7 +62416,7 @@
       <c r="B15" t="n">
         <v>3.81</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>190</v>
       </c>
     </row>
@@ -62284,7 +62427,7 @@
       <c r="B16" t="n">
         <v>3.9</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>200</v>
       </c>
     </row>
@@ -62295,7 +62438,7 @@
       <c r="B17" t="n">
         <v>4.08</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>210</v>
       </c>
     </row>
